--- a/InputData/trans/AIiBCbVT/Ann Impvmt in Bat Cap by Veh Type.xlsx
+++ b/InputData/trans/AIiBCbVT/Ann Impvmt in Bat Cap by Veh Type.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\LA\trans\AIiBCbVT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\trans\AIiBCbVT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{02713715-C041-4155-A380-C21B10B4A348}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABBE6D39-0A27-45C8-9DE2-3E3243F2013A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2250" yWindow="2250" windowWidth="21600" windowHeight="12645" xr2:uid="{374B4FBC-450D-4288-A34A-EB3F11585D06}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{374B4FBC-450D-4288-A34A-EB3F11585D06}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -81,7 +81,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="225">
   <si>
     <t>AIiBCbVT Annual Improvement in Battery Capacity by Vehicle Type</t>
   </si>
@@ -815,9 +815,6 @@
   <si>
     <t>Estimated freight vehicle miles traveled by vehicle class</t>
   </si>
-  <si>
-    <t>Louisiana</t>
-  </si>
 </sst>
 </file>
 
@@ -828,7 +825,7 @@
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1306,7 +1303,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="116">
+  <cellXfs count="115">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyFont="1"/>
@@ -1494,28 +1491,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="centerContinuous"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" xfId="3" applyFill="1"/>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" xfId="5" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1548,15 +1536,23 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" xfId="3" applyFill="1"/>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" xfId="5" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2146,63 +2142,57 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C572C255-1CE5-4B90-9F93-9029BE5772B2}">
-  <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="60.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>225</v>
-      </c>
-      <c r="C1" s="100">
-        <v>45391</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="B3" s="99" t="s">
+      <c r="B3" s="114" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2">
       <c r="A4" s="1"/>
       <c r="B4" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2">
       <c r="B5" s="88">
         <v>2022</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2">
       <c r="B6" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="99" t="s">
+    <row r="8" spans="1:2">
+      <c r="B8" s="114" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2">
       <c r="B9" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2">
       <c r="B10" s="88">
         <v>2024</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2">
       <c r="B11" t="s">
         <v>224</v>
       </c>
@@ -2215,9 +2205,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0BFFAA5-E2EC-4E15-BFB4-74AA3CE497CC}">
   <dimension ref="A1:AG187"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:33">
       <c r="A1" s="55" t="s">
         <v>88</v>
       </c>
@@ -2256,7 +2246,7 @@
       <c r="AF1" s="3"/>
       <c r="AG1" s="3"/>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:33">
       <c r="A2" s="3" t="s">
         <v>90</v>
       </c>
@@ -2297,7 +2287,7 @@
       <c r="AF2" s="3"/>
       <c r="AG2" s="3"/>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:33">
       <c r="A3" s="3" t="s">
         <v>92</v>
       </c>
@@ -2336,7 +2326,7 @@
       <c r="AF3" s="3"/>
       <c r="AG3" s="3"/>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:33">
       <c r="A4" s="3" t="s">
         <v>9</v>
       </c>
@@ -2375,7 +2365,7 @@
       <c r="AF4" s="3"/>
       <c r="AG4" s="3"/>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:33">
       <c r="A5" s="3" t="s">
         <v>93</v>
       </c>
@@ -2414,7 +2404,7 @@
       <c r="AF5" s="3"/>
       <c r="AG5" s="3"/>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:33">
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -2449,7 +2439,7 @@
       <c r="AF6" s="3"/>
       <c r="AG6" s="3"/>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:33">
       <c r="A7" s="58" t="s">
         <v>94</v>
       </c>
@@ -2480,7 +2470,7 @@
       <c r="AF7" s="3"/>
       <c r="AG7" s="3"/>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:33">
       <c r="A8" s="3" t="s">
         <v>2</v>
       </c>
@@ -2526,7 +2516,7 @@
       <c r="AF8" s="3"/>
       <c r="AG8" s="3"/>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:33">
       <c r="A9" s="3" t="s">
         <v>37</v>
       </c>
@@ -2572,7 +2562,7 @@
       <c r="AF9" s="3"/>
       <c r="AG9" s="3"/>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:33">
       <c r="A10" s="3" t="s">
         <v>38</v>
       </c>
@@ -2618,7 +2608,7 @@
       <c r="AF10" s="3"/>
       <c r="AG10" s="3"/>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:33">
       <c r="A11" s="3" t="s">
         <v>39</v>
       </c>
@@ -2664,7 +2654,7 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
     </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:33">
       <c r="A12" s="3" t="s">
         <v>40</v>
       </c>
@@ -2711,7 +2701,7 @@
       <c r="AF12" s="3"/>
       <c r="AG12" s="3"/>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:33">
       <c r="A13" s="3" t="s">
         <v>41</v>
       </c>
@@ -2757,7 +2747,7 @@
       <c r="AF13" s="3"/>
       <c r="AG13" s="3"/>
     </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:33">
       <c r="A14" s="3" t="s">
         <v>42</v>
       </c>
@@ -2803,7 +2793,7 @@
       <c r="AF14" s="3"/>
       <c r="AG14" s="3"/>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:33">
       <c r="A15" s="3" t="s">
         <v>43</v>
       </c>
@@ -2849,7 +2839,7 @@
       <c r="AF15" s="3"/>
       <c r="AG15" s="3"/>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:33">
       <c r="A16" s="3" t="s">
         <v>44</v>
       </c>
@@ -2895,7 +2885,7 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
     </row>
-    <row r="17" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:33">
       <c r="A17" s="3" t="s">
         <v>45</v>
       </c>
@@ -2941,7 +2931,7 @@
       <c r="AF17" s="3"/>
       <c r="AG17" s="3"/>
     </row>
-    <row r="18" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:33">
       <c r="A18" s="3" t="s">
         <v>46</v>
       </c>
@@ -2988,7 +2978,7 @@
       <c r="AF18" s="3"/>
       <c r="AG18" s="3"/>
     </row>
-    <row r="19" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:33">
       <c r="A19" s="3" t="s">
         <v>47</v>
       </c>
@@ -3034,7 +3024,7 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
     </row>
-    <row r="20" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:33">
       <c r="A20" s="3" t="s">
         <v>48</v>
       </c>
@@ -3080,7 +3070,7 @@
       <c r="AF20" s="3"/>
       <c r="AG20" s="3"/>
     </row>
-    <row r="21" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:33">
       <c r="A21" s="3" t="s">
         <v>87</v>
       </c>
@@ -3126,7 +3116,7 @@
       <c r="AF21" s="3"/>
       <c r="AG21" s="3"/>
     </row>
-    <row r="22" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:33">
       <c r="A22" s="3" t="s">
         <v>49</v>
       </c>
@@ -3172,7 +3162,7 @@
       <c r="AF22" s="3"/>
       <c r="AG22" s="3"/>
     </row>
-    <row r="23" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:33">
       <c r="A23" s="3" t="s">
         <v>50</v>
       </c>
@@ -3218,7 +3208,7 @@
       <c r="AF23" s="3"/>
       <c r="AG23" s="3"/>
     </row>
-    <row r="24" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:33">
       <c r="A24" s="3" t="s">
         <v>51</v>
       </c>
@@ -3265,7 +3255,7 @@
       <c r="AF24" s="3"/>
       <c r="AG24" s="3"/>
     </row>
-    <row r="25" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:33">
       <c r="A25" s="3" t="s">
         <v>52</v>
       </c>
@@ -3311,7 +3301,7 @@
       <c r="AF25" s="3"/>
       <c r="AG25" s="3"/>
     </row>
-    <row r="26" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:33">
       <c r="A26" s="3" t="s">
         <v>53</v>
       </c>
@@ -3357,7 +3347,7 @@
       <c r="AF26" s="3"/>
       <c r="AG26" s="3"/>
     </row>
-    <row r="27" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:33">
       <c r="A27" s="3" t="s">
         <v>54</v>
       </c>
@@ -3403,7 +3393,7 @@
       <c r="AF27" s="3"/>
       <c r="AG27" s="3"/>
     </row>
-    <row r="28" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:33">
       <c r="A28" s="3" t="s">
         <v>55</v>
       </c>
@@ -3449,7 +3439,7 @@
       <c r="AF28" s="3"/>
       <c r="AG28" s="3"/>
     </row>
-    <row r="29" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:33">
       <c r="A29" s="3" t="s">
         <v>56</v>
       </c>
@@ -3495,7 +3485,7 @@
       <c r="AF29" s="3"/>
       <c r="AG29" s="3"/>
     </row>
-    <row r="30" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:33">
       <c r="A30" s="3" t="s">
         <v>57</v>
       </c>
@@ -3542,7 +3532,7 @@
       <c r="AF30" s="3"/>
       <c r="AG30" s="3"/>
     </row>
-    <row r="31" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:33">
       <c r="A31" s="3" t="s">
         <v>58</v>
       </c>
@@ -3588,7 +3578,7 @@
       <c r="AF31" s="3"/>
       <c r="AG31" s="3"/>
     </row>
-    <row r="32" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:33">
       <c r="A32" s="3" t="s">
         <v>59</v>
       </c>
@@ -3634,7 +3624,7 @@
       <c r="AF32" s="3"/>
       <c r="AG32" s="3"/>
     </row>
-    <row r="33" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:33">
       <c r="A33" s="3"/>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
@@ -3668,7 +3658,7 @@
       <c r="AF33" s="3"/>
       <c r="AG33" s="3"/>
     </row>
-    <row r="34" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:33">
       <c r="A34" s="3"/>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
@@ -3702,7 +3692,7 @@
       <c r="AF34" s="3"/>
       <c r="AG34" s="3"/>
     </row>
-    <row r="35" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:33">
       <c r="A35" s="58" t="s">
         <v>95</v>
       </c>
@@ -3748,7 +3738,7 @@
       <c r="AF35" s="3"/>
       <c r="AG35" s="3"/>
     </row>
-    <row r="36" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:33">
       <c r="A36" s="3" t="s">
         <v>61</v>
       </c>
@@ -3794,7 +3784,7 @@
       <c r="AF36" s="3"/>
       <c r="AG36" s="3"/>
     </row>
-    <row r="37" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:33">
       <c r="A37" s="3" t="s">
         <v>62</v>
       </c>
@@ -3840,7 +3830,7 @@
       <c r="AF37" s="3"/>
       <c r="AG37" s="3"/>
     </row>
-    <row r="38" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:33">
       <c r="A38" s="3" t="s">
         <v>63</v>
       </c>
@@ -3886,7 +3876,7 @@
       <c r="AF38" s="3"/>
       <c r="AG38" s="3"/>
     </row>
-    <row r="39" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:33">
       <c r="A39" s="3" t="s">
         <v>64</v>
       </c>
@@ -3933,7 +3923,7 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
     </row>
-    <row r="40" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:33">
       <c r="A40" s="3" t="s">
         <v>65</v>
       </c>
@@ -3979,7 +3969,7 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
     </row>
-    <row r="41" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:33">
       <c r="A41" s="3" t="s">
         <v>66</v>
       </c>
@@ -4025,7 +4015,7 @@
       <c r="AF41" s="3"/>
       <c r="AG41" s="3"/>
     </row>
-    <row r="42" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:33">
       <c r="A42" s="3" t="s">
         <v>67</v>
       </c>
@@ -4071,7 +4061,7 @@
       <c r="AF42" s="3"/>
       <c r="AG42" s="3"/>
     </row>
-    <row r="43" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:33">
       <c r="A43" s="3" t="s">
         <v>68</v>
       </c>
@@ -4117,7 +4107,7 @@
       <c r="AF43" s="3"/>
       <c r="AG43" s="3"/>
     </row>
-    <row r="44" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:33">
       <c r="A44" s="3" t="s">
         <v>69</v>
       </c>
@@ -4163,7 +4153,7 @@
       <c r="AF44" s="3"/>
       <c r="AG44" s="3"/>
     </row>
-    <row r="45" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:33">
       <c r="A45" s="3" t="s">
         <v>70</v>
       </c>
@@ -4210,7 +4200,7 @@
       <c r="AF45" s="3"/>
       <c r="AG45" s="3"/>
     </row>
-    <row r="46" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:33">
       <c r="A46" s="3" t="s">
         <v>71</v>
       </c>
@@ -4256,7 +4246,7 @@
       <c r="AF46" s="3"/>
       <c r="AG46" s="3"/>
     </row>
-    <row r="47" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:33">
       <c r="A47" s="3" t="s">
         <v>72</v>
       </c>
@@ -4302,7 +4292,7 @@
       <c r="AF47" s="3"/>
       <c r="AG47" s="3"/>
     </row>
-    <row r="48" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:33">
       <c r="A48" s="3" t="s">
         <v>73</v>
       </c>
@@ -4348,7 +4338,7 @@
       <c r="AF48" s="3"/>
       <c r="AG48" s="3"/>
     </row>
-    <row r="49" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:33">
       <c r="A49" s="3" t="s">
         <v>74</v>
       </c>
@@ -4394,7 +4384,7 @@
       <c r="AF49" s="3"/>
       <c r="AG49" s="3"/>
     </row>
-    <row r="50" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:33">
       <c r="A50" s="3" t="s">
         <v>75</v>
       </c>
@@ -4440,7 +4430,7 @@
       <c r="AF50" s="3"/>
       <c r="AG50" s="3"/>
     </row>
-    <row r="51" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:33">
       <c r="A51" s="3" t="s">
         <v>76</v>
       </c>
@@ -4487,7 +4477,7 @@
       <c r="AF51" s="3"/>
       <c r="AG51" s="3"/>
     </row>
-    <row r="52" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:33">
       <c r="A52" s="3" t="s">
         <v>77</v>
       </c>
@@ -4533,7 +4523,7 @@
       <c r="AF52" s="3"/>
       <c r="AG52" s="3"/>
     </row>
-    <row r="53" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:33">
       <c r="A53" s="3" t="s">
         <v>78</v>
       </c>
@@ -4579,7 +4569,7 @@
       <c r="AF53" s="3"/>
       <c r="AG53" s="3"/>
     </row>
-    <row r="54" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:33">
       <c r="A54" s="3" t="s">
         <v>79</v>
       </c>
@@ -4625,7 +4615,7 @@
       <c r="AF54" s="3"/>
       <c r="AG54" s="3"/>
     </row>
-    <row r="55" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:33">
       <c r="A55" s="3" t="s">
         <v>80</v>
       </c>
@@ -4671,7 +4661,7 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
     </row>
-    <row r="56" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:33">
       <c r="A56" s="3" t="s">
         <v>81</v>
       </c>
@@ -4717,7 +4707,7 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
     </row>
-    <row r="57" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:33">
       <c r="A57" s="3" t="s">
         <v>82</v>
       </c>
@@ -4764,7 +4754,7 @@
       <c r="AF57" s="3"/>
       <c r="AG57" s="3"/>
     </row>
-    <row r="58" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:33">
       <c r="A58" s="3" t="s">
         <v>83</v>
       </c>
@@ -4810,7 +4800,7 @@
       <c r="AF58" s="3"/>
       <c r="AG58" s="3"/>
     </row>
-    <row r="59" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:33">
       <c r="A59" s="3" t="s">
         <v>84</v>
       </c>
@@ -4856,7 +4846,7 @@
       <c r="AF59" s="3"/>
       <c r="AG59" s="3"/>
     </row>
-    <row r="60" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:33">
       <c r="A60" s="3"/>
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
@@ -4890,7 +4880,7 @@
       <c r="AF60" s="3"/>
       <c r="AG60" s="3"/>
     </row>
-    <row r="61" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:33">
       <c r="A61" s="53" t="s">
         <v>96</v>
       </c>
@@ -4926,7 +4916,7 @@
       <c r="AF61" s="3"/>
       <c r="AG61" s="3"/>
     </row>
-    <row r="62" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:33">
       <c r="A62" s="49" t="s">
         <v>36</v>
       </c>
@@ -4962,7 +4952,7 @@
       <c r="AF62" s="3"/>
       <c r="AG62" s="3"/>
     </row>
-    <row r="63" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:33">
       <c r="A63" s="3"/>
       <c r="C63" s="2">
         <v>2020</v>
@@ -5027,7 +5017,7 @@
       <c r="AF63" s="3"/>
       <c r="AG63" s="3"/>
     </row>
-    <row r="64" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:33">
       <c r="A64" s="54" t="s">
         <v>37</v>
       </c>
@@ -5111,7 +5101,7 @@
       <c r="AF64" s="3"/>
       <c r="AG64" s="3"/>
     </row>
-    <row r="65" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:33">
       <c r="A65" s="54" t="s">
         <v>38</v>
       </c>
@@ -5195,7 +5185,7 @@
       <c r="AF65" s="3"/>
       <c r="AG65" s="3"/>
     </row>
-    <row r="66" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:33">
       <c r="A66" s="54" t="s">
         <v>39</v>
       </c>
@@ -5279,7 +5269,7 @@
       <c r="AF66" s="3"/>
       <c r="AG66" s="3"/>
     </row>
-    <row r="67" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:33">
       <c r="A67" s="54" t="s">
         <v>40</v>
       </c>
@@ -5363,7 +5353,7 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
     </row>
-    <row r="68" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:33">
       <c r="A68" s="54" t="s">
         <v>41</v>
       </c>
@@ -5447,7 +5437,7 @@
       <c r="AF68" s="3"/>
       <c r="AG68" s="3"/>
     </row>
-    <row r="69" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:33">
       <c r="A69" s="54" t="s">
         <v>42</v>
       </c>
@@ -5531,7 +5521,7 @@
       <c r="AF69" s="3"/>
       <c r="AG69" s="3"/>
     </row>
-    <row r="70" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:33">
       <c r="A70" s="54" t="s">
         <v>43</v>
       </c>
@@ -5615,7 +5605,7 @@
       <c r="AF70" s="3"/>
       <c r="AG70" s="3"/>
     </row>
-    <row r="71" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:33">
       <c r="A71" s="54" t="s">
         <v>44</v>
       </c>
@@ -5699,7 +5689,7 @@
       <c r="AF71" s="3"/>
       <c r="AG71" s="3"/>
     </row>
-    <row r="72" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:33">
       <c r="A72" s="54" t="s">
         <v>45</v>
       </c>
@@ -5783,7 +5773,7 @@
       <c r="AF72" s="3"/>
       <c r="AG72" s="3"/>
     </row>
-    <row r="73" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:33">
       <c r="A73" s="54" t="s">
         <v>46</v>
       </c>
@@ -5867,7 +5857,7 @@
       <c r="AF73" s="3"/>
       <c r="AG73" s="3"/>
     </row>
-    <row r="74" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:33">
       <c r="A74" s="54" t="s">
         <v>47</v>
       </c>
@@ -5951,7 +5941,7 @@
       <c r="AF74" s="3"/>
       <c r="AG74" s="3"/>
     </row>
-    <row r="75" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:33">
       <c r="A75" s="54" t="s">
         <v>48</v>
       </c>
@@ -6035,7 +6025,7 @@
       <c r="AF75" s="3"/>
       <c r="AG75" s="3"/>
     </row>
-    <row r="76" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:33">
       <c r="A76" s="54" t="s">
         <v>87</v>
       </c>
@@ -6119,7 +6109,7 @@
       <c r="AF76" s="3"/>
       <c r="AG76" s="3"/>
     </row>
-    <row r="77" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:33">
       <c r="A77" s="54" t="s">
         <v>49</v>
       </c>
@@ -6203,7 +6193,7 @@
       <c r="AF77" s="3"/>
       <c r="AG77" s="3"/>
     </row>
-    <row r="78" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:33">
       <c r="A78" s="54" t="s">
         <v>50</v>
       </c>
@@ -6287,7 +6277,7 @@
       <c r="AF78" s="3"/>
       <c r="AG78" s="3"/>
     </row>
-    <row r="79" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:33">
       <c r="A79" s="54" t="s">
         <v>51</v>
       </c>
@@ -6371,7 +6361,7 @@
       <c r="AF79" s="3"/>
       <c r="AG79" s="3"/>
     </row>
-    <row r="80" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:33">
       <c r="A80" s="54" t="s">
         <v>52</v>
       </c>
@@ -6455,7 +6445,7 @@
       <c r="AF80" s="3"/>
       <c r="AG80" s="3"/>
     </row>
-    <row r="81" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:33">
       <c r="A81" s="54" t="s">
         <v>53</v>
       </c>
@@ -6539,7 +6529,7 @@
       <c r="AF81" s="3"/>
       <c r="AG81" s="3"/>
     </row>
-    <row r="82" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:33">
       <c r="A82" s="54" t="s">
         <v>54</v>
       </c>
@@ -6623,7 +6613,7 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
     </row>
-    <row r="83" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:33">
       <c r="A83" s="54" t="s">
         <v>55</v>
       </c>
@@ -6707,7 +6697,7 @@
       <c r="AF83" s="3"/>
       <c r="AG83" s="3"/>
     </row>
-    <row r="84" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:33">
       <c r="A84" s="54" t="s">
         <v>56</v>
       </c>
@@ -6791,7 +6781,7 @@
       <c r="AF84" s="3"/>
       <c r="AG84" s="3"/>
     </row>
-    <row r="85" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:33">
       <c r="A85" s="54" t="s">
         <v>57</v>
       </c>
@@ -6875,7 +6865,7 @@
       <c r="AF85" s="3"/>
       <c r="AG85" s="3"/>
     </row>
-    <row r="86" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:33">
       <c r="A86" s="54" t="s">
         <v>58</v>
       </c>
@@ -6959,7 +6949,7 @@
       <c r="AF86" s="3"/>
       <c r="AG86" s="3"/>
     </row>
-    <row r="87" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:33">
       <c r="A87" s="54" t="s">
         <v>59</v>
       </c>
@@ -7043,7 +7033,7 @@
       <c r="AF87" s="3"/>
       <c r="AG87" s="3"/>
     </row>
-    <row r="89" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:33">
       <c r="A89" s="53" t="s">
         <v>97</v>
       </c>
@@ -7080,7 +7070,7 @@
       <c r="AF89" s="3"/>
       <c r="AG89" s="3"/>
     </row>
-    <row r="90" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:33">
       <c r="A90" s="49" t="s">
         <v>60</v>
       </c>
@@ -7117,7 +7107,7 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
     </row>
-    <row r="91" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:33">
       <c r="A91" s="3"/>
       <c r="C91" s="2">
         <v>2020</v>
@@ -7183,7 +7173,7 @@
       <c r="AF91" s="3"/>
       <c r="AG91" s="3"/>
     </row>
-    <row r="92" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:33">
       <c r="A92" s="54" t="s">
         <v>61</v>
       </c>
@@ -7267,7 +7257,7 @@
       <c r="AF92" s="3"/>
       <c r="AG92" s="3"/>
     </row>
-    <row r="93" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:33">
       <c r="A93" s="54" t="s">
         <v>62</v>
       </c>
@@ -7351,7 +7341,7 @@
       <c r="AF93" s="3"/>
       <c r="AG93" s="3"/>
     </row>
-    <row r="94" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:33">
       <c r="A94" s="54" t="s">
         <v>63</v>
       </c>
@@ -7435,7 +7425,7 @@
       <c r="AF94" s="3"/>
       <c r="AG94" s="3"/>
     </row>
-    <row r="95" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:33">
       <c r="A95" s="54" t="s">
         <v>64</v>
       </c>
@@ -7519,7 +7509,7 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
     </row>
-    <row r="96" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:33">
       <c r="A96" s="54" t="s">
         <v>65</v>
       </c>
@@ -7603,7 +7593,7 @@
       <c r="AF96" s="3"/>
       <c r="AG96" s="3"/>
     </row>
-    <row r="97" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:33">
       <c r="A97" s="54" t="s">
         <v>66</v>
       </c>
@@ -7687,7 +7677,7 @@
       <c r="AF97" s="3"/>
       <c r="AG97" s="3"/>
     </row>
-    <row r="98" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:33">
       <c r="A98" s="54" t="s">
         <v>67</v>
       </c>
@@ -7771,7 +7761,7 @@
       <c r="AF98" s="3"/>
       <c r="AG98" s="3"/>
     </row>
-    <row r="99" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:33">
       <c r="A99" s="54" t="s">
         <v>68</v>
       </c>
@@ -7855,7 +7845,7 @@
       <c r="AF99" s="3"/>
       <c r="AG99" s="3"/>
     </row>
-    <row r="100" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:33">
       <c r="A100" s="54" t="s">
         <v>69</v>
       </c>
@@ -7939,7 +7929,7 @@
       <c r="AF100" s="3"/>
       <c r="AG100" s="3"/>
     </row>
-    <row r="101" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:33">
       <c r="A101" s="54" t="s">
         <v>70</v>
       </c>
@@ -8023,7 +8013,7 @@
       <c r="AF101" s="3"/>
       <c r="AG101" s="3"/>
     </row>
-    <row r="102" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:33">
       <c r="A102" s="54" t="s">
         <v>71</v>
       </c>
@@ -8107,7 +8097,7 @@
       <c r="AF102" s="3"/>
       <c r="AG102" s="3"/>
     </row>
-    <row r="103" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:33">
       <c r="A103" s="54" t="s">
         <v>72</v>
       </c>
@@ -8191,7 +8181,7 @@
       <c r="AF103" s="3"/>
       <c r="AG103" s="3"/>
     </row>
-    <row r="104" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:33">
       <c r="A104" s="54" t="s">
         <v>73</v>
       </c>
@@ -8275,7 +8265,7 @@
       <c r="AF104" s="3"/>
       <c r="AG104" s="3"/>
     </row>
-    <row r="105" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:33">
       <c r="A105" s="54" t="s">
         <v>74</v>
       </c>
@@ -8359,7 +8349,7 @@
       <c r="AF105" s="3"/>
       <c r="AG105" s="3"/>
     </row>
-    <row r="106" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:33">
       <c r="A106" s="54" t="s">
         <v>75</v>
       </c>
@@ -8443,7 +8433,7 @@
       <c r="AF106" s="3"/>
       <c r="AG106" s="3"/>
     </row>
-    <row r="107" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:33">
       <c r="A107" s="54" t="s">
         <v>76</v>
       </c>
@@ -8527,7 +8517,7 @@
       <c r="AF107" s="3"/>
       <c r="AG107" s="3"/>
     </row>
-    <row r="108" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:33">
       <c r="A108" s="54" t="s">
         <v>77</v>
       </c>
@@ -8611,7 +8601,7 @@
       <c r="AF108" s="3"/>
       <c r="AG108" s="3"/>
     </row>
-    <row r="109" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:33">
       <c r="A109" s="54" t="s">
         <v>78</v>
       </c>
@@ -8695,7 +8685,7 @@
       <c r="AF109" s="3"/>
       <c r="AG109" s="3"/>
     </row>
-    <row r="110" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:33">
       <c r="A110" s="54" t="s">
         <v>79</v>
       </c>
@@ -8771,7 +8761,7 @@
       <c r="AF110" s="3"/>
       <c r="AG110" s="3"/>
     </row>
-    <row r="111" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:33">
       <c r="A111" s="54" t="s">
         <v>80</v>
       </c>
@@ -8847,7 +8837,7 @@
       <c r="AF111" s="3"/>
       <c r="AG111" s="3"/>
     </row>
-    <row r="112" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:33">
       <c r="A112" s="54" t="s">
         <v>81</v>
       </c>
@@ -8923,7 +8913,7 @@
       <c r="AF112" s="3"/>
       <c r="AG112" s="3"/>
     </row>
-    <row r="113" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:33">
       <c r="A113" s="54" t="s">
         <v>82</v>
       </c>
@@ -9009,7 +8999,7 @@
       <c r="AF113" s="3"/>
       <c r="AG113" s="3"/>
     </row>
-    <row r="114" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:33">
       <c r="A114" s="54" t="s">
         <v>83</v>
       </c>
@@ -9085,7 +9075,7 @@
       <c r="AF114" s="3"/>
       <c r="AG114" s="3"/>
     </row>
-    <row r="115" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:33">
       <c r="A115" s="54" t="s">
         <v>84</v>
       </c>
@@ -9161,8 +9151,8 @@
       <c r="AF115" s="3"/>
       <c r="AG115" s="3"/>
     </row>
-    <row r="117" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="118" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:33" ht="15.75" thickBot="1"/>
+    <row r="118" spans="1:33" ht="15.75" thickBot="1">
       <c r="A118" s="2" t="s">
         <v>1</v>
       </c>
@@ -9182,7 +9172,7 @@
       <c r="O118" s="3"/>
       <c r="P118" s="3"/>
       <c r="Q118" s="18"/>
-      <c r="R118" s="108"/>
+      <c r="R118" s="99"/>
       <c r="S118" s="19"/>
       <c r="T118" s="20"/>
       <c r="U118" s="20"/>
@@ -9197,25 +9187,25 @@
       <c r="AD118" s="20"/>
       <c r="AE118" s="20"/>
     </row>
-    <row r="119" spans="1:33" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="103" t="s">
+    <row r="119" spans="1:33" ht="23.25" thickBot="1">
+      <c r="A119" s="94" t="s">
         <v>2</v>
       </c>
-      <c r="B119" s="105" t="s">
+      <c r="B119" s="96" t="s">
         <v>3</v>
       </c>
-      <c r="C119" s="106" t="s">
+      <c r="C119" s="97" t="s">
         <v>4</v>
       </c>
-      <c r="D119" s="107"/>
-      <c r="E119" s="107"/>
-      <c r="F119" s="107"/>
-      <c r="G119" s="106" t="s">
+      <c r="D119" s="98"/>
+      <c r="E119" s="98"/>
+      <c r="F119" s="98"/>
+      <c r="G119" s="97" t="s">
         <v>5</v>
       </c>
-      <c r="H119" s="107"/>
-      <c r="I119" s="107"/>
-      <c r="J119" s="107"/>
+      <c r="H119" s="98"/>
+      <c r="I119" s="98"/>
+      <c r="J119" s="98"/>
       <c r="K119" s="3"/>
       <c r="L119" s="3"/>
       <c r="M119" s="3"/>
@@ -9223,8 +9213,8 @@
       <c r="O119" s="3"/>
       <c r="P119" s="3"/>
       <c r="Q119" s="18"/>
-      <c r="R119" s="109"/>
-      <c r="S119" s="111" t="s">
+      <c r="R119" s="100"/>
+      <c r="S119" s="102" t="s">
         <v>24</v>
       </c>
       <c r="T119" s="19" t="s">
@@ -9264,9 +9254,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="120" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="104"/>
-      <c r="B120" s="105"/>
+    <row r="120" spans="1:33" ht="15.75" thickBot="1">
+      <c r="A120" s="95"/>
+      <c r="B120" s="96"/>
       <c r="C120" s="4">
         <v>2020</v>
       </c>
@@ -9298,8 +9288,8 @@
       <c r="O120" s="3"/>
       <c r="P120" s="3"/>
       <c r="Q120" s="18"/>
-      <c r="R120" s="110"/>
-      <c r="S120" s="112"/>
+      <c r="R120" s="101"/>
+      <c r="S120" s="103"/>
       <c r="T120" s="22">
         <v>2022</v>
       </c>
@@ -9337,7 +9327,7 @@
         <v>2035</v>
       </c>
     </row>
-    <row r="121" spans="1:33" ht="34.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:33" ht="34.5" thickBot="1">
       <c r="A121" s="6" t="s">
         <v>6</v>
       </c>
@@ -9408,7 +9398,7 @@
         <v>252.86951483455164</v>
       </c>
     </row>
-    <row r="122" spans="1:33" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:33" ht="23.25" thickBot="1">
       <c r="A122" s="10" t="s">
         <v>8</v>
       </c>
@@ -9437,41 +9427,41 @@
       <c r="N122" s="3"/>
       <c r="O122" s="3"/>
       <c r="P122" s="3"/>
-      <c r="Q122" s="113"/>
+      <c r="Q122" s="91"/>
       <c r="R122" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="S122" s="114"/>
-      <c r="T122" s="101" t="s">
+      <c r="S122" s="92"/>
+      <c r="T122" s="89" t="s">
         <v>27</v>
       </c>
-      <c r="U122" s="101" t="s">
+      <c r="U122" s="89" t="s">
         <v>27</v>
       </c>
-      <c r="V122" s="101" t="s">
+      <c r="V122" s="89" t="s">
         <v>27</v>
       </c>
-      <c r="W122" s="101" t="s">
+      <c r="W122" s="89" t="s">
         <v>27</v>
       </c>
-      <c r="X122" s="101" t="s">
+      <c r="X122" s="89" t="s">
         <v>27</v>
       </c>
-      <c r="Y122" s="101" t="s">
+      <c r="Y122" s="89" t="s">
         <v>27</v>
       </c>
-      <c r="Z122" s="101" t="s">
+      <c r="Z122" s="89" t="s">
         <v>27</v>
       </c>
-      <c r="AA122" s="101" t="s">
+      <c r="AA122" s="89" t="s">
         <v>27</v>
       </c>
-      <c r="AB122" s="101"/>
-      <c r="AC122" s="101"/>
-      <c r="AD122" s="101"/>
-      <c r="AE122" s="101"/>
-    </row>
-    <row r="123" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="AB122" s="89"/>
+      <c r="AC122" s="89"/>
+      <c r="AD122" s="89"/>
+      <c r="AE122" s="89"/>
+    </row>
+    <row r="123" spans="1:33" ht="15.75" thickBot="1">
       <c r="A123" s="6" t="s">
         <v>9</v>
       </c>
@@ -9500,25 +9490,25 @@
       <c r="N123" s="3"/>
       <c r="O123" s="3"/>
       <c r="P123" s="3"/>
-      <c r="Q123" s="113"/>
+      <c r="Q123" s="91"/>
       <c r="R123" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="S123" s="115"/>
-      <c r="T123" s="102"/>
-      <c r="U123" s="102"/>
-      <c r="V123" s="102"/>
-      <c r="W123" s="102"/>
-      <c r="X123" s="102"/>
-      <c r="Y123" s="102"/>
-      <c r="Z123" s="102"/>
-      <c r="AA123" s="102"/>
-      <c r="AB123" s="102"/>
-      <c r="AC123" s="102"/>
-      <c r="AD123" s="102"/>
-      <c r="AE123" s="102"/>
-    </row>
-    <row r="124" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="S123" s="93"/>
+      <c r="T123" s="90"/>
+      <c r="U123" s="90"/>
+      <c r="V123" s="90"/>
+      <c r="W123" s="90"/>
+      <c r="X123" s="90"/>
+      <c r="Y123" s="90"/>
+      <c r="Z123" s="90"/>
+      <c r="AA123" s="90"/>
+      <c r="AB123" s="90"/>
+      <c r="AC123" s="90"/>
+      <c r="AD123" s="90"/>
+      <c r="AE123" s="90"/>
+    </row>
+    <row r="124" spans="1:33" ht="15.75" thickBot="1">
       <c r="A124" s="10" t="s">
         <v>10</v>
       </c>
@@ -9591,7 +9581,7 @@
         <v>0.30309995733807726</v>
       </c>
     </row>
-    <row r="125" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:33" ht="15.75" thickBot="1">
       <c r="A125" s="6" t="s">
         <v>6</v>
       </c>
@@ -9674,7 +9664,7 @@
         <v>0.31939450393345609</v>
       </c>
     </row>
-    <row r="126" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:33" ht="15.75" thickBot="1">
       <c r="A126" s="10" t="s">
         <v>6</v>
       </c>
@@ -9755,7 +9745,7 @@
         <v>0.33656503959554668</v>
       </c>
     </row>
-    <row r="127" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:33" ht="15.75" thickBot="1">
       <c r="A127" s="6" t="s">
         <v>6</v>
       </c>
@@ -9836,7 +9826,7 @@
         <v>0.35465865718701378</v>
       </c>
     </row>
-    <row r="128" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:33" ht="15.75" thickBot="1">
       <c r="A128" s="10" t="s">
         <v>6</v>
       </c>
@@ -9917,7 +9907,7 @@
         <v>0.37372498126617681</v>
       </c>
     </row>
-    <row r="129" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:31" ht="15.75" thickBot="1">
       <c r="A129" s="6" t="s">
         <v>6</v>
       </c>
@@ -9998,7 +9988,7 @@
         <v>0.3927913053453399</v>
       </c>
     </row>
-    <row r="130" spans="1:31" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:31" ht="23.25" thickBot="1">
       <c r="A130" s="10" t="s">
         <v>6</v>
       </c>
@@ -10081,7 +10071,7 @@
         <v>43.366609280678752</v>
       </c>
     </row>
-    <row r="131" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:31" ht="15.75" thickBot="1">
       <c r="A131" s="6" t="s">
         <v>8</v>
       </c>
@@ -10164,7 +10154,7 @@
         <v>60.930643827305474</v>
       </c>
     </row>
-    <row r="132" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:31" ht="15.75" thickBot="1">
       <c r="A132" s="10" t="s">
         <v>8</v>
       </c>
@@ -10245,7 +10235,7 @@
         <v>80.257817134322678</v>
       </c>
     </row>
-    <row r="133" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:31" ht="15.75" thickBot="1">
       <c r="A133" s="6" t="s">
         <v>8</v>
       </c>
@@ -10326,7 +10316,7 @@
         <v>101.48693882582241</v>
       </c>
     </row>
-    <row r="134" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:31" ht="15.75" thickBot="1">
       <c r="A134" s="10" t="s">
         <v>8</v>
       </c>
@@ -10407,7 +10397,7 @@
         <v>124.76664759193905</v>
       </c>
     </row>
-    <row r="135" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:31" ht="15.75" thickBot="1">
       <c r="A135" s="6" t="s">
         <v>8</v>
       </c>
@@ -10488,7 +10478,7 @@
         <v>149.86499034714507</v>
       </c>
     </row>
-    <row r="136" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:31" ht="15.75" thickBot="1">
       <c r="A136" s="10" t="s">
         <v>8</v>
       </c>
@@ -10571,7 +10561,7 @@
         <v>64.187199212787178</v>
       </c>
     </row>
-    <row r="137" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:31" ht="15.75" thickBot="1">
       <c r="A137" s="6" t="s">
         <v>9</v>
       </c>
@@ -10654,7 +10644,7 @@
         <v>61.594360138983198</v>
       </c>
     </row>
-    <row r="138" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:31" ht="15.75" thickBot="1">
       <c r="A138" s="10" t="s">
         <v>9</v>
       </c>
@@ -10735,7 +10725,7 @@
         <v>59.493624410996297</v>
       </c>
     </row>
-    <row r="139" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:31" ht="15.75" thickBot="1">
       <c r="A139" s="6" t="s">
         <v>9</v>
       </c>
@@ -10816,7 +10806,7 @@
         <v>57.704154570920309</v>
       </c>
     </row>
-    <row r="140" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:31" ht="15.75" thickBot="1">
       <c r="A140" s="10" t="s">
         <v>9</v>
       </c>
@@ -10897,7 +10887,7 @@
         <v>56.691118280256852</v>
       </c>
     </row>
-    <row r="141" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:31" ht="15.75" thickBot="1">
       <c r="A141" s="6" t="s">
         <v>9</v>
       </c>
@@ -10978,7 +10968,7 @@
         <v>56.691118280256852</v>
       </c>
     </row>
-    <row r="142" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:31" ht="15.75" thickBot="1">
       <c r="A142" s="10" t="s">
         <v>9</v>
       </c>
@@ -11061,7 +11051,7 @@
         <v>0.44039766865078672</v>
       </c>
     </row>
-    <row r="143" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:31" ht="15.75" thickBot="1">
       <c r="A143" s="6" t="s">
         <v>10</v>
       </c>
@@ -11144,7 +11134,7 @@
         <v>0.4423415530336538</v>
       </c>
     </row>
-    <row r="144" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:31" ht="15.75" thickBot="1">
       <c r="A144" s="10" t="s">
         <v>10</v>
       </c>
@@ -11225,7 +11215,7 @@
         <v>0.44429401758567916</v>
       </c>
     </row>
-    <row r="145" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:31" ht="15.75" thickBot="1">
       <c r="A145" s="6" t="s">
         <v>10</v>
       </c>
@@ -11306,7 +11296,7 @@
         <v>0.44625510017912701</v>
       </c>
     </row>
-    <row r="146" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:31" ht="15.75" thickBot="1">
       <c r="A146" s="10" t="s">
         <v>10</v>
       </c>
@@ -11387,7 +11377,7 @@
         <v>0.44822483885342695</v>
       </c>
     </row>
-    <row r="147" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:31" ht="15.75" thickBot="1">
       <c r="A147" s="6" t="s">
         <v>10</v>
       </c>
@@ -11468,7 +11458,7 @@
         <v>0.45020327181591202</v>
       </c>
     </row>
-    <row r="148" spans="1:31" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:31" ht="23.25" thickBot="1">
       <c r="A148" s="10" t="s">
         <v>10</v>
       </c>
@@ -11551,7 +11541,7 @@
         <v>9.3256645451888076</v>
       </c>
     </row>
-    <row r="149" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:31" ht="15.75" thickBot="1">
       <c r="A149" s="6" t="s">
         <v>6</v>
       </c>
@@ -11634,7 +11624,7 @@
         <v>14.05024106040643</v>
       </c>
     </row>
-    <row r="150" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:31" ht="15.75" thickBot="1">
       <c r="A150" s="10" t="s">
         <v>6</v>
       </c>
@@ -11715,7 +11705,7 @@
         <v>18.816343783707534</v>
       </c>
     </row>
-    <row r="151" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:31" ht="15.75" thickBot="1">
       <c r="A151" s="6" t="s">
         <v>6</v>
       </c>
@@ -11796,7 +11786,7 @@
         <v>23.62424725475854</v>
       </c>
     </row>
-    <row r="152" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:31" ht="15.75" thickBot="1">
       <c r="A152" s="10" t="s">
         <v>6</v>
       </c>
@@ -11877,7 +11867,7 @@
         <v>28.474227627777672</v>
       </c>
     </row>
-    <row r="153" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:31" ht="15.75" thickBot="1">
       <c r="A153" s="6" t="s">
         <v>6</v>
       </c>
@@ -11958,7 +11948,7 @@
         <v>33.366562680439209</v>
       </c>
     </row>
-    <row r="154" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:31" ht="15.75" thickBot="1">
       <c r="A154" s="10" t="s">
         <v>6</v>
       </c>
@@ -12041,7 +12031,7 @@
         <v>83.61781376609099</v>
       </c>
     </row>
-    <row r="155" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:31" ht="15.75" thickBot="1">
       <c r="A155" s="6" t="s">
         <v>8</v>
       </c>
@@ -12124,7 +12114,7 @@
         <v>83.61781376609099</v>
       </c>
     </row>
-    <row r="156" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:31" ht="15.75" thickBot="1">
       <c r="A156" s="10" t="s">
         <v>8</v>
       </c>
@@ -12205,7 +12195,7 @@
         <v>83.61781376609099</v>
       </c>
     </row>
-    <row r="157" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:31" ht="15.75" thickBot="1">
       <c r="A157" s="6" t="s">
         <v>8</v>
       </c>
@@ -12286,7 +12276,7 @@
         <v>83.61781376609099</v>
       </c>
     </row>
-    <row r="158" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:31" ht="15.75" thickBot="1">
       <c r="A158" s="10" t="s">
         <v>8</v>
       </c>
@@ -12367,7 +12357,7 @@
         <v>83.61781376609099</v>
       </c>
     </row>
-    <row r="159" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:31" ht="15.75" thickBot="1">
       <c r="A159" s="6" t="s">
         <v>8</v>
       </c>
@@ -12448,7 +12438,7 @@
         <v>83.61781376609099</v>
       </c>
     </row>
-    <row r="160" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:31" ht="15.75" thickBot="1">
       <c r="A160" s="10" t="s">
         <v>8</v>
       </c>
@@ -12499,7 +12489,7 @@
       <c r="Z160" s="3"/>
       <c r="AA160" s="3"/>
     </row>
-    <row r="161" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:27" ht="15.75" thickBot="1">
       <c r="A161" s="6" t="s">
         <v>9</v>
       </c>
@@ -12550,7 +12540,7 @@
       <c r="Z161" s="3"/>
       <c r="AA161" s="3"/>
     </row>
-    <row r="162" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:27" ht="15.75" thickBot="1">
       <c r="A162" s="10" t="s">
         <v>9</v>
       </c>
@@ -12601,7 +12591,7 @@
       <c r="Z162" s="3"/>
       <c r="AA162" s="3"/>
     </row>
-    <row r="163" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:27" ht="15.75" thickBot="1">
       <c r="A163" s="6" t="s">
         <v>9</v>
       </c>
@@ -12652,7 +12642,7 @@
       <c r="Z163" s="3"/>
       <c r="AA163" s="3"/>
     </row>
-    <row r="164" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:27" ht="15.75" thickBot="1">
       <c r="A164" s="10" t="s">
         <v>9</v>
       </c>
@@ -12703,7 +12693,7 @@
       <c r="Z164" s="3"/>
       <c r="AA164" s="3"/>
     </row>
-    <row r="165" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:27" ht="15.75" thickBot="1">
       <c r="A165" s="6" t="s">
         <v>9</v>
       </c>
@@ -12754,7 +12744,7 @@
       <c r="Z165" s="3"/>
       <c r="AA165" s="3"/>
     </row>
-    <row r="166" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:27" ht="15.75" thickBot="1">
       <c r="A166" s="10" t="s">
         <v>9</v>
       </c>
@@ -12805,7 +12795,7 @@
       <c r="Z166" s="3"/>
       <c r="AA166" s="3"/>
     </row>
-    <row r="167" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:27" ht="15.75" thickBot="1">
       <c r="A167" s="6" t="s">
         <v>10</v>
       </c>
@@ -12856,7 +12846,7 @@
       <c r="Z167" s="3"/>
       <c r="AA167" s="3"/>
     </row>
-    <row r="168" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:27" ht="15.75" thickBot="1">
       <c r="A168" s="10" t="s">
         <v>10</v>
       </c>
@@ -12907,7 +12897,7 @@
       <c r="Z168" s="3"/>
       <c r="AA168" s="3"/>
     </row>
-    <row r="169" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:27" ht="15.75" thickBot="1">
       <c r="A169" s="6" t="s">
         <v>10</v>
       </c>
@@ -12958,7 +12948,7 @@
       <c r="Z169" s="3"/>
       <c r="AA169" s="3"/>
     </row>
-    <row r="170" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:27" ht="15.75" thickBot="1">
       <c r="A170" s="10" t="s">
         <v>10</v>
       </c>
@@ -13009,7 +12999,7 @@
       <c r="Z170" s="3"/>
       <c r="AA170" s="3"/>
     </row>
-    <row r="171" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:27" ht="15.75" thickBot="1">
       <c r="A171" s="6" t="s">
         <v>10</v>
       </c>
@@ -13060,7 +13050,7 @@
       <c r="Z171" s="3"/>
       <c r="AA171" s="3"/>
     </row>
-    <row r="172" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:27" ht="15.75" thickBot="1">
       <c r="A172" s="10" t="s">
         <v>10</v>
       </c>
@@ -13111,7 +13101,7 @@
       <c r="Z172" s="3"/>
       <c r="AA172" s="3"/>
     </row>
-    <row r="173" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:27" ht="15.75" thickBot="1">
       <c r="A173" s="15" t="s">
         <v>6</v>
       </c>
@@ -13153,7 +13143,7 @@
       <c r="Z173" s="3"/>
       <c r="AA173" s="3"/>
     </row>
-    <row r="174" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:27" ht="15.75" thickBot="1">
       <c r="A174" s="15" t="s">
         <v>8</v>
       </c>
@@ -13195,7 +13185,7 @@
       <c r="Z174" s="3"/>
       <c r="AA174" s="3"/>
     </row>
-    <row r="175" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:27" ht="15.75" thickBot="1">
       <c r="A175" s="15" t="s">
         <v>9</v>
       </c>
@@ -13237,7 +13227,7 @@
       <c r="Z175" s="3"/>
       <c r="AA175" s="3"/>
     </row>
-    <row r="176" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:27" ht="15.75" thickBot="1">
       <c r="A176" s="15" t="s">
         <v>10</v>
       </c>
@@ -13279,7 +13269,7 @@
       <c r="Z176" s="3"/>
       <c r="AA176" s="3"/>
     </row>
-    <row r="177" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:32">
       <c r="A177" s="3"/>
       <c r="B177" s="3"/>
       <c r="C177" s="3"/>
@@ -13308,7 +13298,7 @@
       <c r="Z177" s="3"/>
       <c r="AA177" s="3"/>
     </row>
-    <row r="178" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:32">
       <c r="A178" s="3"/>
       <c r="B178" s="3"/>
       <c r="C178" s="3"/>
@@ -13337,7 +13327,7 @@
       <c r="Z178" s="3"/>
       <c r="AA178" s="3"/>
     </row>
-    <row r="179" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:32">
       <c r="A179" s="49" t="s">
         <v>99</v>
       </c>
@@ -13368,7 +13358,7 @@
       <c r="Z179" s="3"/>
       <c r="AA179" s="3"/>
     </row>
-    <row r="180" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:32">
       <c r="A180" s="3" t="s">
         <v>85</v>
       </c>
@@ -13431,7 +13421,7 @@
       <c r="Z180" s="3"/>
       <c r="AA180" s="3"/>
     </row>
-    <row r="181" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:32">
       <c r="A181" s="3" t="s">
         <v>86</v>
       </c>
@@ -13510,7 +13500,7 @@
       <c r="Z181" s="3"/>
       <c r="AA181" s="3"/>
     </row>
-    <row r="182" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:32">
       <c r="A182" s="3" t="s">
         <v>23</v>
       </c>
@@ -13589,7 +13579,7 @@
       <c r="Z182" s="3"/>
       <c r="AA182" s="3"/>
     </row>
-    <row r="183" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:32">
       <c r="A183" s="3"/>
       <c r="B183" s="3"/>
       <c r="C183" s="53"/>
@@ -13618,7 +13608,7 @@
       <c r="Z183" s="3"/>
       <c r="AA183" s="3"/>
     </row>
-    <row r="184" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:32">
       <c r="A184" s="49" t="s">
         <v>100</v>
       </c>
@@ -13654,7 +13644,7 @@
       <c r="AE184" s="49"/>
       <c r="AF184" s="49"/>
     </row>
-    <row r="185" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:32">
       <c r="A185" s="3" t="s">
         <v>85</v>
       </c>
@@ -13752,7 +13742,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="186" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:32">
       <c r="A186" s="3" t="s">
         <v>86</v>
       </c>
@@ -13880,7 +13870,7 @@
         <v>5.5925664622652749E-3</v>
       </c>
     </row>
-    <row r="187" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:32">
       <c r="A187" s="3" t="s">
         <v>23</v>
       </c>
@@ -14038,7 +14028,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DB4BDA9-C258-4593-B06F-5EA0519CE561}">
   <dimension ref="A1:AE372"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.140625" customWidth="1"/>
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
@@ -14046,12 +14036,12 @@
     <col min="28" max="28" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31">
       <c r="A1" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31">
       <c r="B2">
         <v>2021</v>
       </c>
@@ -14143,7 +14133,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31">
       <c r="A3" s="64" t="s">
         <v>184</v>
       </c>
@@ -14268,7 +14258,7 @@
         <v>130641797616</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31">
       <c r="A4">
         <v>3</v>
       </c>
@@ -14393,7 +14383,7 @@
         <v>123324758518</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31">
       <c r="A5">
         <v>4</v>
       </c>
@@ -14518,7 +14508,7 @@
         <v>22481978241</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31">
       <c r="A6">
         <v>5</v>
       </c>
@@ -14643,7 +14633,7 @@
         <v>34590984593</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31">
       <c r="A7">
         <v>6</v>
       </c>
@@ -14768,7 +14758,7 @@
         <v>27570635908</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31">
       <c r="A8">
         <v>7</v>
       </c>
@@ -14893,7 +14883,7 @@
         <v>19474802616</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:31">
       <c r="A9">
         <v>8</v>
       </c>
@@ -15018,12 +15008,12 @@
         <v>185700776885</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:31">
       <c r="A11" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:31">
       <c r="B12">
         <v>2021</v>
       </c>
@@ -15115,7 +15105,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:31">
       <c r="A13" t="s">
         <v>185</v>
       </c>
@@ -15240,7 +15230,7 @@
         <v>0.58604270197066977</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:31">
       <c r="A14" s="64" t="s">
         <v>186</v>
       </c>
@@ -15365,7 +15355,7 @@
         <v>9.4917741494206828E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:31">
       <c r="A15" s="64" t="s">
         <v>187</v>
       </c>
@@ -15490,47 +15480,47 @@
         <v>0.90508225850579316</v>
       </c>
     </row>
-    <row r="17" spans="1:30" s="90" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="89" t="s">
+    <row r="17" spans="1:30" s="105" customFormat="1" ht="15.75">
+      <c r="A17" s="104" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="18" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:30">
       <c r="A18" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="19" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="H19" s="91"/>
-      <c r="M19" s="91"/>
-      <c r="P19" s="91"/>
-      <c r="W19" s="91"/>
-    </row>
-    <row r="20" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="H20" s="92" t="s">
+    <row r="19" spans="1:30">
+      <c r="H19" s="106"/>
+      <c r="M19" s="106"/>
+      <c r="P19" s="106"/>
+      <c r="W19" s="106"/>
+    </row>
+    <row r="20" spans="1:30">
+      <c r="H20" s="107" t="s">
         <v>190</v>
       </c>
-      <c r="I20" s="93"/>
-      <c r="J20" s="93"/>
-      <c r="K20" s="93"/>
-      <c r="L20" s="94"/>
-      <c r="M20" s="92" t="s">
+      <c r="I20" s="108"/>
+      <c r="J20" s="108"/>
+      <c r="K20" s="108"/>
+      <c r="L20" s="109"/>
+      <c r="M20" s="107" t="s">
         <v>191</v>
       </c>
-      <c r="N20" s="93"/>
-      <c r="O20" s="94"/>
-      <c r="P20" s="92" t="s">
+      <c r="N20" s="108"/>
+      <c r="O20" s="109"/>
+      <c r="P20" s="107" t="s">
         <v>192</v>
       </c>
-      <c r="Q20" s="93"/>
-      <c r="R20" s="93"/>
-      <c r="S20" s="93"/>
-      <c r="T20" s="93"/>
-      <c r="U20" s="93"/>
-      <c r="V20" s="94"/>
-      <c r="W20" s="91"/>
-    </row>
-    <row r="21" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="Q20" s="108"/>
+      <c r="R20" s="108"/>
+      <c r="S20" s="108"/>
+      <c r="T20" s="108"/>
+      <c r="U20" s="108"/>
+      <c r="V20" s="109"/>
+      <c r="W20" s="106"/>
+    </row>
+    <row r="21" spans="1:30">
       <c r="B21" t="s">
         <v>193</v>
       </c>
@@ -15546,7 +15536,7 @@
       <c r="G21" t="s">
         <v>197</v>
       </c>
-      <c r="H21" s="91">
+      <c r="H21" s="106">
         <v>3</v>
       </c>
       <c r="I21">
@@ -15558,19 +15548,19 @@
       <c r="K21">
         <v>6</v>
       </c>
-      <c r="L21" s="95">
+      <c r="L21" s="110">
         <v>7</v>
       </c>
-      <c r="M21" s="91" t="s">
+      <c r="M21" s="106" t="s">
         <v>198</v>
       </c>
       <c r="N21" t="s">
         <v>199</v>
       </c>
-      <c r="O21" s="95" t="s">
+      <c r="O21" s="110" t="s">
         <v>200</v>
       </c>
-      <c r="P21" s="91" t="s">
+      <c r="P21" s="106" t="s">
         <v>201</v>
       </c>
       <c r="Q21" t="s">
@@ -15588,10 +15578,10 @@
       <c r="U21" t="s">
         <v>204</v>
       </c>
-      <c r="V21" s="95" t="s">
+      <c r="V21" s="110" t="s">
         <v>205</v>
       </c>
-      <c r="W21" s="91" t="s">
+      <c r="W21" s="106" t="s">
         <v>206</v>
       </c>
       <c r="AA21" t="s">
@@ -15604,7 +15594,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="22" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:30">
       <c r="B22">
         <v>2012</v>
       </c>
@@ -15691,7 +15681,7 @@
         <v>269204.92893499997</v>
       </c>
     </row>
-    <row r="23" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:30">
       <c r="B23">
         <v>2012</v>
       </c>
@@ -15778,7 +15768,7 @@
         <v>275014.26959799998</v>
       </c>
     </row>
-    <row r="24" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:30">
       <c r="B24">
         <v>2012</v>
       </c>
@@ -15865,7 +15855,7 @@
         <v>279128.70267299999</v>
       </c>
     </row>
-    <row r="25" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:30">
       <c r="B25">
         <v>2012</v>
       </c>
@@ -15952,7 +15942,7 @@
         <v>279838.554198</v>
       </c>
     </row>
-    <row r="26" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:30">
       <c r="B26">
         <v>2012</v>
       </c>
@@ -16039,7 +16029,7 @@
         <v>287889.96027500002</v>
       </c>
     </row>
-    <row r="27" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:30">
       <c r="B27">
         <v>2012</v>
       </c>
@@ -16126,7 +16116,7 @@
         <v>297585.30382600002</v>
       </c>
     </row>
-    <row r="28" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:30">
       <c r="B28">
         <v>2012</v>
       </c>
@@ -16213,7 +16203,7 @@
         <v>304857.04434000002</v>
       </c>
     </row>
-    <row r="29" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:30">
       <c r="B29">
         <v>2012</v>
       </c>
@@ -16300,7 +16290,7 @@
         <v>300044.746866</v>
       </c>
     </row>
-    <row r="30" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:30">
       <c r="B30">
         <v>2012</v>
       </c>
@@ -16387,7 +16377,7 @@
         <v>302135.239413</v>
       </c>
     </row>
-    <row r="31" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:30">
       <c r="B31">
         <v>2013</v>
       </c>
@@ -16475,7 +16465,7 @@
         <v>315286.512973</v>
       </c>
     </row>
-    <row r="32" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:30">
       <c r="B32">
         <v>2013</v>
       </c>
@@ -16563,7 +16553,7 @@
         <v>321947.05459299998</v>
       </c>
     </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:30">
       <c r="B33">
         <v>2013</v>
       </c>
@@ -16651,7 +16641,7 @@
         <v>320699.79185600003</v>
       </c>
     </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:30">
       <c r="B34">
         <v>2013</v>
       </c>
@@ -16739,7 +16729,7 @@
         <v>321099.69637999998</v>
       </c>
     </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:30">
       <c r="B35">
         <v>2013</v>
       </c>
@@ -16827,7 +16817,7 @@
         <v>324016.78480200004</v>
       </c>
     </row>
-    <row r="36" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:30">
       <c r="B36">
         <v>2013</v>
       </c>
@@ -16915,7 +16905,7 @@
         <v>328476.361515</v>
       </c>
     </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:30">
       <c r="B37">
         <v>2013</v>
       </c>
@@ -17003,7 +16993,7 @@
         <v>332291.28607899998</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:30">
       <c r="B38">
         <v>2013</v>
       </c>
@@ -17091,7 +17081,7 @@
         <v>335752.19136</v>
       </c>
     </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:30">
       <c r="B39">
         <v>2013</v>
       </c>
@@ -17179,7 +17169,7 @@
         <v>338568.93268099998</v>
       </c>
     </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:30">
       <c r="B40">
         <v>2014</v>
       </c>
@@ -17267,7 +17257,7 @@
         <v>341094.03420599998</v>
       </c>
     </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:30">
       <c r="B41">
         <v>2014</v>
       </c>
@@ -17355,7 +17345,7 @@
         <v>344130.233381</v>
       </c>
     </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:30">
       <c r="B42">
         <v>2014</v>
       </c>
@@ -17443,7 +17433,7 @@
         <v>348243.08857100003</v>
       </c>
     </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:30">
       <c r="B43">
         <v>2014</v>
       </c>
@@ -17531,7 +17521,7 @@
         <v>351625.99503300001</v>
       </c>
     </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:30">
       <c r="B44">
         <v>2014</v>
       </c>
@@ -17619,7 +17609,7 @@
         <v>354872.73295999999</v>
       </c>
     </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:30">
       <c r="B45">
         <v>2014</v>
       </c>
@@ -17707,7 +17697,7 @@
         <v>358367.67353300005</v>
       </c>
     </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:30">
       <c r="B46">
         <v>2014</v>
       </c>
@@ -17795,7 +17785,7 @@
         <v>361320.58264000004</v>
       </c>
     </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:30">
       <c r="B47">
         <v>2014</v>
       </c>
@@ -17883,7 +17873,7 @@
         <v>364871.36687600001</v>
       </c>
     </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:30">
       <c r="B48">
         <v>2014</v>
       </c>
@@ -17971,7 +17961,7 @@
         <v>368410.84730599995</v>
       </c>
     </row>
-    <row r="49" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:30">
       <c r="B49">
         <v>2015</v>
       </c>
@@ -18059,7 +18049,7 @@
         <v>371886.64559299999</v>
       </c>
     </row>
-    <row r="50" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:30">
       <c r="B50">
         <v>2015</v>
       </c>
@@ -18147,7 +18137,7 @@
         <v>375662.94042900001</v>
       </c>
     </row>
-    <row r="51" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:30">
       <c r="B51">
         <v>2015</v>
       </c>
@@ -18235,7 +18225,7 @@
         <v>379485.037556</v>
       </c>
     </row>
-    <row r="52" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:30">
       <c r="B52">
         <v>2015</v>
       </c>
@@ -18323,7 +18313,7 @@
         <v>383492.49935100001</v>
       </c>
     </row>
-    <row r="53" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:30">
       <c r="B53">
         <v>2015</v>
       </c>
@@ -18411,7 +18401,7 @@
         <v>387363.04502800002</v>
       </c>
     </row>
-    <row r="54" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:30">
       <c r="B54">
         <v>2015</v>
       </c>
@@ -18499,7 +18489,7 @@
         <v>390923.53863600001</v>
       </c>
     </row>
-    <row r="55" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:30">
       <c r="B55">
         <v>2015</v>
       </c>
@@ -18587,7 +18577,7 @@
         <v>394061.25975500001</v>
       </c>
     </row>
-    <row r="56" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:30">
       <c r="B56">
         <v>2015</v>
       </c>
@@ -18675,7 +18665,7 @@
         <v>397535.01028799999</v>
       </c>
     </row>
-    <row r="57" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:30">
       <c r="B57">
         <v>2015</v>
       </c>
@@ -18763,7 +18753,7 @@
         <v>401206.37462900003</v>
       </c>
     </row>
-    <row r="58" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:30">
       <c r="B58">
         <v>2016</v>
       </c>
@@ -18851,7 +18841,7 @@
         <v>404637.34415300004</v>
       </c>
     </row>
-    <row r="59" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:30">
       <c r="B59">
         <v>2016</v>
       </c>
@@ -18939,7 +18929,7 @@
         <v>408336.174405</v>
       </c>
     </row>
-    <row r="60" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:30">
       <c r="B60">
         <v>2016</v>
       </c>
@@ -19027,7 +19017,7 @@
         <v>413143.93676100002</v>
       </c>
     </row>
-    <row r="61" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:30">
       <c r="B61">
         <v>2016</v>
       </c>
@@ -19096,7 +19086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:30">
       <c r="B62">
         <v>2016</v>
       </c>
@@ -19165,7 +19155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:30">
       <c r="B63">
         <v>2016</v>
       </c>
@@ -19234,7 +19224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:30">
       <c r="B64">
         <v>2016</v>
       </c>
@@ -19303,7 +19293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:23">
       <c r="B65">
         <v>2016</v>
       </c>
@@ -19372,7 +19362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:23">
       <c r="B66">
         <v>2016</v>
       </c>
@@ -19441,7 +19431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:23">
       <c r="B67">
         <v>2017</v>
       </c>
@@ -19510,7 +19500,7 @@
         <v>6775192</v>
       </c>
     </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:23">
       <c r="B68">
         <v>2017</v>
       </c>
@@ -19579,7 +19569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:23">
       <c r="B69">
         <v>2017</v>
       </c>
@@ -19648,7 +19638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:23">
       <c r="B70">
         <v>2017</v>
       </c>
@@ -19717,7 +19707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:23">
       <c r="B71">
         <v>2017</v>
       </c>
@@ -19786,7 +19776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:23">
       <c r="B72">
         <v>2017</v>
       </c>
@@ -19855,7 +19845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:23">
       <c r="B73">
         <v>2017</v>
       </c>
@@ -19924,7 +19914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:23">
       <c r="B74">
         <v>2017</v>
       </c>
@@ -19993,7 +19983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:23">
       <c r="B75">
         <v>2017</v>
       </c>
@@ -20062,7 +20052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:23">
       <c r="B76">
         <v>2018</v>
       </c>
@@ -20131,7 +20121,7 @@
         <v>6854305</v>
       </c>
     </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:23">
       <c r="B77">
         <v>2018</v>
       </c>
@@ -20200,7 +20190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:23">
       <c r="B78">
         <v>2018</v>
       </c>
@@ -20266,7 +20256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:23">
       <c r="B79">
         <v>2018</v>
       </c>
@@ -20335,7 +20325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:23">
       <c r="B80">
         <v>2018</v>
       </c>
@@ -20404,7 +20394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:23">
       <c r="B81">
         <v>2018</v>
       </c>
@@ -20473,7 +20463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:23">
       <c r="B82">
         <v>2018</v>
       </c>
@@ -20542,7 +20532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:23">
       <c r="B83">
         <v>2018</v>
       </c>
@@ -20611,7 +20601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:23">
       <c r="B84">
         <v>2018</v>
       </c>
@@ -20680,7 +20670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:23">
       <c r="B85">
         <v>2019</v>
       </c>
@@ -20749,7 +20739,7 @@
         <v>6500376</v>
       </c>
     </row>
-    <row r="86" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:23">
       <c r="B86">
         <v>2019</v>
       </c>
@@ -20818,7 +20808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:23">
       <c r="B87">
         <v>2019</v>
       </c>
@@ -20887,7 +20877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:23">
       <c r="B88">
         <v>2019</v>
       </c>
@@ -20956,7 +20946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:23">
       <c r="B89">
         <v>2019</v>
       </c>
@@ -21025,7 +21015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:23">
       <c r="B90">
         <v>2019</v>
       </c>
@@ -21094,7 +21084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:23">
       <c r="B91">
         <v>2019</v>
       </c>
@@ -21163,7 +21153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:23">
       <c r="B92">
         <v>2019</v>
       </c>
@@ -21232,7 +21222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:23">
       <c r="B93">
         <v>2019</v>
       </c>
@@ -21301,7 +21291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:23">
       <c r="B94">
         <v>2020</v>
       </c>
@@ -21370,7 +21360,7 @@
         <v>5911418</v>
       </c>
     </row>
-    <row r="95" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:23">
       <c r="B95">
         <v>2020</v>
       </c>
@@ -21439,7 +21429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:23">
       <c r="B96">
         <v>2020</v>
       </c>
@@ -21508,7 +21498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:23">
       <c r="B97">
         <v>2020</v>
       </c>
@@ -21577,7 +21567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:23">
       <c r="B98">
         <v>2020</v>
       </c>
@@ -21646,7 +21636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:23">
       <c r="B99">
         <v>2020</v>
       </c>
@@ -21715,7 +21705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:23">
       <c r="B100">
         <v>2020</v>
       </c>
@@ -21784,7 +21774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:23">
       <c r="B101">
         <v>2020</v>
       </c>
@@ -21853,7 +21843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:23">
       <c r="B102">
         <v>2020</v>
       </c>
@@ -21922,7 +21912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:23">
       <c r="B103">
         <v>2021</v>
       </c>
@@ -21991,7 +21981,7 @@
         <v>7145296</v>
       </c>
     </row>
-    <row r="104" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:23">
       <c r="B104">
         <v>2021</v>
       </c>
@@ -22060,7 +22050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:23">
       <c r="B105">
         <v>2021</v>
       </c>
@@ -22129,7 +22119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:23">
       <c r="B106">
         <v>2021</v>
       </c>
@@ -22198,7 +22188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:23">
       <c r="B107">
         <v>2021</v>
       </c>
@@ -22267,7 +22257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:23">
       <c r="B108">
         <v>2021</v>
       </c>
@@ -22336,7 +22326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:23">
       <c r="B109">
         <v>2021</v>
       </c>
@@ -22405,7 +22395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:23">
       <c r="B110">
         <v>2021</v>
       </c>
@@ -22474,7 +22464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:23">
       <c r="B111">
         <v>2021</v>
       </c>
@@ -22543,7 +22533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:23">
       <c r="B112">
         <v>2022</v>
       </c>
@@ -22612,7 +22602,7 @@
         <v>7899190</v>
       </c>
     </row>
-    <row r="113" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:23">
       <c r="B113">
         <v>2022</v>
       </c>
@@ -22681,7 +22671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:23">
       <c r="B114">
         <v>2022</v>
       </c>
@@ -22750,7 +22740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:23">
       <c r="B115">
         <v>2022</v>
       </c>
@@ -22819,7 +22809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="116" spans="2:23">
       <c r="B116">
         <v>2022</v>
       </c>
@@ -22888,7 +22878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:23">
       <c r="B117">
         <v>2022</v>
       </c>
@@ -22957,7 +22947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:23">
       <c r="B118">
         <v>2022</v>
       </c>
@@ -23026,7 +23016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:23">
       <c r="B119">
         <v>2022</v>
       </c>
@@ -23095,7 +23085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:23">
       <c r="B120">
         <v>2022</v>
       </c>
@@ -23164,7 +23154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:23">
       <c r="B121">
         <v>2023</v>
       </c>
@@ -23233,7 +23223,7 @@
         <v>8510344</v>
       </c>
     </row>
-    <row r="122" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="122" spans="2:23">
       <c r="B122">
         <v>2023</v>
       </c>
@@ -23302,7 +23292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="123" spans="2:23">
       <c r="B123">
         <v>2023</v>
       </c>
@@ -23371,7 +23361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="124" spans="2:23">
       <c r="B124">
         <v>2023</v>
       </c>
@@ -23440,7 +23430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="125" spans="2:23">
       <c r="B125">
         <v>2023</v>
       </c>
@@ -23509,7 +23499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="126" spans="2:23">
       <c r="B126">
         <v>2023</v>
       </c>
@@ -23578,7 +23568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:23">
       <c r="B127">
         <v>2023</v>
       </c>
@@ -23647,7 +23637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="128" spans="2:23">
       <c r="B128">
         <v>2023</v>
       </c>
@@ -23716,7 +23706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="129" spans="2:23">
       <c r="B129">
         <v>2023</v>
       </c>
@@ -23785,7 +23775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="130" spans="2:23">
       <c r="B130">
         <v>2024</v>
       </c>
@@ -23854,7 +23844,7 @@
         <v>9126118</v>
       </c>
     </row>
-    <row r="131" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="131" spans="2:23">
       <c r="B131">
         <v>2024</v>
       </c>
@@ -23923,7 +23913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="132" spans="2:23">
       <c r="B132">
         <v>2024</v>
       </c>
@@ -23992,7 +23982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="133" spans="2:23">
       <c r="B133">
         <v>2024</v>
       </c>
@@ -24061,7 +24051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="134" spans="2:23">
       <c r="B134">
         <v>2024</v>
       </c>
@@ -24130,7 +24120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="135" spans="2:23">
       <c r="B135">
         <v>2024</v>
       </c>
@@ -24199,7 +24189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="136" spans="2:23">
       <c r="B136">
         <v>2024</v>
       </c>
@@ -24268,7 +24258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="137" spans="2:23">
       <c r="B137">
         <v>2024</v>
       </c>
@@ -24337,7 +24327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="138" spans="2:23">
       <c r="B138">
         <v>2024</v>
       </c>
@@ -24406,7 +24396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="139" spans="2:23">
       <c r="B139">
         <v>2025</v>
       </c>
@@ -24475,7 +24465,7 @@
         <v>9739533</v>
       </c>
     </row>
-    <row r="140" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="140" spans="2:23">
       <c r="B140">
         <v>2025</v>
       </c>
@@ -24544,7 +24534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="141" spans="2:23">
       <c r="B141">
         <v>2025</v>
       </c>
@@ -24613,7 +24603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="142" spans="2:23">
       <c r="B142">
         <v>2025</v>
       </c>
@@ -24682,7 +24672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="143" spans="2:23">
       <c r="B143">
         <v>2025</v>
       </c>
@@ -24751,7 +24741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="144" spans="2:23">
       <c r="B144">
         <v>2025</v>
       </c>
@@ -24820,7 +24810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="145" spans="2:23">
       <c r="B145">
         <v>2025</v>
       </c>
@@ -24889,7 +24879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="146" spans="2:23">
       <c r="B146">
         <v>2025</v>
       </c>
@@ -24958,7 +24948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="147" spans="2:23">
       <c r="B147">
         <v>2025</v>
       </c>
@@ -25027,7 +25017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="148" spans="2:23">
       <c r="B148">
         <v>2026</v>
       </c>
@@ -25096,7 +25086,7 @@
         <v>10316053</v>
       </c>
     </row>
-    <row r="149" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="149" spans="2:23">
       <c r="B149">
         <v>2026</v>
       </c>
@@ -25165,7 +25155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="150" spans="2:23">
       <c r="B150">
         <v>2026</v>
       </c>
@@ -25234,7 +25224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="151" spans="2:23">
       <c r="B151">
         <v>2026</v>
       </c>
@@ -25303,7 +25293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="152" spans="2:23">
       <c r="B152">
         <v>2026</v>
       </c>
@@ -25372,7 +25362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="153" spans="2:23">
       <c r="B153">
         <v>2026</v>
       </c>
@@ -25441,7 +25431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="154" spans="2:23">
       <c r="B154">
         <v>2026</v>
       </c>
@@ -25510,7 +25500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="155" spans="2:23">
       <c r="B155">
         <v>2026</v>
       </c>
@@ -25579,7 +25569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="156" spans="2:23">
       <c r="B156">
         <v>2026</v>
       </c>
@@ -25648,7 +25638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="157" spans="2:23">
       <c r="B157">
         <v>2027</v>
       </c>
@@ -25717,7 +25707,7 @@
         <v>10792452</v>
       </c>
     </row>
-    <row r="158" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="158" spans="2:23">
       <c r="B158">
         <v>2027</v>
       </c>
@@ -25786,7 +25776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="159" spans="2:23">
       <c r="B159">
         <v>2027</v>
       </c>
@@ -25855,7 +25845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="160" spans="2:23">
       <c r="B160">
         <v>2027</v>
       </c>
@@ -25924,7 +25914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="161" spans="2:23">
       <c r="B161">
         <v>2027</v>
       </c>
@@ -25993,7 +25983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="162" spans="2:23">
       <c r="B162">
         <v>2027</v>
       </c>
@@ -26062,7 +26052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="163" spans="2:23">
       <c r="B163">
         <v>2027</v>
       </c>
@@ -26131,7 +26121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="164" spans="2:23">
       <c r="B164">
         <v>2027</v>
       </c>
@@ -26200,7 +26190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="165" spans="2:23">
       <c r="B165">
         <v>2027</v>
       </c>
@@ -26269,7 +26259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="166" spans="2:23">
       <c r="B166">
         <v>2028</v>
       </c>
@@ -26338,7 +26328,7 @@
         <v>11176272</v>
       </c>
     </row>
-    <row r="167" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="167" spans="2:23">
       <c r="B167">
         <v>2028</v>
       </c>
@@ -26407,7 +26397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="168" spans="2:23">
       <c r="B168">
         <v>2028</v>
       </c>
@@ -26476,7 +26466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="169" spans="2:23">
       <c r="B169">
         <v>2028</v>
       </c>
@@ -26545,7 +26535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="170" spans="2:23">
       <c r="B170">
         <v>2028</v>
       </c>
@@ -26614,7 +26604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="171" spans="2:23">
       <c r="B171">
         <v>2028</v>
       </c>
@@ -26683,7 +26673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="172" spans="2:23">
       <c r="B172">
         <v>2028</v>
       </c>
@@ -26752,7 +26742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="173" spans="2:23">
       <c r="B173">
         <v>2028</v>
       </c>
@@ -26821,7 +26811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="174" spans="2:23">
       <c r="B174">
         <v>2028</v>
       </c>
@@ -26890,7 +26880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="175" spans="2:23">
       <c r="B175">
         <v>2029</v>
       </c>
@@ -26959,7 +26949,7 @@
         <v>11474709</v>
       </c>
     </row>
-    <row r="176" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="176" spans="2:23">
       <c r="B176">
         <v>2029</v>
       </c>
@@ -27028,7 +27018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="177" spans="2:23">
       <c r="B177">
         <v>2029</v>
       </c>
@@ -27097,7 +27087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="178" spans="2:23">
       <c r="B178">
         <v>2029</v>
       </c>
@@ -27166,7 +27156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="179" spans="2:23">
       <c r="B179">
         <v>2029</v>
       </c>
@@ -27235,7 +27225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="180" spans="2:23">
       <c r="B180">
         <v>2029</v>
       </c>
@@ -27304,7 +27294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="181" spans="2:23">
       <c r="B181">
         <v>2029</v>
       </c>
@@ -27373,7 +27363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="182" spans="2:23">
       <c r="B182">
         <v>2029</v>
       </c>
@@ -27442,7 +27432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="183" spans="2:23">
       <c r="B183">
         <v>2029</v>
       </c>
@@ -27511,7 +27501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="184" spans="2:23">
       <c r="B184">
         <v>2030</v>
       </c>
@@ -27580,7 +27570,7 @@
         <v>11718101</v>
       </c>
     </row>
-    <row r="185" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="185" spans="2:23">
       <c r="B185">
         <v>2030</v>
       </c>
@@ -27649,7 +27639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="186" spans="2:23">
       <c r="B186">
         <v>2030</v>
       </c>
@@ -27718,7 +27708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="187" spans="2:23">
       <c r="B187">
         <v>2030</v>
       </c>
@@ -27787,7 +27777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="188" spans="2:23">
       <c r="B188">
         <v>2030</v>
       </c>
@@ -27856,7 +27846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="189" spans="2:23">
       <c r="B189">
         <v>2030</v>
       </c>
@@ -27925,7 +27915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="190" spans="2:23">
       <c r="B190">
         <v>2030</v>
       </c>
@@ -27994,7 +27984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="191" spans="2:23">
       <c r="B191">
         <v>2030</v>
       </c>
@@ -28063,7 +28053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="192" spans="2:23">
       <c r="B192">
         <v>2030</v>
       </c>
@@ -28132,7 +28122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="193" spans="2:23">
       <c r="B193">
         <v>2031</v>
       </c>
@@ -28201,7 +28191,7 @@
         <v>11950609</v>
       </c>
     </row>
-    <row r="194" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="194" spans="2:23">
       <c r="B194">
         <v>2031</v>
       </c>
@@ -28270,7 +28260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="195" spans="2:23">
       <c r="B195">
         <v>2031</v>
       </c>
@@ -28339,7 +28329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="196" spans="2:23">
       <c r="B196">
         <v>2031</v>
       </c>
@@ -28408,7 +28398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="197" spans="2:23">
       <c r="B197">
         <v>2031</v>
       </c>
@@ -28477,7 +28467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="198" spans="2:23">
       <c r="B198">
         <v>2031</v>
       </c>
@@ -28546,7 +28536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="199" spans="2:23">
       <c r="B199">
         <v>2031</v>
       </c>
@@ -28615,7 +28605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="200" spans="2:23">
       <c r="B200">
         <v>2031</v>
       </c>
@@ -28684,7 +28674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="201" spans="2:23">
       <c r="B201">
         <v>2031</v>
       </c>
@@ -28753,7 +28743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="202" spans="2:23">
       <c r="B202">
         <v>2032</v>
       </c>
@@ -28822,7 +28812,7 @@
         <v>12202189</v>
       </c>
     </row>
-    <row r="203" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="203" spans="2:23">
       <c r="B203">
         <v>2032</v>
       </c>
@@ -28891,7 +28881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="204" spans="2:23">
       <c r="B204">
         <v>2032</v>
       </c>
@@ -28960,7 +28950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="205" spans="2:23">
       <c r="B205">
         <v>2032</v>
       </c>
@@ -29029,7 +29019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="206" spans="2:23">
       <c r="B206">
         <v>2032</v>
       </c>
@@ -29098,7 +29088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="207" spans="2:23">
       <c r="B207">
         <v>2032</v>
       </c>
@@ -29167,7 +29157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="208" spans="2:23">
       <c r="B208">
         <v>2032</v>
       </c>
@@ -29236,7 +29226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="209" spans="2:23">
       <c r="B209">
         <v>2032</v>
       </c>
@@ -29305,7 +29295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="210" spans="2:23">
       <c r="B210">
         <v>2032</v>
       </c>
@@ -29374,7 +29364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="211" spans="2:23">
       <c r="B211">
         <v>2033</v>
       </c>
@@ -29443,7 +29433,7 @@
         <v>12426002</v>
       </c>
     </row>
-    <row r="212" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="212" spans="2:23">
       <c r="B212">
         <v>2033</v>
       </c>
@@ -29512,7 +29502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="213" spans="2:23">
       <c r="B213">
         <v>2033</v>
       </c>
@@ -29581,7 +29571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="214" spans="2:23">
       <c r="B214">
         <v>2033</v>
       </c>
@@ -29650,7 +29640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="215" spans="2:23">
       <c r="B215">
         <v>2033</v>
       </c>
@@ -29719,7 +29709,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="216" spans="2:23">
       <c r="B216">
         <v>2033</v>
       </c>
@@ -29788,7 +29778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="217" spans="2:23">
       <c r="B217">
         <v>2033</v>
       </c>
@@ -29857,7 +29847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="218" spans="2:23">
       <c r="B218">
         <v>2033</v>
       </c>
@@ -29926,7 +29916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="219" spans="2:23">
       <c r="B219">
         <v>2033</v>
       </c>
@@ -29995,7 +29985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="220" spans="2:23">
       <c r="B220">
         <v>2034</v>
       </c>
@@ -30064,7 +30054,7 @@
         <v>12642420</v>
       </c>
     </row>
-    <row r="221" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="221" spans="2:23">
       <c r="B221">
         <v>2034</v>
       </c>
@@ -30133,7 +30123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="222" spans="2:23">
       <c r="B222">
         <v>2034</v>
       </c>
@@ -30202,7 +30192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="223" spans="2:23">
       <c r="B223">
         <v>2034</v>
       </c>
@@ -30271,7 +30261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="224" spans="2:23">
       <c r="B224">
         <v>2034</v>
       </c>
@@ -30340,7 +30330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="225" spans="2:23">
       <c r="B225">
         <v>2034</v>
       </c>
@@ -30409,7 +30399,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="226" spans="2:23">
       <c r="B226">
         <v>2034</v>
       </c>
@@ -30478,7 +30468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="227" spans="2:23">
       <c r="B227">
         <v>2034</v>
       </c>
@@ -30547,7 +30537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="228" spans="2:23">
       <c r="B228">
         <v>2034</v>
       </c>
@@ -30616,7 +30606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="229" spans="2:23">
       <c r="B229">
         <v>2035</v>
       </c>
@@ -30685,7 +30675,7 @@
         <v>12841677</v>
       </c>
     </row>
-    <row r="230" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="230" spans="2:23">
       <c r="B230">
         <v>2035</v>
       </c>
@@ -30754,7 +30744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="231" spans="2:23">
       <c r="B231">
         <v>2035</v>
       </c>
@@ -30823,7 +30813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="232" spans="2:23">
       <c r="B232">
         <v>2035</v>
       </c>
@@ -30892,7 +30882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="233" spans="2:23">
       <c r="B233">
         <v>2035</v>
       </c>
@@ -30961,7 +30951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="234" spans="2:23">
       <c r="B234">
         <v>2035</v>
       </c>
@@ -31030,7 +31020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="235" spans="2:23">
       <c r="B235">
         <v>2035</v>
       </c>
@@ -31099,7 +31089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="236" spans="2:23">
       <c r="B236">
         <v>2035</v>
       </c>
@@ -31168,7 +31158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="237" spans="2:23">
       <c r="B237">
         <v>2035</v>
       </c>
@@ -31237,7 +31227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="238" spans="2:23">
       <c r="B238">
         <v>2036</v>
       </c>
@@ -31306,7 +31296,7 @@
         <v>12991660</v>
       </c>
     </row>
-    <row r="239" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="239" spans="2:23">
       <c r="B239">
         <v>2036</v>
       </c>
@@ -31375,7 +31365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="240" spans="2:23">
       <c r="B240">
         <v>2036</v>
       </c>
@@ -31444,7 +31434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="241" spans="2:23">
       <c r="B241">
         <v>2036</v>
       </c>
@@ -31513,7 +31503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="242" spans="2:23">
       <c r="B242">
         <v>2036</v>
       </c>
@@ -31582,7 +31572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="243" spans="2:23">
       <c r="B243">
         <v>2036</v>
       </c>
@@ -31651,7 +31641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="244" spans="2:23">
       <c r="B244">
         <v>2036</v>
       </c>
@@ -31720,7 +31710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="245" spans="2:23">
       <c r="B245">
         <v>2036</v>
       </c>
@@ -31789,7 +31779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="246" spans="2:23">
       <c r="B246">
         <v>2036</v>
       </c>
@@ -31858,7 +31848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="247" spans="2:23">
       <c r="B247">
         <v>2037</v>
       </c>
@@ -31927,7 +31917,7 @@
         <v>13129167</v>
       </c>
     </row>
-    <row r="248" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="248" spans="2:23">
       <c r="B248">
         <v>2037</v>
       </c>
@@ -31996,7 +31986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="249" spans="2:23">
       <c r="B249">
         <v>2037</v>
       </c>
@@ -32065,7 +32055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="250" spans="2:23">
       <c r="B250">
         <v>2037</v>
       </c>
@@ -32134,7 +32124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="251" spans="2:23">
       <c r="B251">
         <v>2037</v>
       </c>
@@ -32203,7 +32193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="252" spans="2:23">
       <c r="B252">
         <v>2037</v>
       </c>
@@ -32272,7 +32262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="253" spans="2:23">
       <c r="B253">
         <v>2037</v>
       </c>
@@ -32341,7 +32331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="254" spans="2:23">
       <c r="B254">
         <v>2037</v>
       </c>
@@ -32410,7 +32400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="255" spans="2:23">
       <c r="B255">
         <v>2037</v>
       </c>
@@ -32479,7 +32469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="256" spans="2:23">
       <c r="B256">
         <v>2038</v>
       </c>
@@ -32548,7 +32538,7 @@
         <v>13234496</v>
       </c>
     </row>
-    <row r="257" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="257" spans="2:23">
       <c r="B257">
         <v>2038</v>
       </c>
@@ -32617,7 +32607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="258" spans="2:23">
       <c r="B258">
         <v>2038</v>
       </c>
@@ -32686,7 +32676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="259" spans="2:23">
       <c r="B259">
         <v>2038</v>
       </c>
@@ -32755,7 +32745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="260" spans="2:23">
       <c r="B260">
         <v>2038</v>
       </c>
@@ -32824,7 +32814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="261" spans="2:23">
       <c r="B261">
         <v>2038</v>
       </c>
@@ -32893,7 +32883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="262" spans="2:23">
       <c r="B262">
         <v>2038</v>
       </c>
@@ -32962,7 +32952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="263" spans="2:23">
       <c r="B263">
         <v>2038</v>
       </c>
@@ -33031,7 +33021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="264" spans="2:23">
       <c r="B264">
         <v>2038</v>
       </c>
@@ -33100,7 +33090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="265" spans="2:23">
       <c r="B265">
         <v>2039</v>
       </c>
@@ -33169,7 +33159,7 @@
         <v>13310591</v>
       </c>
     </row>
-    <row r="266" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="266" spans="2:23">
       <c r="B266">
         <v>2039</v>
       </c>
@@ -33238,7 +33228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="267" spans="2:23">
       <c r="B267">
         <v>2039</v>
       </c>
@@ -33307,7 +33297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="268" spans="2:23">
       <c r="B268">
         <v>2039</v>
       </c>
@@ -33376,7 +33366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="269" spans="2:23">
       <c r="B269">
         <v>2039</v>
       </c>
@@ -33445,7 +33435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="270" spans="2:23">
       <c r="B270">
         <v>2039</v>
       </c>
@@ -33514,7 +33504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="271" spans="2:23">
       <c r="B271">
         <v>2039</v>
       </c>
@@ -33583,7 +33573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="272" spans="2:23">
       <c r="B272">
         <v>2039</v>
       </c>
@@ -33652,7 +33642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="273" spans="2:23">
       <c r="B273">
         <v>2039</v>
       </c>
@@ -33721,7 +33711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="274" spans="2:23">
       <c r="B274">
         <v>2040</v>
       </c>
@@ -33790,7 +33780,7 @@
         <v>13386520</v>
       </c>
     </row>
-    <row r="275" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="275" spans="2:23">
       <c r="B275">
         <v>2040</v>
       </c>
@@ -33859,7 +33849,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="276" spans="2:23">
       <c r="B276">
         <v>2040</v>
       </c>
@@ -33928,7 +33918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="277" spans="2:23">
       <c r="B277">
         <v>2040</v>
       </c>
@@ -33997,7 +33987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="278" spans="2:23">
       <c r="B278">
         <v>2040</v>
       </c>
@@ -34066,7 +34056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="279" spans="2:23">
       <c r="B279">
         <v>2040</v>
       </c>
@@ -34135,7 +34125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="280" spans="2:23">
       <c r="B280">
         <v>2040</v>
       </c>
@@ -34204,7 +34194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="281" spans="2:23">
       <c r="B281">
         <v>2040</v>
       </c>
@@ -34273,7 +34263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="282" spans="2:23">
       <c r="B282">
         <v>2040</v>
       </c>
@@ -34342,7 +34332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="283" spans="2:23">
       <c r="B283">
         <v>2041</v>
       </c>
@@ -34411,7 +34401,7 @@
         <v>13460125</v>
       </c>
     </row>
-    <row r="284" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="284" spans="2:23">
       <c r="B284">
         <v>2041</v>
       </c>
@@ -34480,7 +34470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="285" spans="2:23">
       <c r="B285">
         <v>2041</v>
       </c>
@@ -34549,7 +34539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="286" spans="2:23">
       <c r="B286">
         <v>2041</v>
       </c>
@@ -34618,7 +34608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="287" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="287" spans="2:23">
       <c r="B287">
         <v>2041</v>
       </c>
@@ -34687,7 +34677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="288" spans="2:23">
       <c r="B288">
         <v>2041</v>
       </c>
@@ -34756,7 +34746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="289" spans="2:23">
       <c r="B289">
         <v>2041</v>
       </c>
@@ -34825,7 +34815,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="290" spans="2:23">
       <c r="B290">
         <v>2041</v>
       </c>
@@ -34894,7 +34884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="291" spans="2:23">
       <c r="B291">
         <v>2041</v>
       </c>
@@ -34963,7 +34953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="292" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="292" spans="2:23">
       <c r="B292">
         <v>2042</v>
       </c>
@@ -35032,7 +35022,7 @@
         <v>13537213</v>
       </c>
     </row>
-    <row r="293" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="293" spans="2:23">
       <c r="B293">
         <v>2042</v>
       </c>
@@ -35101,7 +35091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="294" spans="2:23">
       <c r="B294">
         <v>2042</v>
       </c>
@@ -35170,7 +35160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="295" spans="2:23">
       <c r="B295">
         <v>2042</v>
       </c>
@@ -35239,7 +35229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="296" spans="2:23">
       <c r="B296">
         <v>2042</v>
       </c>
@@ -35308,7 +35298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="297" spans="2:23">
       <c r="B297">
         <v>2042</v>
       </c>
@@ -35377,7 +35367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="298" spans="2:23">
       <c r="B298">
         <v>2042</v>
       </c>
@@ -35446,7 +35436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="299" spans="2:23">
       <c r="B299">
         <v>2042</v>
       </c>
@@ -35515,7 +35505,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="300" spans="2:23">
       <c r="B300">
         <v>2042</v>
       </c>
@@ -35584,7 +35574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="301" spans="2:23">
       <c r="B301">
         <v>2043</v>
       </c>
@@ -35653,7 +35643,7 @@
         <v>13610875</v>
       </c>
     </row>
-    <row r="302" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="302" spans="2:23">
       <c r="B302">
         <v>2043</v>
       </c>
@@ -35722,7 +35712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="303" spans="2:23">
       <c r="B303">
         <v>2043</v>
       </c>
@@ -35791,7 +35781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="304" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="304" spans="2:23">
       <c r="B304">
         <v>2043</v>
       </c>
@@ -35860,7 +35850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="305" spans="2:23">
       <c r="B305">
         <v>2043</v>
       </c>
@@ -35929,7 +35919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="306" spans="2:23">
       <c r="B306">
         <v>2043</v>
       </c>
@@ -35998,7 +35988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="307" spans="2:23">
       <c r="B307">
         <v>2043</v>
       </c>
@@ -36067,7 +36057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="308" spans="2:23">
       <c r="B308">
         <v>2043</v>
       </c>
@@ -36136,7 +36126,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="309" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="309" spans="2:23">
       <c r="B309">
         <v>2043</v>
       </c>
@@ -36205,7 +36195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="310" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="310" spans="2:23">
       <c r="B310">
         <v>2044</v>
       </c>
@@ -36274,7 +36264,7 @@
         <v>13671004</v>
       </c>
     </row>
-    <row r="311" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="311" spans="2:23">
       <c r="B311">
         <v>2044</v>
       </c>
@@ -36343,7 +36333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="312" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="312" spans="2:23">
       <c r="B312">
         <v>2044</v>
       </c>
@@ -36412,7 +36402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="313" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="313" spans="2:23">
       <c r="B313">
         <v>2044</v>
       </c>
@@ -36481,7 +36471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="314" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="314" spans="2:23">
       <c r="B314">
         <v>2044</v>
       </c>
@@ -36550,7 +36540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="315" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="315" spans="2:23">
       <c r="B315">
         <v>2044</v>
       </c>
@@ -36619,7 +36609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="316" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="316" spans="2:23">
       <c r="B316">
         <v>2044</v>
       </c>
@@ -36688,7 +36678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="317" spans="2:23">
       <c r="B317">
         <v>2044</v>
       </c>
@@ -36757,7 +36747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="318" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="318" spans="2:23">
       <c r="B318">
         <v>2044</v>
       </c>
@@ -36826,7 +36816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="319" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="319" spans="2:23">
       <c r="B319">
         <v>2045</v>
       </c>
@@ -36895,7 +36885,7 @@
         <v>13698105</v>
       </c>
     </row>
-    <row r="320" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="320" spans="2:23">
       <c r="B320">
         <v>2045</v>
       </c>
@@ -36964,7 +36954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="321" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="321" spans="2:23">
       <c r="B321">
         <v>2045</v>
       </c>
@@ -37033,7 +37023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="322" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="322" spans="2:23">
       <c r="B322">
         <v>2045</v>
       </c>
@@ -37102,7 +37092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="323" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="323" spans="2:23">
       <c r="B323">
         <v>2045</v>
       </c>
@@ -37171,7 +37161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="324" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="324" spans="2:23">
       <c r="B324">
         <v>2045</v>
       </c>
@@ -37240,7 +37230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="325" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="325" spans="2:23">
       <c r="B325">
         <v>2045</v>
       </c>
@@ -37309,7 +37299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="326" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="326" spans="2:23">
       <c r="B326">
         <v>2045</v>
       </c>
@@ -37378,7 +37368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="327" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="327" spans="2:23">
       <c r="B327">
         <v>2045</v>
       </c>
@@ -37447,7 +37437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="328" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="328" spans="2:23">
       <c r="B328">
         <v>2046</v>
       </c>
@@ -37516,7 +37506,7 @@
         <v>13712468</v>
       </c>
     </row>
-    <row r="329" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="329" spans="2:23">
       <c r="B329">
         <v>2046</v>
       </c>
@@ -37585,7 +37575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="330" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="330" spans="2:23">
       <c r="B330">
         <v>2046</v>
       </c>
@@ -37654,7 +37644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="331" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="331" spans="2:23">
       <c r="B331">
         <v>2046</v>
       </c>
@@ -37723,7 +37713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="332" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="332" spans="2:23">
       <c r="B332">
         <v>2046</v>
       </c>
@@ -37792,7 +37782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="333" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="333" spans="2:23">
       <c r="B333">
         <v>2046</v>
       </c>
@@ -37861,7 +37851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="334" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="334" spans="2:23">
       <c r="B334">
         <v>2046</v>
       </c>
@@ -37930,7 +37920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="335" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="335" spans="2:23">
       <c r="B335">
         <v>2046</v>
       </c>
@@ -37999,7 +37989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="336" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="336" spans="2:23">
       <c r="B336">
         <v>2046</v>
       </c>
@@ -38068,7 +38058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="337" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="337" spans="2:23">
       <c r="B337">
         <v>2047</v>
       </c>
@@ -38137,7 +38127,7 @@
         <v>13729347</v>
       </c>
     </row>
-    <row r="338" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="338" spans="2:23">
       <c r="B338">
         <v>2047</v>
       </c>
@@ -38206,7 +38196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="339" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="339" spans="2:23">
       <c r="B339">
         <v>2047</v>
       </c>
@@ -38275,7 +38265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="340" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="340" spans="2:23">
       <c r="B340">
         <v>2047</v>
       </c>
@@ -38344,7 +38334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="341" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="341" spans="2:23">
       <c r="B341">
         <v>2047</v>
       </c>
@@ -38413,7 +38403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="342" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="342" spans="2:23">
       <c r="B342">
         <v>2047</v>
       </c>
@@ -38482,7 +38472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="343" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="343" spans="2:23">
       <c r="B343">
         <v>2047</v>
       </c>
@@ -38551,7 +38541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="344" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="344" spans="2:23">
       <c r="B344">
         <v>2047</v>
       </c>
@@ -38620,7 +38610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="345" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="345" spans="2:23">
       <c r="B345">
         <v>2047</v>
       </c>
@@ -38689,7 +38679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="346" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="346" spans="2:23">
       <c r="B346">
         <v>2048</v>
       </c>
@@ -38758,7 +38748,7 @@
         <v>13744756</v>
       </c>
     </row>
-    <row r="347" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="347" spans="2:23">
       <c r="B347">
         <v>2048</v>
       </c>
@@ -38827,7 +38817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="348" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="348" spans="2:23">
       <c r="B348">
         <v>2048</v>
       </c>
@@ -38896,7 +38886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="349" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="349" spans="2:23">
       <c r="B349">
         <v>2048</v>
       </c>
@@ -38965,7 +38955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="350" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="350" spans="2:23">
       <c r="B350">
         <v>2048</v>
       </c>
@@ -39034,7 +39024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="351" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="351" spans="2:23">
       <c r="B351">
         <v>2048</v>
       </c>
@@ -39103,7 +39093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="352" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="352" spans="2:23">
       <c r="B352">
         <v>2048</v>
       </c>
@@ -39172,7 +39162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="353" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="353" spans="2:23">
       <c r="B353">
         <v>2048</v>
       </c>
@@ -39241,7 +39231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="354" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="354" spans="2:23">
       <c r="B354">
         <v>2048</v>
       </c>
@@ -39310,7 +39300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="355" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="355" spans="2:23">
       <c r="B355">
         <v>2049</v>
       </c>
@@ -39379,7 +39369,7 @@
         <v>13758281</v>
       </c>
     </row>
-    <row r="356" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="356" spans="2:23">
       <c r="B356">
         <v>2049</v>
       </c>
@@ -39448,7 +39438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="357" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="357" spans="2:23">
       <c r="B357">
         <v>2049</v>
       </c>
@@ -39517,7 +39507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="358" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="358" spans="2:23">
       <c r="B358">
         <v>2049</v>
       </c>
@@ -39586,7 +39576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="359" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="359" spans="2:23">
       <c r="B359">
         <v>2049</v>
       </c>
@@ -39655,7 +39645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="360" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="360" spans="2:23">
       <c r="B360">
         <v>2049</v>
       </c>
@@ -39724,7 +39714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="361" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="361" spans="2:23">
       <c r="B361">
         <v>2049</v>
       </c>
@@ -39793,7 +39783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="362" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="362" spans="2:23">
       <c r="B362">
         <v>2049</v>
       </c>
@@ -39862,7 +39852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="363" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="363" spans="2:23">
       <c r="B363">
         <v>2049</v>
       </c>
@@ -39931,7 +39921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="364" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="364" spans="2:23">
       <c r="B364">
         <v>2050</v>
       </c>
@@ -40000,7 +39990,7 @@
         <v>13817684</v>
       </c>
     </row>
-    <row r="365" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="365" spans="2:23">
       <c r="B365">
         <v>2050</v>
       </c>
@@ -40069,7 +40059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="366" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="366" spans="2:23">
       <c r="B366">
         <v>2050</v>
       </c>
@@ -40138,7 +40128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="367" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="367" spans="2:23">
       <c r="B367">
         <v>2050</v>
       </c>
@@ -40207,7 +40197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="368" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="368" spans="2:23">
       <c r="B368">
         <v>2050</v>
       </c>
@@ -40276,7 +40266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="369" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="369" spans="2:23">
       <c r="B369">
         <v>2050</v>
       </c>
@@ -40345,7 +40335,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="370" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="370" spans="2:23">
       <c r="B370">
         <v>2050</v>
       </c>
@@ -40414,7 +40404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="371" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="371" spans="2:23">
       <c r="B371">
         <v>2050</v>
       </c>
@@ -40483,7 +40473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="372" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="372" spans="2:23">
       <c r="B372">
         <v>2050</v>
       </c>
@@ -40560,14 +40550,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A245027-04A3-4219-9613-1C42FD0D1DCE}">
   <dimension ref="A1:BC137"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="33" width="10.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:36">
       <c r="A1" s="2" t="s">
         <v>101</v>
       </c>
@@ -40665,7 +40655,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:36">
       <c r="A2" s="63" t="s">
         <v>102</v>
       </c>
@@ -40765,7 +40755,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:36">
       <c r="A3" s="63" t="s">
         <v>103</v>
       </c>
@@ -40865,7 +40855,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:36">
       <c r="A4" s="63" t="s">
         <v>104</v>
       </c>
@@ -40965,7 +40955,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:36">
       <c r="A5" s="63" t="s">
         <v>105</v>
       </c>
@@ -41065,7 +41055,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:36">
       <c r="A6" s="63" t="s">
         <v>106</v>
       </c>
@@ -41165,7 +41155,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:36">
       <c r="A7" s="63" t="s">
         <v>107</v>
       </c>
@@ -41265,7 +41255,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:36">
       <c r="A8" s="63" t="s">
         <v>108</v>
       </c>
@@ -41365,7 +41355,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:36">
       <c r="A9" s="63" t="s">
         <v>109</v>
       </c>
@@ -41465,7 +41455,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:36">
       <c r="A10" s="63" t="s">
         <v>110</v>
       </c>
@@ -41565,7 +41555,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:36">
       <c r="A11" s="63" t="s">
         <v>111</v>
       </c>
@@ -41665,12 +41655,12 @@
         <v>646</v>
       </c>
     </row>
-    <row r="14" spans="1:36" s="66" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" s="66" customFormat="1" ht="12.75">
       <c r="A14" s="65" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="15" spans="1:36" s="65" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" s="65" customFormat="1" ht="12.75">
       <c r="A15" s="67"/>
       <c r="B15" s="65">
         <v>2020</v>
@@ -41778,7 +41768,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="16" spans="1:36" s="67" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" s="67" customFormat="1" ht="12.75">
       <c r="A16" s="68" t="s">
         <v>113</v>
       </c>
@@ -41804,7 +41794,7 @@
       <c r="U16" s="69"/>
       <c r="V16" s="69"/>
     </row>
-    <row r="17" spans="1:36" s="66" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:36" s="66" customFormat="1" ht="12.75">
       <c r="A17" s="66" t="s">
         <v>102</v>
       </c>
@@ -41943,7 +41933,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="18" spans="1:36" s="66" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:36" s="66" customFormat="1" ht="12.75">
       <c r="A18" s="66" t="s">
         <v>103</v>
       </c>
@@ -42082,7 +42072,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="19" spans="1:36" s="66" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:36" s="66" customFormat="1" ht="12.75">
       <c r="A19" s="66" t="s">
         <v>104</v>
       </c>
@@ -42221,7 +42211,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="20" spans="1:36" s="66" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:36" s="66" customFormat="1" ht="12.75">
       <c r="A20" s="66" t="s">
         <v>105</v>
       </c>
@@ -42360,7 +42350,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="21" spans="1:36" s="66" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:36" s="66" customFormat="1" ht="12.75">
       <c r="A21" s="66" t="s">
         <v>106</v>
       </c>
@@ -42499,7 +42489,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="22" spans="1:36" s="66" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:36" s="66" customFormat="1" ht="12.75">
       <c r="A22" s="66" t="s">
         <v>107</v>
       </c>
@@ -42638,7 +42628,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="23" spans="1:36" s="73" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:36" s="73" customFormat="1" ht="12.75">
       <c r="A23" s="71" t="s">
         <v>114</v>
       </c>
@@ -42692,7 +42682,7 @@
       <c r="AH23" s="79"/>
       <c r="AI23" s="79"/>
     </row>
-    <row r="24" spans="1:36" s="66" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:36" s="66" customFormat="1" ht="12.75">
       <c r="A24" s="66" t="s">
         <v>108</v>
       </c>
@@ -42831,7 +42821,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="25" spans="1:36" s="66" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:36" s="66" customFormat="1" ht="12.75">
       <c r="A25" s="66" t="s">
         <v>109</v>
       </c>
@@ -42970,7 +42960,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="26" spans="1:36" s="66" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:36" s="66" customFormat="1" ht="12.75">
       <c r="A26" s="66" t="s">
         <v>110</v>
       </c>
@@ -43109,7 +43099,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="27" spans="1:36" s="66" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:36" s="66" customFormat="1" ht="12.75">
       <c r="A27" s="66" t="s">
         <v>111</v>
       </c>
@@ -43248,7 +43238,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="28" spans="1:36" s="73" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:36" s="73" customFormat="1" ht="12.75">
       <c r="A28" s="71" t="s">
         <v>115</v>
       </c>
@@ -43302,17 +43292,17 @@
       <c r="AH28" s="70"/>
       <c r="AI28" s="70"/>
     </row>
-    <row r="31" spans="1:36" s="74" customFormat="1" ht="33.75" x14ac:dyDescent="0.5">
+    <row r="31" spans="1:36" s="74" customFormat="1" ht="33.75">
       <c r="B31" s="75" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="32" spans="1:36" s="74" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:36" s="74" customFormat="1" ht="17.25" customHeight="1">
       <c r="B32" s="74" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="33" spans="1:55" s="74" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:55" s="74" customFormat="1" ht="15.75">
       <c r="B33" s="74" t="s">
         <v>122</v>
       </c>
@@ -43476,7 +43466,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="34" spans="1:55" s="74" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:55" s="74" customFormat="1" ht="15.75">
       <c r="A34" s="74" t="s">
         <v>125</v>
       </c>
@@ -43640,7 +43630,7 @@
         <v>8941.1253098647539</v>
       </c>
     </row>
-    <row r="35" spans="1:55" s="74" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:55" s="74" customFormat="1" ht="15.75">
       <c r="A35" s="74" t="s">
         <v>125</v>
       </c>
@@ -43804,7 +43794,7 @@
         <v>9335.2229055276457</v>
       </c>
     </row>
-    <row r="36" spans="1:55" s="74" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:55" s="74" customFormat="1" ht="15.75">
       <c r="A36" s="74" t="s">
         <v>125</v>
       </c>
@@ -43968,7 +43958,7 @@
         <v>9449.9949414654075</v>
       </c>
     </row>
-    <row r="37" spans="1:55" s="74" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:55" s="74" customFormat="1" ht="15.75">
       <c r="A37" s="74" t="s">
         <v>125</v>
       </c>
@@ -44132,7 +44122,7 @@
         <v>49876.035846764251</v>
       </c>
     </row>
-    <row r="38" spans="1:55" s="74" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:55" s="74" customFormat="1" ht="15.75">
       <c r="A38" s="3" t="s">
         <v>111</v>
       </c>
@@ -44296,7 +44286,7 @@
         <v>48998.777404870685</v>
       </c>
     </row>
-    <row r="39" spans="1:55" s="74" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:55" s="74" customFormat="1" ht="15.75">
       <c r="A39" s="3" t="s">
         <v>111</v>
       </c>
@@ -44460,7 +44450,7 @@
         <v>48193.856381193618</v>
       </c>
     </row>
-    <row r="40" spans="1:55" s="74" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:55" s="74" customFormat="1" ht="15.75">
       <c r="A40" s="3" t="s">
         <v>108</v>
       </c>
@@ -44624,7 +44614,7 @@
         <v>16842.299684166632</v>
       </c>
     </row>
-    <row r="41" spans="1:55" s="74" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:55" s="74" customFormat="1" ht="15.75">
       <c r="A41" s="3" t="s">
         <v>110</v>
       </c>
@@ -44788,7 +44778,7 @@
         <v>16665.30579126858</v>
       </c>
     </row>
-    <row r="42" spans="1:55" s="74" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:55" s="74" customFormat="1" ht="15.75">
       <c r="A42" s="3" t="s">
         <v>110</v>
       </c>
@@ -44952,7 +44942,7 @@
         <v>16757.077087471102</v>
       </c>
     </row>
-    <row r="43" spans="1:55" s="74" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:55" s="74" customFormat="1" ht="15.75">
       <c r="A43" s="3" t="s">
         <v>108</v>
       </c>
@@ -45116,7 +45106,7 @@
         <v>49997.893522427854</v>
       </c>
     </row>
-    <row r="44" spans="1:55" s="74" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:55" s="74" customFormat="1" ht="15.75">
       <c r="A44" s="3" t="s">
         <v>109</v>
       </c>
@@ -45280,7 +45270,7 @@
         <v>49806.329843386644</v>
       </c>
     </row>
-    <row r="45" spans="1:55" s="74" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:55" s="74" customFormat="1" ht="15.75">
       <c r="A45" s="3" t="s">
         <v>109</v>
       </c>
@@ -45444,7 +45434,7 @@
         <v>32848.683068259023</v>
       </c>
     </row>
-    <row r="46" spans="1:55" s="74" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:55" s="74" customFormat="1" ht="15.75">
       <c r="A46" s="74" t="s">
         <v>125</v>
       </c>
@@ -45608,7 +45598,7 @@
         <v>49918.549378741227</v>
       </c>
     </row>
-    <row r="47" spans="1:55" s="74" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:55" s="74" customFormat="1" ht="15.75">
       <c r="A47" s="74" t="s">
         <v>139</v>
       </c>
@@ -45772,7 +45762,7 @@
         <v>19869.544927123421</v>
       </c>
     </row>
-    <row r="48" spans="1:55" s="74" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:55" s="74" customFormat="1" ht="15.75">
       <c r="A48" s="74" t="s">
         <v>139</v>
       </c>
@@ -45936,7 +45926,7 @@
         <v>20407.15243008138</v>
       </c>
     </row>
-    <row r="49" spans="1:55" s="74" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:55" s="74" customFormat="1" ht="15.75">
       <c r="A49" s="74" t="s">
         <v>139</v>
       </c>
@@ -46100,7 +46090,7 @@
         <v>20211.770846553783</v>
       </c>
     </row>
-    <row r="50" spans="1:55" s="74" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:55" s="74" customFormat="1" ht="15.75">
       <c r="A50" s="74" t="s">
         <v>139</v>
       </c>
@@ -46264,7 +46254,7 @@
         <v>3807.8853271450416</v>
       </c>
     </row>
-    <row r="51" spans="1:55" s="74" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:55" s="74" customFormat="1" ht="15.75">
       <c r="A51" s="74" t="s">
         <v>139</v>
       </c>
@@ -46428,7 +46418,7 @@
         <v>18552.652863838659</v>
       </c>
     </row>
-    <row r="52" spans="1:55" s="74" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:55" s="74" customFormat="1" ht="15.75">
       <c r="A52" s="74" t="s">
         <v>139</v>
       </c>
@@ -46592,7 +46582,7 @@
         <v>19882.163050778829</v>
       </c>
     </row>
-    <row r="53" spans="1:55" s="74" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:55" s="74" customFormat="1" ht="15.75">
       <c r="A53" s="74" t="s">
         <v>139</v>
       </c>
@@ -46756,7 +46746,7 @@
         <v>7249.3066990766138</v>
       </c>
     </row>
-    <row r="54" spans="1:55" s="74" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:55" s="74" customFormat="1" ht="15.75">
       <c r="A54" s="74" t="s">
         <v>139</v>
       </c>
@@ -46920,7 +46910,7 @@
         <v>9896.7090327829428</v>
       </c>
     </row>
-    <row r="55" spans="1:55" s="74" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:55" s="74" customFormat="1" ht="15.75">
       <c r="A55" s="74" t="s">
         <v>139</v>
       </c>
@@ -47084,7 +47074,7 @@
         <v>35740.823754379227</v>
       </c>
     </row>
-    <row r="56" spans="1:55" s="74" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:55" s="74" customFormat="1" ht="15.75">
       <c r="A56" s="74" t="s">
         <v>139</v>
       </c>
@@ -47248,7 +47238,7 @@
         <v>23790.748009964722</v>
       </c>
     </row>
-    <row r="57" spans="1:55" s="74" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:55" s="74" customFormat="1" ht="15.75">
       <c r="A57" s="3" t="s">
         <v>106</v>
       </c>
@@ -47412,7 +47402,7 @@
         <v>166426.06571909611</v>
       </c>
     </row>
-    <row r="58" spans="1:55" s="74" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:55" s="74" customFormat="1" ht="15.75">
       <c r="A58" s="3" t="s">
         <v>106</v>
       </c>
@@ -47576,7 +47566,7 @@
         <v>38356.83368908472</v>
       </c>
     </row>
-    <row r="59" spans="1:55" s="74" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:55" s="74" customFormat="1" ht="15.75">
       <c r="A59" s="3" t="s">
         <v>106</v>
       </c>
@@ -47740,7 +47730,7 @@
         <v>155258.70386157703</v>
       </c>
     </row>
-    <row r="60" spans="1:55" s="74" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:55" s="74" customFormat="1" ht="15.75">
       <c r="A60" s="3" t="s">
         <v>105</v>
       </c>
@@ -47904,7 +47894,7 @@
         <v>78994.790843715484</v>
       </c>
     </row>
-    <row r="61" spans="1:55" s="74" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:55" s="74" customFormat="1" ht="15.75">
       <c r="A61" s="3" t="s">
         <v>105</v>
       </c>
@@ -48068,7 +48058,7 @@
         <v>68790.444903315016</v>
       </c>
     </row>
-    <row r="62" spans="1:55" s="74" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:55" s="74" customFormat="1" ht="15.75">
       <c r="A62" s="3" t="s">
         <v>105</v>
       </c>
@@ -48232,7 +48222,7 @@
         <v>68126.066685689249</v>
       </c>
     </row>
-    <row r="63" spans="1:55" s="74" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:55" s="74" customFormat="1" ht="15.75">
       <c r="A63" s="3" t="s">
         <v>107</v>
       </c>
@@ -48396,7 +48386,7 @@
         <v>11871.71555095992</v>
       </c>
     </row>
-    <row r="64" spans="1:55" s="74" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:55" s="74" customFormat="1" ht="15.75">
       <c r="A64" s="3" t="s">
         <v>107</v>
       </c>
@@ -48560,7 +48550,7 @@
         <v>34354.151463321126</v>
       </c>
     </row>
-    <row r="65" spans="1:55" s="74" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:55" s="74" customFormat="1" ht="15.75">
       <c r="A65" s="3" t="s">
         <v>107</v>
       </c>
@@ -48724,7 +48714,7 @@
         <v>34961.745255937552</v>
       </c>
     </row>
-    <row r="66" spans="1:55" s="74" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:55" s="74" customFormat="1" ht="15.75">
       <c r="A66" s="3" t="s">
         <v>102</v>
       </c>
@@ -48888,7 +48878,7 @@
         <v>38399.901376300746</v>
       </c>
     </row>
-    <row r="67" spans="1:55" s="74" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:55" s="74" customFormat="1" ht="15.75">
       <c r="A67" s="3" t="s">
         <v>103</v>
       </c>
@@ -49052,7 +49042,7 @@
         <v>33700.276020704143</v>
       </c>
     </row>
-    <row r="68" spans="1:55" s="74" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:55" s="74" customFormat="1" ht="15.75">
       <c r="A68" s="3" t="s">
         <v>104</v>
       </c>
@@ -49216,7 +49206,7 @@
         <v>35644.527293675485</v>
       </c>
     </row>
-    <row r="69" spans="1:55" s="74" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:55" s="74" customFormat="1" ht="15.75">
       <c r="A69" s="3" t="s">
         <v>102</v>
       </c>
@@ -49380,7 +49370,7 @@
         <v>24778.887723792297</v>
       </c>
     </row>
-    <row r="70" spans="1:55" s="74" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:55" s="74" customFormat="1" ht="15.75">
       <c r="A70" s="3" t="s">
         <v>103</v>
       </c>
@@ -49544,7 +49534,7 @@
         <v>22251.772967826735</v>
       </c>
     </row>
-    <row r="71" spans="1:55" s="74" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:55" s="74" customFormat="1" ht="15.75">
       <c r="A71" s="3" t="s">
         <v>104</v>
       </c>
@@ -49708,12 +49698,12 @@
         <v>23473.477713170843</v>
       </c>
     </row>
-    <row r="72" spans="1:55" s="74" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:55" s="74" customFormat="1" ht="15.75">
       <c r="B72" s="74" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="73" spans="1:55" s="74" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:55" s="74" customFormat="1" ht="15.75">
       <c r="B73" s="74" t="s">
         <v>124</v>
       </c>
@@ -49874,9 +49864,9 @@
         <v>36810.263386482577</v>
       </c>
     </row>
-    <row r="74" spans="1:55" s="74" customFormat="1" ht="15.75" x14ac:dyDescent="0.25"/>
-    <row r="75" spans="1:55" s="74" customFormat="1" ht="15.75" x14ac:dyDescent="0.25"/>
-    <row r="76" spans="1:55" s="74" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:55" s="74" customFormat="1" ht="15.75"/>
+    <row r="75" spans="1:55" s="74" customFormat="1" ht="15.75"/>
+    <row r="76" spans="1:55" s="74" customFormat="1" ht="15.75">
       <c r="A76" s="2" t="s">
         <v>165</v>
       </c>
@@ -49980,7 +49970,7 @@
       <c r="AI76" s="76"/>
       <c r="AJ76" s="76"/>
     </row>
-    <row r="77" spans="1:55" s="74" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:55" s="74" customFormat="1" ht="15.75">
       <c r="A77" s="3" t="s">
         <v>102</v>
       </c>
@@ -50116,7 +50106,7 @@
       <c r="AI77" s="77"/>
       <c r="AJ77" s="77"/>
     </row>
-    <row r="78" spans="1:55" s="74" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:55" s="74" customFormat="1" ht="15.75">
       <c r="A78" s="3" t="s">
         <v>103</v>
       </c>
@@ -50252,7 +50242,7 @@
       <c r="AI78" s="77"/>
       <c r="AJ78" s="77"/>
     </row>
-    <row r="79" spans="1:55" s="74" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:55" s="74" customFormat="1" ht="15.75">
       <c r="A79" s="3" t="s">
         <v>104</v>
       </c>
@@ -50388,7 +50378,7 @@
       <c r="AI79" s="77"/>
       <c r="AJ79" s="77"/>
     </row>
-    <row r="80" spans="1:55" s="74" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:55" s="74" customFormat="1" ht="15.75">
       <c r="A80" s="3" t="s">
         <v>105</v>
       </c>
@@ -50524,7 +50514,7 @@
       <c r="AI80" s="77"/>
       <c r="AJ80" s="77"/>
     </row>
-    <row r="81" spans="1:36" s="74" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:36" s="74" customFormat="1" ht="15.75">
       <c r="A81" s="3" t="s">
         <v>106</v>
       </c>
@@ -50660,7 +50650,7 @@
       <c r="AI81" s="77"/>
       <c r="AJ81" s="77"/>
     </row>
-    <row r="82" spans="1:36" s="74" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:36" s="74" customFormat="1" ht="15.75">
       <c r="A82" s="3" t="s">
         <v>107</v>
       </c>
@@ -50796,7 +50786,7 @@
       <c r="AI82" s="77"/>
       <c r="AJ82" s="77"/>
     </row>
-    <row r="83" spans="1:36" s="74" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:36" s="74" customFormat="1" ht="15.75">
       <c r="A83" s="3" t="s">
         <v>108</v>
       </c>
@@ -50932,7 +50922,7 @@
       <c r="AI83" s="77"/>
       <c r="AJ83" s="77"/>
     </row>
-    <row r="84" spans="1:36" s="74" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:36" s="74" customFormat="1" ht="15.75">
       <c r="A84" s="3" t="s">
         <v>109</v>
       </c>
@@ -51068,7 +51058,7 @@
       <c r="AI84" s="77"/>
       <c r="AJ84" s="77"/>
     </row>
-    <row r="85" spans="1:36" s="74" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:36" s="74" customFormat="1" ht="15.75">
       <c r="A85" s="3" t="s">
         <v>110</v>
       </c>
@@ -51204,7 +51194,7 @@
       <c r="AI85" s="77"/>
       <c r="AJ85" s="77"/>
     </row>
-    <row r="86" spans="1:36" s="74" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:36" s="74" customFormat="1" ht="15.75">
       <c r="A86" s="3" t="s">
         <v>111</v>
       </c>
@@ -51340,8 +51330,8 @@
       <c r="AI86" s="77"/>
       <c r="AJ86" s="77"/>
     </row>
-    <row r="87" spans="1:36" s="74" customFormat="1" ht="15.75" x14ac:dyDescent="0.25"/>
-    <row r="88" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:36" s="74" customFormat="1" ht="15.75"/>
+    <row r="88" spans="1:36" ht="15.75">
       <c r="A88" s="2" t="s">
         <v>167</v>
       </c>
@@ -51442,7 +51432,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="89" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:36" ht="15.75">
       <c r="A89" s="3" t="s">
         <v>102</v>
       </c>
@@ -51575,7 +51565,7 @@
         <v>5996857491.3620796</v>
       </c>
     </row>
-    <row r="90" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:36" ht="15.75">
       <c r="A90" s="3" t="s">
         <v>103</v>
       </c>
@@ -51708,7 +51698,7 @@
         <v>6092649373.6413736</v>
       </c>
     </row>
-    <row r="91" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:36" ht="15.75">
       <c r="A91" s="3" t="s">
         <v>104</v>
       </c>
@@ -51841,7 +51831,7 @@
         <v>4921899033.8039122</v>
       </c>
     </row>
-    <row r="92" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:36" ht="15.75">
       <c r="A92" s="3" t="s">
         <v>105</v>
       </c>
@@ -51974,7 +51964,7 @@
         <v>4009203689.6150379</v>
       </c>
     </row>
-    <row r="93" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:36" ht="15.75">
       <c r="A93" s="3" t="s">
         <v>106</v>
       </c>
@@ -52107,7 +52097,7 @@
         <v>13858416762.7997</v>
       </c>
     </row>
-    <row r="94" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:36" ht="15.75">
       <c r="A94" s="3" t="s">
         <v>107</v>
       </c>
@@ -52240,7 +52230,7 @@
         <v>202489837.31678164</v>
       </c>
     </row>
-    <row r="95" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:36" ht="15.75">
       <c r="A95" s="3" t="s">
         <v>108</v>
       </c>
@@ -52373,7 +52363,7 @@
         <v>270851560.49265301</v>
       </c>
     </row>
-    <row r="96" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:36" ht="15.75">
       <c r="A96" s="3" t="s">
         <v>109</v>
       </c>
@@ -52506,7 +52496,7 @@
         <v>305107518.63828403</v>
       </c>
     </row>
-    <row r="97" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:33" ht="15.75">
       <c r="A97" s="3" t="s">
         <v>110</v>
       </c>
@@ -52639,7 +52629,7 @@
         <v>648709168.4910059</v>
       </c>
     </row>
-    <row r="98" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:33" ht="15.75">
       <c r="A98" s="3" t="s">
         <v>111</v>
       </c>
@@ -52772,7 +52762,7 @@
         <v>1128440351.9515312</v>
       </c>
     </row>
-    <row r="100" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:33" ht="15.75">
       <c r="A100" s="2" t="s">
         <v>168</v>
       </c>
@@ -52873,7 +52863,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="101" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:33" ht="15.75">
       <c r="A101" s="3" t="s">
         <v>102</v>
       </c>
@@ -53006,7 +52996,7 @@
         <v>0.49603822209834753</v>
       </c>
     </row>
-    <row r="102" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:33" ht="15.75">
       <c r="A102" s="3" t="s">
         <v>103</v>
       </c>
@@ -53139,7 +53129,7 @@
         <v>0.50396177790165253</v>
       </c>
     </row>
-    <row r="103" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:33" ht="15.75">
       <c r="A103" s="3" t="s">
         <v>104</v>
       </c>
@@ -53272,7 +53262,7 @@
         <v>0.21406998251195397</v>
       </c>
     </row>
-    <row r="104" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:33" ht="15.75">
       <c r="A104" s="3" t="s">
         <v>105</v>
       </c>
@@ -53405,7 +53395,7 @@
         <v>0.17437378496150294</v>
       </c>
     </row>
-    <row r="105" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:33" ht="15.75">
       <c r="A105" s="3" t="s">
         <v>106</v>
       </c>
@@ -53538,7 +53528,7 @@
         <v>0.60274926683392283</v>
       </c>
     </row>
-    <row r="106" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:33" ht="15.75">
       <c r="A106" s="3" t="s">
         <v>107</v>
       </c>
@@ -53671,7 +53661,7 @@
         <v>8.806965692620258E-3</v>
       </c>
     </row>
-    <row r="107" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:33" ht="15.75">
       <c r="A107" s="3" t="s">
         <v>108</v>
       </c>
@@ -53804,7 +53794,7 @@
         <v>0.11510372302483096</v>
       </c>
     </row>
-    <row r="108" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:33" ht="15.75">
       <c r="A108" s="3" t="s">
         <v>109</v>
       </c>
@@ -53937,7 +53927,7 @@
         <v>0.12966146938292097</v>
       </c>
     </row>
-    <row r="109" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:33" ht="15.75">
       <c r="A109" s="3" t="s">
         <v>110</v>
       </c>
@@ -54070,7 +54060,7 @@
         <v>0.27568178052155834</v>
       </c>
     </row>
-    <row r="110" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:33" ht="15.75">
       <c r="A110" s="3" t="s">
         <v>111</v>
       </c>
@@ -54203,7 +54193,7 @@
         <v>0.47955302707068981</v>
       </c>
     </row>
-    <row r="111" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:33" ht="15.75">
       <c r="A111" s="3"/>
       <c r="B111" s="76"/>
       <c r="C111" s="78"/>
@@ -54238,7 +54228,7 @@
       <c r="AF111" s="78"/>
       <c r="AG111" s="78"/>
     </row>
-    <row r="112" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:33" ht="15.75">
       <c r="A112" s="3" t="s">
         <v>218</v>
       </c>
@@ -54368,7 +54358,7 @@
         <v>0.58604270197066977</v>
       </c>
     </row>
-    <row r="113" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:33" ht="15.75">
       <c r="A113" s="3" t="s">
         <v>219</v>
       </c>
@@ -54498,7 +54488,7 @@
         <v>0.41395729802933023</v>
       </c>
     </row>
-    <row r="114" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:33" ht="15.75">
       <c r="A114" s="3"/>
       <c r="B114" s="76"/>
       <c r="C114" s="78"/>
@@ -54533,7 +54523,7 @@
       <c r="AF114" s="78"/>
       <c r="AG114" s="78"/>
     </row>
-    <row r="115" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:33" ht="15.75">
       <c r="A115" s="3"/>
       <c r="B115" s="76"/>
       <c r="C115" s="78"/>
@@ -54568,7 +54558,7 @@
       <c r="AF115" s="78"/>
       <c r="AG115" s="78"/>
     </row>
-    <row r="116" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:33" ht="15.75">
       <c r="A116" s="2" t="s">
         <v>169</v>
       </c>
@@ -54669,7 +54659,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="117" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:33" ht="15.75">
       <c r="A117" s="3" t="s">
         <v>102</v>
       </c>
@@ -54678,395 +54668,395 @@
         <v>Freight LDV</v>
       </c>
       <c r="C117">
-        <f t="shared" ref="C117:AG117" si="58">C101*B2</f>
+        <f>C101*B2</f>
         <v>69.651741796091258</v>
       </c>
       <c r="D117">
-        <f t="shared" si="58"/>
+        <f>D101*C2</f>
         <v>68.405343880097718</v>
       </c>
       <c r="E117">
-        <f t="shared" si="58"/>
+        <f>E101*D2</f>
         <v>67.153063461395078</v>
       </c>
       <c r="F117">
-        <f t="shared" si="58"/>
+        <f>F101*E2</f>
         <v>65.894961294575467</v>
       </c>
       <c r="G117">
-        <f t="shared" si="58"/>
+        <f>G101*F2</f>
         <v>64.631099417151148</v>
       </c>
       <c r="H117">
-        <f t="shared" si="58"/>
+        <f>H101*G2</f>
         <v>63.361541137073736</v>
       </c>
       <c r="I117">
-        <f t="shared" si="58"/>
+        <f>I101*H2</f>
         <v>61.65653785333879</v>
       </c>
       <c r="J117">
-        <f t="shared" si="58"/>
+        <f>J101*I2</f>
         <v>59.968005769883867</v>
       </c>
       <c r="K117">
-        <f t="shared" si="58"/>
+        <f>K101*J2</f>
         <v>58.295897152462935</v>
       </c>
       <c r="L117">
-        <f t="shared" si="58"/>
+        <f>L101*K2</f>
         <v>56.640156563174976</v>
       </c>
       <c r="M117">
-        <f t="shared" si="58"/>
+        <f>M101*L2</f>
         <v>55.00072090811355</v>
       </c>
       <c r="N117">
-        <f t="shared" si="58"/>
+        <f>N101*M2</f>
         <v>55.111791955109659</v>
       </c>
       <c r="O117">
-        <f t="shared" si="58"/>
+        <f>O101*N2</f>
         <v>55.221041303228596</v>
       </c>
       <c r="P117">
-        <f t="shared" si="58"/>
+        <f>P101*O2</f>
         <v>55.328513029986425</v>
       </c>
       <c r="Q117">
-        <f t="shared" si="58"/>
+        <f>Q101*P2</f>
         <v>55.434249814191332</v>
       </c>
       <c r="R117">
-        <f t="shared" si="58"/>
+        <f>R101*Q2</f>
         <v>55.53829299042345</v>
       </c>
       <c r="S117">
-        <f t="shared" si="58"/>
+        <f>S101*R2</f>
         <v>55.519054476441021</v>
       </c>
       <c r="T117">
-        <f t="shared" si="58"/>
+        <f>T101*S2</f>
         <v>55.50003654867146</v>
       </c>
       <c r="U117">
-        <f t="shared" si="58"/>
+        <f>U101*T2</f>
         <v>55.481235440652426</v>
       </c>
       <c r="V117">
-        <f t="shared" si="58"/>
+        <f>V101*U2</f>
         <v>55.462647471201414</v>
       </c>
       <c r="W117">
-        <f t="shared" si="58"/>
+        <f>W101*V2</f>
         <v>55.444269042002567</v>
       </c>
       <c r="X117">
-        <f t="shared" si="58"/>
+        <f>X101*W2</f>
         <v>55.566617424537355</v>
       </c>
       <c r="Y117">
-        <f t="shared" si="58"/>
+        <f>Y101*X2</f>
         <v>55.688599727335038</v>
       </c>
       <c r="Z117">
-        <f t="shared" si="58"/>
+        <f>Z101*Y2</f>
         <v>55.810209419003954</v>
       </c>
       <c r="AA117">
-        <f t="shared" si="58"/>
+        <f>AA101*Z2</f>
         <v>55.931448114783805</v>
       </c>
       <c r="AB117">
-        <f t="shared" si="58"/>
+        <f>AB101*AA2</f>
         <v>56.052317421007245</v>
       </c>
       <c r="AC117">
-        <f t="shared" si="58"/>
+        <f>AC101*AB2</f>
         <v>56.052317517385902</v>
       </c>
       <c r="AD117">
-        <f t="shared" si="58"/>
+        <f>AD101*AC2</f>
         <v>56.052317740118177</v>
       </c>
       <c r="AE117">
-        <f t="shared" si="58"/>
+        <f>AE101*AD2</f>
         <v>56.052318082035598</v>
       </c>
       <c r="AF117">
-        <f t="shared" si="58"/>
+        <f>AF101*AE2</f>
         <v>56.052318536449839</v>
       </c>
       <c r="AG117">
-        <f t="shared" si="58"/>
+        <f>AG101*AF2</f>
         <v>56.052319097113269</v>
       </c>
     </row>
-    <row r="118" spans="1:33" s="98" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A118" s="96" t="s">
+    <row r="118" spans="1:33" s="113" customFormat="1" ht="15.75">
+      <c r="A118" s="111" t="s">
         <v>220</v>
       </c>
-      <c r="B118" s="97" t="s">
+      <c r="B118" s="112" t="s">
         <v>119</v>
       </c>
-      <c r="C118" s="98">
+      <c r="C118" s="113">
         <f>B3*C102*C112</f>
         <v>53.304021866824961</v>
       </c>
-      <c r="D118" s="98">
+      <c r="D118" s="113">
         <f>C3*D102*D112</f>
         <v>52.155018482028517</v>
       </c>
-      <c r="E118" s="98">
-        <f t="shared" ref="E118:AG118" si="59">D3*E102*E112</f>
+      <c r="E118" s="113">
+        <f t="shared" ref="E118:AG118" si="58">D3*E102*E112</f>
         <v>51.277836879458782</v>
       </c>
-      <c r="F118" s="98">
-        <f t="shared" si="59"/>
+      <c r="F118" s="113">
+        <f t="shared" si="58"/>
         <v>50.34987839511178</v>
       </c>
-      <c r="G118" s="98">
-        <f t="shared" si="59"/>
+      <c r="G118" s="113">
+        <f t="shared" si="58"/>
         <v>49.409317984171402</v>
       </c>
-      <c r="H118" s="98">
-        <f t="shared" si="59"/>
+      <c r="H118" s="113">
+        <f t="shared" si="58"/>
         <v>48.442664362737659</v>
       </c>
-      <c r="I118" s="98">
-        <f t="shared" si="59"/>
+      <c r="I118" s="113">
+        <f t="shared" si="58"/>
         <v>47.808026257758918</v>
       </c>
-      <c r="J118" s="98">
-        <f t="shared" si="59"/>
+      <c r="J118" s="113">
+        <f t="shared" si="58"/>
         <v>47.186220905640262</v>
       </c>
-      <c r="K118" s="98">
-        <f t="shared" si="59"/>
+      <c r="K118" s="113">
+        <f t="shared" si="58"/>
         <v>46.576900169665052</v>
       </c>
-      <c r="L118" s="98">
-        <f t="shared" si="59"/>
+      <c r="L118" s="113">
+        <f t="shared" si="58"/>
         <v>45.975132659327556</v>
       </c>
-      <c r="M118" s="98">
-        <f t="shared" si="59"/>
+      <c r="M118" s="113">
+        <f t="shared" si="58"/>
         <v>45.362043357630569</v>
       </c>
-      <c r="N118" s="98">
-        <f t="shared" si="59"/>
+      <c r="N118" s="113">
+        <f t="shared" si="58"/>
         <v>45.567511626139769</v>
       </c>
-      <c r="O118" s="98">
-        <f t="shared" si="59"/>
+      <c r="O118" s="113">
+        <f t="shared" si="58"/>
         <v>45.788556878920801</v>
       </c>
-      <c r="P118" s="98">
-        <f t="shared" si="59"/>
+      <c r="P118" s="113">
+        <f t="shared" si="58"/>
         <v>46.00234845534608</v>
       </c>
-      <c r="Q118" s="98">
-        <f t="shared" si="59"/>
+      <c r="Q118" s="113">
+        <f t="shared" si="58"/>
         <v>46.210918943367602</v>
       </c>
-      <c r="R118" s="98">
-        <f t="shared" si="59"/>
+      <c r="R118" s="113">
+        <f t="shared" si="58"/>
         <v>46.420651933431621</v>
       </c>
-      <c r="S118" s="98">
-        <f t="shared" si="59"/>
+      <c r="S118" s="113">
+        <f t="shared" si="58"/>
         <v>46.730173109712759</v>
       </c>
-      <c r="T118" s="98">
-        <f t="shared" si="59"/>
+      <c r="T118" s="113">
+        <f t="shared" si="58"/>
         <v>47.044993988181922</v>
       </c>
-      <c r="U118" s="98">
-        <f t="shared" si="59"/>
+      <c r="U118" s="113">
+        <f t="shared" si="58"/>
         <v>47.342243651751318</v>
       </c>
-      <c r="V118" s="98">
-        <f t="shared" si="59"/>
+      <c r="V118" s="113">
+        <f t="shared" si="58"/>
         <v>47.66766743986048</v>
       </c>
-      <c r="W118" s="98">
-        <f t="shared" si="59"/>
+      <c r="W118" s="113">
+        <f t="shared" si="58"/>
         <v>47.998141783158182</v>
       </c>
-      <c r="X118" s="98">
-        <f t="shared" si="59"/>
+      <c r="X118" s="113">
+        <f t="shared" si="58"/>
         <v>48.200867151882065</v>
       </c>
-      <c r="Y118" s="98">
-        <f t="shared" si="59"/>
+      <c r="Y118" s="113">
+        <f t="shared" si="58"/>
         <v>48.400507821761643</v>
       </c>
-      <c r="Z118" s="98">
-        <f t="shared" si="59"/>
+      <c r="Z118" s="113">
+        <f t="shared" si="58"/>
         <v>48.604601230918732</v>
       </c>
-      <c r="AA118" s="98">
-        <f t="shared" si="59"/>
+      <c r="AA118" s="113">
+        <f t="shared" si="58"/>
         <v>48.809614035663294</v>
       </c>
-      <c r="AB118" s="98">
-        <f t="shared" si="59"/>
+      <c r="AB118" s="113">
+        <f t="shared" si="58"/>
         <v>49.009633942897182</v>
       </c>
-      <c r="AC118" s="98">
-        <f t="shared" si="59"/>
+      <c r="AC118" s="113">
+        <f t="shared" si="58"/>
         <v>49.312416471325243</v>
       </c>
-      <c r="AD118" s="98">
-        <f t="shared" si="59"/>
+      <c r="AD118" s="113">
+        <f t="shared" si="58"/>
         <v>49.615613646906461</v>
       </c>
-      <c r="AE118" s="98">
-        <f t="shared" si="59"/>
+      <c r="AE118" s="113">
+        <f t="shared" si="58"/>
         <v>49.916476278090919</v>
       </c>
-      <c r="AF118" s="98">
-        <f t="shared" si="59"/>
+      <c r="AF118" s="113">
+        <f t="shared" si="58"/>
         <v>50.213960108784036</v>
       </c>
-      <c r="AG118" s="98">
-        <f t="shared" si="59"/>
+      <c r="AG118" s="113">
+        <f t="shared" si="58"/>
         <v>50.50367386395402</v>
       </c>
     </row>
-    <row r="119" spans="1:33" s="98" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A119" s="96" t="s">
+    <row r="119" spans="1:33" s="113" customFormat="1" ht="15.75">
+      <c r="A119" s="111" t="s">
         <v>221</v>
       </c>
-      <c r="B119" s="97" t="s">
+      <c r="B119" s="112" t="s">
         <v>117</v>
       </c>
-      <c r="C119" s="98">
+      <c r="C119" s="113">
         <f>B3*C102*C113</f>
         <v>54.355075119185805</v>
       </c>
-      <c r="D119" s="98">
+      <c r="D119" s="113">
         <f>C3*D102*D113</f>
         <v>53.183415587587142</v>
       </c>
-      <c r="E119" s="98">
-        <f t="shared" ref="E119:AG119" si="60">D3*E102*E113</f>
+      <c r="E119" s="113">
+        <f t="shared" ref="E119:AG119" si="59">D3*E102*E113</f>
         <v>51.7489926791635</v>
       </c>
-      <c r="F119" s="98">
-        <f t="shared" si="60"/>
+      <c r="F119" s="113">
+        <f t="shared" si="59"/>
         <v>50.374310792895571</v>
       </c>
-      <c r="G119" s="98">
-        <f t="shared" si="60"/>
+      <c r="G119" s="113">
+        <f t="shared" si="59"/>
         <v>49.021098730344441</v>
       </c>
-      <c r="H119" s="98">
-        <f t="shared" si="60"/>
+      <c r="H119" s="113">
+        <f t="shared" si="59"/>
         <v>47.702749573337883</v>
       </c>
-      <c r="I119" s="98">
-        <f t="shared" si="60"/>
+      <c r="I119" s="113">
+        <f t="shared" si="59"/>
         <v>46.712706674275829</v>
       </c>
-      <c r="J119" s="98">
-        <f t="shared" si="60"/>
+      <c r="J119" s="113">
+        <f t="shared" si="59"/>
         <v>45.684430144123361</v>
       </c>
-      <c r="K119" s="98">
-        <f t="shared" si="60"/>
+      <c r="K119" s="113">
+        <f t="shared" si="59"/>
         <v>44.618344228080957</v>
       </c>
-      <c r="L119" s="98">
-        <f t="shared" si="60"/>
+      <c r="L119" s="113">
+        <f t="shared" si="59"/>
         <v>43.519468310897793</v>
       </c>
-      <c r="M119" s="98">
-        <f t="shared" si="60"/>
+      <c r="M119" s="113">
+        <f t="shared" si="59"/>
         <v>42.406777215047157</v>
       </c>
-      <c r="N119" s="98">
-        <f t="shared" si="60"/>
+      <c r="N119" s="113">
+        <f t="shared" si="59"/>
         <v>42.033227981614651</v>
       </c>
-      <c r="O119" s="98">
-        <f t="shared" si="60"/>
+      <c r="O119" s="113">
+        <f t="shared" si="59"/>
         <v>41.646858494069562</v>
       </c>
-      <c r="P119" s="98">
-        <f t="shared" si="60"/>
+      <c r="P119" s="113">
+        <f t="shared" si="59"/>
         <v>41.27043271166562</v>
       </c>
-      <c r="Q119" s="98">
-        <f t="shared" si="60"/>
+      <c r="Q119" s="113">
+        <f t="shared" si="59"/>
         <v>40.901853461705699</v>
       </c>
-      <c r="R119" s="98">
-        <f t="shared" si="60"/>
+      <c r="R119" s="113">
+        <f t="shared" si="59"/>
         <v>40.534674603184207</v>
       </c>
-      <c r="S119" s="98">
-        <f t="shared" si="60"/>
+      <c r="S119" s="113">
+        <f t="shared" si="59"/>
         <v>40.254266576380921</v>
       </c>
-      <c r="T119" s="98">
-        <f t="shared" si="60"/>
+      <c r="T119" s="113">
+        <f t="shared" si="59"/>
         <v>39.96822503993473</v>
       </c>
-      <c r="U119" s="98">
-        <f t="shared" si="60"/>
+      <c r="U119" s="113">
+        <f t="shared" si="59"/>
         <v>39.699426610624215</v>
       </c>
-      <c r="V119" s="98">
-        <f t="shared" si="60"/>
+      <c r="V119" s="113">
+        <f t="shared" si="59"/>
         <v>39.40213151964889</v>
       </c>
-      <c r="W119" s="98">
-        <f t="shared" si="60"/>
+      <c r="W119" s="113">
+        <f t="shared" si="59"/>
         <v>39.099468781598993</v>
       </c>
-      <c r="X119" s="98">
-        <f t="shared" si="60"/>
+      <c r="X119" s="113">
+        <f t="shared" si="59"/>
         <v>38.711596745499477</v>
       </c>
-      <c r="Y119" s="98">
-        <f t="shared" si="60"/>
+      <c r="Y119" s="113">
+        <f t="shared" si="59"/>
         <v>38.327363387315437</v>
       </c>
-      <c r="Z119" s="98">
-        <f t="shared" si="60"/>
+      <c r="Z119" s="113">
+        <f t="shared" si="59"/>
         <v>37.939241152712441</v>
       </c>
-      <c r="AA119" s="98">
-        <f t="shared" si="60"/>
+      <c r="AA119" s="113">
+        <f t="shared" si="59"/>
         <v>37.550760941079794</v>
       </c>
-      <c r="AB119" s="98">
-        <f t="shared" si="60"/>
+      <c r="AB119" s="113">
+        <f t="shared" si="59"/>
         <v>37.167832614693609</v>
       </c>
-      <c r="AC119" s="98">
-        <f t="shared" si="60"/>
+      <c r="AC119" s="113">
+        <f t="shared" si="59"/>
         <v>36.865049940418224</v>
       </c>
-      <c r="AD119" s="98">
-        <f t="shared" si="60"/>
+      <c r="AD119" s="113">
+        <f t="shared" si="59"/>
         <v>36.561852427781936</v>
       </c>
-      <c r="AE119" s="98">
-        <f t="shared" si="60"/>
+      <c r="AE119" s="113">
+        <f t="shared" si="59"/>
         <v>36.26098927918266</v>
       </c>
-      <c r="AF119" s="98">
-        <f t="shared" si="60"/>
+      <c r="AF119" s="113">
+        <f t="shared" si="59"/>
         <v>35.96350476083613</v>
       </c>
-      <c r="AG119" s="98">
-        <f t="shared" si="60"/>
+      <c r="AG119" s="113">
+        <f t="shared" si="59"/>
         <v>35.673790157228566</v>
       </c>
     </row>
-    <row r="120" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:33" ht="15.75">
       <c r="A120" s="3" t="s">
         <v>104</v>
       </c>
@@ -55075,131 +55065,131 @@
         <v>Freight HDV</v>
       </c>
       <c r="C120">
-        <f t="shared" ref="C120:AG120" si="61">C103*B4</f>
+        <f>C103*B4</f>
         <v>55.633888302938409</v>
       </c>
       <c r="D120">
-        <f t="shared" si="61"/>
+        <f>D103*C4</f>
         <v>55.669202360246473</v>
       </c>
       <c r="E120">
-        <f t="shared" si="61"/>
+        <f>E103*D4</f>
         <v>55.620997456266807</v>
       </c>
       <c r="F120">
-        <f t="shared" si="61"/>
+        <f>F103*E4</f>
         <v>55.484335261845807</v>
       </c>
       <c r="G120">
-        <f t="shared" si="61"/>
+        <f>G103*F4</f>
         <v>55.254376094041554</v>
       </c>
       <c r="H120">
-        <f t="shared" si="61"/>
+        <f>H103*G4</f>
         <v>54.926430967111244</v>
       </c>
       <c r="I120">
-        <f t="shared" si="61"/>
+        <f>I103*H4</f>
         <v>54.33284293507856</v>
       </c>
       <c r="J120">
-        <f t="shared" si="61"/>
+        <f>J103*I4</f>
         <v>53.65022818064854</v>
       </c>
       <c r="K120">
-        <f t="shared" si="61"/>
+        <f>K103*J4</f>
         <v>52.876870138999905</v>
       </c>
       <c r="L120">
-        <f t="shared" si="61"/>
+        <f>L103*K4</f>
         <v>52.011203310904747</v>
       </c>
       <c r="M120">
-        <f t="shared" si="61"/>
+        <f>M103*L4</f>
         <v>51.051825741548299</v>
       </c>
       <c r="N120">
-        <f t="shared" si="61"/>
+        <f>N103*M4</f>
         <v>51.985107237942564</v>
       </c>
       <c r="O120">
-        <f t="shared" si="61"/>
+        <f>O103*N4</f>
         <v>52.903063174294616</v>
       </c>
       <c r="P120">
-        <f t="shared" si="61"/>
+        <f>P103*O4</f>
         <v>53.805731025450449</v>
       </c>
       <c r="Q120">
-        <f t="shared" si="61"/>
+        <f>Q103*P4</f>
         <v>54.69315370179158</v>
       </c>
       <c r="R120">
-        <f t="shared" si="61"/>
+        <f>R103*Q4</f>
         <v>55.565379417587131</v>
       </c>
       <c r="S120">
-        <f t="shared" si="61"/>
+        <f>S103*R4</f>
         <v>56.284072481521378</v>
       </c>
       <c r="T120">
-        <f t="shared" si="61"/>
+        <f>T103*S4</f>
         <v>56.989254802837443</v>
       </c>
       <c r="U120">
-        <f t="shared" si="61"/>
+        <f>U103*T4</f>
         <v>57.68118808798679</v>
       </c>
       <c r="V120">
-        <f t="shared" si="61"/>
+        <f>V103*U4</f>
         <v>58.360128839886066</v>
       </c>
       <c r="W120">
-        <f t="shared" si="61"/>
+        <f>W103*V4</f>
         <v>59.02632845318027</v>
       </c>
       <c r="X120">
-        <f t="shared" si="61"/>
+        <f>X103*W4</f>
         <v>59.615919986244933</v>
       </c>
       <c r="Y120">
-        <f t="shared" si="61"/>
+        <f>Y103*X4</f>
         <v>60.17722546491602</v>
       </c>
       <c r="Z120">
-        <f t="shared" si="61"/>
+        <f>Z103*Y4</f>
         <v>60.726423671766206</v>
       </c>
       <c r="AA120">
-        <f t="shared" si="61"/>
+        <f>AA103*Z4</f>
         <v>61.263799593207757</v>
       </c>
       <c r="AB120">
-        <f t="shared" si="61"/>
+        <f>AB103*AA4</f>
         <v>61.789629352580214</v>
       </c>
       <c r="AC120">
-        <f t="shared" si="61"/>
+        <f>AC103*AB4</f>
         <v>62.29611376875544</v>
       </c>
       <c r="AD120">
-        <f t="shared" si="61"/>
+        <f>AD103*AC4</f>
         <v>62.792228658636922</v>
       </c>
       <c r="AE120">
-        <f t="shared" si="61"/>
+        <f>AE103*AD4</f>
         <v>63.278242149591421</v>
       </c>
       <c r="AF120">
-        <f t="shared" si="61"/>
+        <f>AF103*AE4</f>
         <v>63.75441376452337</v>
       </c>
       <c r="AG120">
-        <f t="shared" si="61"/>
+        <f>AG103*AF4</f>
         <v>64.220994753586197</v>
       </c>
     </row>
-    <row r="121" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:33" ht="15.75">
       <c r="A121" s="3" t="s">
         <v>105</v>
       </c>
@@ -55208,131 +55198,131 @@
         <v>Freight HDV</v>
       </c>
       <c r="C121">
-        <f t="shared" ref="C121:AG121" si="62">C104*B5</f>
+        <f>C104*B5</f>
         <v>94.47671513876567</v>
       </c>
       <c r="D121">
-        <f t="shared" si="62"/>
+        <f>D104*C5</f>
         <v>90.954230220927244</v>
       </c>
       <c r="E121">
-        <f t="shared" si="62"/>
+        <f>E104*D5</f>
         <v>87.529403836024201</v>
       </c>
       <c r="F121">
-        <f t="shared" si="62"/>
+        <f>F104*E5</f>
         <v>84.197091694189581</v>
       </c>
       <c r="G121">
-        <f t="shared" si="62"/>
+        <f>G104*F5</f>
         <v>80.9516946117663</v>
       </c>
       <c r="H121">
-        <f t="shared" si="62"/>
+        <f>H104*G5</f>
         <v>77.78717802795687</v>
       </c>
       <c r="I121">
-        <f t="shared" si="62"/>
+        <f>I104*H5</f>
         <v>74.543172280479624</v>
       </c>
       <c r="J121">
-        <f t="shared" si="62"/>
+        <f>J104*I5</f>
         <v>71.347351879790509</v>
       </c>
       <c r="K121">
-        <f t="shared" si="62"/>
+        <f>K104*J5</f>
         <v>68.197715804196278</v>
       </c>
       <c r="L121">
-        <f t="shared" si="62"/>
+        <f>L104*K5</f>
         <v>65.092129376217898</v>
       </c>
       <c r="M121">
-        <f t="shared" si="62"/>
+        <f>M104*L5</f>
         <v>62.028328296526638</v>
       </c>
       <c r="N121">
-        <f t="shared" si="62"/>
+        <f>N104*M5</f>
         <v>61.735869714283773</v>
       </c>
       <c r="O121">
-        <f t="shared" si="62"/>
+        <f>O104*N5</f>
         <v>61.450542748043603</v>
       </c>
       <c r="P121">
-        <f t="shared" si="62"/>
+        <f>P104*O5</f>
         <v>61.172294065047296</v>
       </c>
       <c r="Q121">
-        <f t="shared" si="62"/>
+        <f>Q104*P5</f>
         <v>60.901068358613152</v>
       </c>
       <c r="R121">
-        <f t="shared" si="62"/>
+        <f>R104*Q5</f>
         <v>60.636808423081277</v>
       </c>
       <c r="S121">
-        <f t="shared" si="62"/>
+        <f>S104*R5</f>
         <v>60.465726162349341</v>
       </c>
       <c r="T121">
-        <f t="shared" si="62"/>
+        <f>T104*S5</f>
         <v>60.29811180207362</v>
       </c>
       <c r="U121">
-        <f t="shared" si="62"/>
+        <f>U104*T5</f>
         <v>60.133891808100977</v>
       </c>
       <c r="V121">
-        <f t="shared" si="62"/>
+        <f>V104*U5</f>
         <v>59.972994281403807</v>
       </c>
       <c r="W121">
-        <f t="shared" si="62"/>
+        <f>W104*V5</f>
         <v>59.815348922101791</v>
       </c>
       <c r="X121">
-        <f t="shared" si="62"/>
+        <f>X104*W5</f>
         <v>59.618237569638055</v>
       </c>
       <c r="Y121">
-        <f t="shared" si="62"/>
+        <f>Y104*X5</f>
         <v>59.428937819381467</v>
       </c>
       <c r="Z121">
-        <f t="shared" si="62"/>
+        <f>Z104*Y5</f>
         <v>59.243229240298341</v>
       </c>
       <c r="AA121">
-        <f t="shared" si="62"/>
+        <f>AA104*Z5</f>
         <v>59.061028426944262</v>
       </c>
       <c r="AB121">
-        <f t="shared" si="62"/>
+        <f>AB104*AA5</f>
         <v>58.882254566791332</v>
       </c>
       <c r="AC121">
-        <f t="shared" si="62"/>
+        <f>AC104*AB5</f>
         <v>58.712961179625943</v>
       </c>
       <c r="AD121">
-        <f t="shared" si="62"/>
+        <f>AD104*AC5</f>
         <v>58.546812822802522</v>
       </c>
       <c r="AE121">
-        <f t="shared" si="62"/>
+        <f>AE104*AD5</f>
         <v>58.383731530826175</v>
       </c>
       <c r="AF121">
-        <f t="shared" si="62"/>
+        <f>AF104*AE5</f>
         <v>58.223641779259381</v>
       </c>
       <c r="AG121">
-        <f t="shared" si="62"/>
+        <f>AG104*AF5</f>
         <v>58.066470392180477</v>
       </c>
     </row>
-    <row r="122" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:33" ht="15.75">
       <c r="A122" s="3" t="s">
         <v>106</v>
       </c>
@@ -55341,131 +55331,131 @@
         <v>Freight HDV</v>
       </c>
       <c r="C122">
-        <f t="shared" ref="C122:AG122" si="63">C105*B6</f>
+        <f>C105*B6</f>
         <v>659.59284421045106</v>
       </c>
       <c r="D122">
-        <f t="shared" si="63"/>
+        <f>D105*C6</f>
         <v>635.17128215792673</v>
       </c>
       <c r="E122">
-        <f t="shared" si="63"/>
+        <f>E105*D6</f>
         <v>610.77145755083734</v>
       </c>
       <c r="F122">
-        <f t="shared" si="63"/>
+        <f>F105*E6</f>
         <v>586.41665980216987</v>
       </c>
       <c r="G122">
-        <f t="shared" si="63"/>
+        <f>G105*F6</f>
         <v>562.13081485367525</v>
       </c>
       <c r="H122">
-        <f t="shared" si="63"/>
+        <f>H105*G6</f>
         <v>537.93830668895453</v>
       </c>
       <c r="I122">
-        <f t="shared" si="63"/>
+        <f>I105*H6</f>
         <v>514.54638033720175</v>
       </c>
       <c r="J122">
-        <f t="shared" si="63"/>
+        <f>J105*I6</f>
         <v>491.29521351057201</v>
       </c>
       <c r="K122">
-        <f t="shared" si="63"/>
+        <f>K105*J6</f>
         <v>468.19356000377155</v>
       </c>
       <c r="L122">
-        <f t="shared" si="63"/>
+        <f>L105*K6</f>
         <v>445.25004057107219</v>
       </c>
       <c r="M122">
-        <f t="shared" si="63"/>
+        <f>M105*L6</f>
         <v>422.47310089013445</v>
       </c>
       <c r="N122">
-        <f t="shared" si="63"/>
+        <f>N105*M6</f>
         <v>420.85786941866127</v>
       </c>
       <c r="O122">
-        <f t="shared" si="63"/>
+        <f>O105*N6</f>
         <v>419.26159648037464</v>
       </c>
       <c r="P122">
-        <f t="shared" si="63"/>
+        <f>P105*O6</f>
         <v>417.68436879348303</v>
       </c>
       <c r="Q122">
-        <f t="shared" si="63"/>
+        <f>Q105*P6</f>
         <v>416.12626414931623</v>
       </c>
       <c r="R122">
-        <f t="shared" si="63"/>
+        <f>R105*Q6</f>
         <v>414.58735149957158</v>
       </c>
       <c r="S122">
-        <f t="shared" si="63"/>
+        <f>S105*R6</f>
         <v>413.24931956659549</v>
       </c>
       <c r="T122">
-        <f t="shared" si="63"/>
+        <f>T105*S6</f>
         <v>411.93482237992498</v>
       </c>
       <c r="U122">
-        <f t="shared" si="63"/>
+        <f>U105*T6</f>
         <v>410.64342757059234</v>
       </c>
       <c r="V122">
-        <f t="shared" si="63"/>
+        <f>V105*U6</f>
         <v>409.3747108681664</v>
       </c>
       <c r="W122">
-        <f t="shared" si="63"/>
+        <f>W105*V6</f>
         <v>408.12825596664248</v>
       </c>
       <c r="X122">
-        <f t="shared" si="63"/>
+        <f>X105*W6</f>
         <v>407.1554809251183</v>
       </c>
       <c r="Y122">
-        <f t="shared" si="63"/>
+        <f>Y105*X6</f>
         <v>406.23193255768859</v>
       </c>
       <c r="Z122">
-        <f t="shared" si="63"/>
+        <f>Z105*Y6</f>
         <v>405.3288541640751</v>
       </c>
       <c r="AA122">
-        <f t="shared" si="63"/>
+        <f>AA105*Z6</f>
         <v>404.44575973443358</v>
       </c>
       <c r="AB122">
-        <f t="shared" si="63"/>
+        <f>AB105*AA6</f>
         <v>403.58217838179917</v>
       </c>
       <c r="AC122">
-        <f t="shared" si="63"/>
+        <f>AC105*AB6</f>
         <v>402.75595818669683</v>
       </c>
       <c r="AD122">
-        <f t="shared" si="63"/>
+        <f>AD105*AC6</f>
         <v>401.94736215722946</v>
       </c>
       <c r="AE122">
-        <f t="shared" si="63"/>
+        <f>AE105*AD6</f>
         <v>401.15592734382062</v>
       </c>
       <c r="AF122">
-        <f t="shared" si="63"/>
+        <f>AF105*AE6</f>
         <v>400.38120578188415</v>
       </c>
       <c r="AG122">
-        <f t="shared" si="63"/>
+        <f>AG105*AF6</f>
         <v>399.62276391089085</v>
       </c>
     </row>
-    <row r="123" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:33" ht="15.75">
       <c r="A123" s="3" t="s">
         <v>107</v>
       </c>
@@ -55474,131 +55464,131 @@
         <v>Freight HDV</v>
       </c>
       <c r="C123">
-        <f t="shared" ref="C123:AG123" si="64">C106*B7</f>
+        <f>C106*B7</f>
         <v>1.8638843724121492</v>
       </c>
       <c r="D123">
-        <f t="shared" si="64"/>
+        <f>D106*C7</f>
         <v>1.8825069619827013</v>
       </c>
       <c r="E123">
-        <f t="shared" si="64"/>
+        <f>E106*D7</f>
         <v>1.900734319478333</v>
       </c>
       <c r="F123">
-        <f t="shared" si="64"/>
+        <f>F106*E7</f>
         <v>1.9183763659700317</v>
       </c>
       <c r="G123">
-        <f t="shared" si="64"/>
+        <f>G106*F7</f>
         <v>1.935222424126815</v>
       </c>
       <c r="H123">
-        <f t="shared" si="64"/>
+        <f>H106*G7</f>
         <v>1.9510407889931005</v>
       </c>
       <c r="I123">
-        <f t="shared" si="64"/>
+        <f>I106*H7</f>
         <v>1.9635953959192864</v>
       </c>
       <c r="J123">
-        <f t="shared" si="64"/>
+        <f>J106*I7</f>
         <v>1.9728146989027788</v>
       </c>
       <c r="K123">
-        <f t="shared" si="64"/>
+        <f>K106*J7</f>
         <v>1.9785117247699857</v>
       </c>
       <c r="L123">
-        <f t="shared" si="64"/>
+        <f>L106*K7</f>
         <v>1.980500794373649</v>
       </c>
       <c r="M123">
-        <f t="shared" si="64"/>
+        <f>M106*L7</f>
         <v>1.9785983042012205</v>
       </c>
       <c r="N123">
-        <f t="shared" si="64"/>
+        <f>N106*M7</f>
         <v>2.0421097239309183</v>
       </c>
       <c r="O123">
-        <f t="shared" si="64"/>
+        <f>O106*N7</f>
         <v>2.1059561889753446</v>
       </c>
       <c r="P123">
-        <f t="shared" si="64"/>
+        <f>P106*O7</f>
         <v>2.1701078863579237</v>
       </c>
       <c r="Q123">
-        <f t="shared" si="64"/>
+        <f>Q106*P7</f>
         <v>2.2345354004701115</v>
       </c>
       <c r="R123">
-        <f t="shared" si="64"/>
+        <f>R106*Q7</f>
         <v>2.2992097387102599</v>
       </c>
       <c r="S123">
-        <f t="shared" si="64"/>
+        <f>S106*R7</f>
         <v>2.3417243276595285</v>
       </c>
       <c r="T123">
-        <f t="shared" si="64"/>
+        <f>T106*S7</f>
         <v>2.3839657101685114</v>
       </c>
       <c r="U123">
-        <f t="shared" si="64"/>
+        <f>U106*T7</f>
         <v>2.4259340761416346</v>
       </c>
       <c r="V123">
-        <f t="shared" si="64"/>
+        <f>V106*U7</f>
         <v>2.4676296840734873</v>
       </c>
       <c r="W123">
-        <f t="shared" si="64"/>
+        <f>W106*V7</f>
         <v>2.5090528587961813</v>
       </c>
       <c r="X123">
-        <f t="shared" si="64"/>
+        <f>X106*W7</f>
         <v>2.5383350613507778</v>
       </c>
       <c r="Y123">
-        <f t="shared" si="64"/>
+        <f>Y106*X7</f>
         <v>2.5665502881387141</v>
       </c>
       <c r="Z123">
-        <f t="shared" si="64"/>
+        <f>Z106*Y7</f>
         <v>2.5943594478463519</v>
       </c>
       <c r="AA123">
-        <f t="shared" si="64"/>
+        <f>AA106*Z7</f>
         <v>2.6217730107615789</v>
       </c>
       <c r="AB123">
-        <f t="shared" si="64"/>
+        <f>AB106*AA7</f>
         <v>2.6488011187194838</v>
       </c>
       <c r="AC123">
-        <f t="shared" si="64"/>
+        <f>AC106*AB7</f>
         <v>2.6694840570892522</v>
       </c>
       <c r="AD123">
-        <f t="shared" si="64"/>
+        <f>AD106*AC7</f>
         <v>2.6897108827046097</v>
       </c>
       <c r="AE123">
-        <f t="shared" si="64"/>
+        <f>AE106*AD7</f>
         <v>2.7094936504803879</v>
       </c>
       <c r="AF123">
-        <f t="shared" si="64"/>
+        <f>AF106*AE7</f>
         <v>2.7288440250951136</v>
       </c>
       <c r="AG123">
-        <f t="shared" si="64"/>
+        <f>AG106*AF7</f>
         <v>2.7477732960975203</v>
       </c>
     </row>
-    <row r="124" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:33" ht="15.75">
       <c r="A124" s="3" t="s">
         <v>108</v>
       </c>
@@ -55607,131 +55597,131 @@
         <v>Passenger HDV</v>
       </c>
       <c r="C124">
-        <f t="shared" ref="C124:AG124" si="65">C107*B8</f>
+        <f>C107*B8</f>
         <v>14.213188382847221</v>
       </c>
       <c r="D124">
-        <f t="shared" si="65"/>
+        <f>D107*C8</f>
         <v>14.078043081441731</v>
       </c>
       <c r="E124">
-        <f t="shared" si="65"/>
+        <f>E107*D8</f>
         <v>13.943114052038192</v>
       </c>
       <c r="F124">
-        <f t="shared" si="65"/>
+        <f>F107*E8</f>
         <v>13.808397705797544</v>
       </c>
       <c r="G124">
-        <f t="shared" si="65"/>
+        <f>G107*F8</f>
         <v>13.673890242928115</v>
       </c>
       <c r="H124">
-        <f t="shared" si="65"/>
+        <f>H107*G8</f>
         <v>13.539587643342651</v>
       </c>
       <c r="I124">
-        <f t="shared" si="65"/>
+        <f>I107*H8</f>
         <v>13.440541412372941</v>
       </c>
       <c r="J124">
-        <f t="shared" si="65"/>
+        <f>J107*I8</f>
         <v>13.341285966355795</v>
       </c>
       <c r="K124">
-        <f t="shared" si="65"/>
+        <f>K107*J8</f>
         <v>13.241816880601329</v>
       </c>
       <c r="L124">
-        <f t="shared" si="65"/>
+        <f>L107*K8</f>
         <v>13.142129580657411</v>
       </c>
       <c r="M124">
-        <f t="shared" si="65"/>
+        <f>M107*L8</f>
         <v>13.042219335983376</v>
       </c>
       <c r="N124">
-        <f t="shared" si="65"/>
+        <f>N107*M8</f>
         <v>13.028573042080531</v>
       </c>
       <c r="O124">
-        <f t="shared" si="65"/>
+        <f>O107*N8</f>
         <v>13.014328761043148</v>
       </c>
       <c r="P124">
-        <f t="shared" si="65"/>
+        <f>P107*O8</f>
         <v>12.999476644387256</v>
       </c>
       <c r="Q124">
-        <f t="shared" si="65"/>
+        <f>Q107*P8</f>
         <v>12.984006608112743</v>
       </c>
       <c r="R124">
-        <f t="shared" si="65"/>
+        <f>R107*Q8</f>
         <v>12.967908326054395</v>
       </c>
       <c r="S124">
-        <f t="shared" si="65"/>
+        <f>S107*R8</f>
         <v>12.997904383128807</v>
       </c>
       <c r="T124">
-        <f t="shared" si="65"/>
+        <f>T107*S8</f>
         <v>13.027687297517366</v>
       </c>
       <c r="U124">
-        <f t="shared" si="65"/>
+        <f>U107*T8</f>
         <v>13.057258916087493</v>
       </c>
       <c r="V124">
-        <f t="shared" si="65"/>
+        <f>V107*U8</f>
         <v>13.08662107075515</v>
       </c>
       <c r="W124">
-        <f t="shared" si="65"/>
+        <f>W107*V8</f>
         <v>13.115775578461323</v>
       </c>
       <c r="X124">
-        <f t="shared" si="65"/>
+        <f>X107*W8</f>
         <v>13.147497245935343</v>
       </c>
       <c r="Y124">
-        <f t="shared" si="65"/>
+        <f>Y107*X8</f>
         <v>13.179304231382698</v>
       </c>
       <c r="Z124">
-        <f t="shared" si="65"/>
+        <f>Z107*Y8</f>
         <v>13.211197945311413</v>
       </c>
       <c r="AA124">
-        <f t="shared" si="65"/>
+        <f>AA107*Z8</f>
         <v>13.243178612406309</v>
       </c>
       <c r="AB124">
-        <f t="shared" si="65"/>
+        <f>AB107*AA8</f>
         <v>13.275246458673314</v>
       </c>
       <c r="AC124">
-        <f t="shared" si="65"/>
+        <f>AC107*AB8</f>
         <v>13.267609567947382</v>
       </c>
       <c r="AD124">
-        <f t="shared" si="65"/>
+        <f>AD107*AC8</f>
         <v>13.259959324871861</v>
       </c>
       <c r="AE124">
-        <f t="shared" si="65"/>
+        <f>AE107*AD8</f>
         <v>13.252295696069099</v>
       </c>
       <c r="AF124">
-        <f t="shared" si="65"/>
+        <f>AF107*AE8</f>
         <v>13.244618648179582</v>
       </c>
       <c r="AG124">
-        <f t="shared" si="65"/>
+        <f>AG107*AF8</f>
         <v>13.236928147855561</v>
       </c>
     </row>
-    <row r="125" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:33" ht="15.75">
       <c r="A125" s="3" t="s">
         <v>109</v>
       </c>
@@ -55740,131 +55730,131 @@
         <v>Passenger HDV</v>
       </c>
       <c r="C125">
-        <f t="shared" ref="C125:AG125" si="66">C108*B9</f>
+        <f>C108*B9</f>
         <v>66.77847192490951</v>
       </c>
       <c r="D125">
-        <f t="shared" si="66"/>
+        <f>D108*C9</f>
         <v>65.698337216983703</v>
       </c>
       <c r="E125">
-        <f t="shared" si="66"/>
+        <f>E108*D9</f>
         <v>64.643934355051599</v>
       </c>
       <c r="F125">
-        <f t="shared" si="66"/>
+        <f>F108*E9</f>
         <v>63.615540303918962</v>
       </c>
       <c r="G125">
-        <f t="shared" si="66"/>
+        <f>G108*F9</f>
         <v>62.613441476474875</v>
       </c>
       <c r="H125">
-        <f t="shared" si="66"/>
+        <f>H108*G9</f>
         <v>61.637934220390534</v>
       </c>
       <c r="I125">
-        <f t="shared" si="66"/>
+        <f>I108*H9</f>
         <v>60.768669924839998</v>
       </c>
       <c r="J125">
-        <f t="shared" si="66"/>
+        <f>J108*I9</f>
         <v>59.924125440277166</v>
       </c>
       <c r="K125">
-        <f t="shared" si="66"/>
+        <f>K108*J9</f>
         <v>59.104479507018965</v>
       </c>
       <c r="L125">
-        <f t="shared" si="66"/>
+        <f>L108*K9</f>
         <v>58.309916138310967</v>
       </c>
       <c r="M125">
-        <f t="shared" si="66"/>
+        <f>M108*L9</f>
         <v>57.540624843612832</v>
       </c>
       <c r="N125">
-        <f t="shared" si="66"/>
+        <f>N108*M9</f>
         <v>57.220318350386123</v>
       </c>
       <c r="O125">
-        <f t="shared" si="66"/>
+        <f>O108*N9</f>
         <v>56.920411431891537</v>
       </c>
       <c r="P125">
-        <f t="shared" si="66"/>
+        <f>P108*O9</f>
         <v>56.64128055751857</v>
       </c>
       <c r="Q125">
-        <f t="shared" si="66"/>
+        <f>Q108*P9</f>
         <v>56.38331041399546</v>
       </c>
       <c r="R125">
-        <f t="shared" si="66"/>
+        <f>R108*Q9</f>
         <v>56.146894152268189</v>
       </c>
       <c r="S125">
-        <f t="shared" si="66"/>
+        <f>S108*R9</f>
         <v>56.123988847070933</v>
       </c>
       <c r="T125">
-        <f t="shared" si="66"/>
+        <f>T108*S9</f>
         <v>56.101282914677171</v>
       </c>
       <c r="U125">
-        <f t="shared" si="66"/>
+        <f>U108*T9</f>
         <v>56.078774805635724</v>
       </c>
       <c r="V125">
-        <f t="shared" si="66"/>
+        <f>V108*U9</f>
         <v>56.056462976318642</v>
       </c>
       <c r="W125">
-        <f t="shared" si="66"/>
+        <f>W108*V9</f>
         <v>56.034345889197596</v>
       </c>
       <c r="X125">
-        <f t="shared" si="66"/>
+        <f>X108*W9</f>
         <v>55.999524746347383</v>
       </c>
       <c r="Y125">
-        <f t="shared" si="66"/>
+        <f>Y108*X9</f>
         <v>55.964740148598736</v>
       </c>
       <c r="Z125">
-        <f t="shared" si="66"/>
+        <f>Z108*Y9</f>
         <v>55.929948098641219</v>
       </c>
       <c r="AA125">
-        <f t="shared" si="66"/>
+        <f>AA108*Z9</f>
         <v>55.895148966243923</v>
       </c>
       <c r="AB125">
-        <f t="shared" si="66"/>
+        <f>AB108*AA9</f>
         <v>55.860343125505089</v>
       </c>
       <c r="AC125">
-        <f t="shared" si="66"/>
+        <f>AC108*AB9</f>
         <v>55.839158376943026</v>
       </c>
       <c r="AD125">
-        <f t="shared" si="66"/>
+        <f>AD108*AC9</f>
         <v>55.817974770549284</v>
       </c>
       <c r="AE125">
-        <f t="shared" si="66"/>
+        <f>AE108*AD9</f>
         <v>55.796792408720862</v>
       </c>
       <c r="AF125">
-        <f t="shared" si="66"/>
+        <f>AF108*AE9</f>
         <v>55.775611395121274</v>
       </c>
       <c r="AG125">
-        <f t="shared" si="66"/>
+        <f>AG108*AF9</f>
         <v>55.754431834656017</v>
       </c>
     </row>
-    <row r="126" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:33" ht="15.75">
       <c r="A126" s="3" t="s">
         <v>110</v>
       </c>
@@ -55873,131 +55863,131 @@
         <v>Passenger HDV</v>
       </c>
       <c r="C126">
-        <f t="shared" ref="C126:AG126" si="67">C109*B10</f>
+        <f>C109*B10</f>
         <v>49.8257686669794</v>
       </c>
       <c r="D126">
-        <f t="shared" si="67"/>
+        <f>D109*C10</f>
         <v>49.620049400820548</v>
       </c>
       <c r="E126">
-        <f t="shared" si="67"/>
+        <f>E109*D10</f>
         <v>49.411296648755588</v>
       </c>
       <c r="F126">
-        <f t="shared" si="67"/>
+        <f>F109*E10</f>
         <v>49.199478606171169</v>
       </c>
       <c r="G126">
-        <f t="shared" si="67"/>
+        <f>G109*F10</f>
         <v>48.984562264382674</v>
       </c>
       <c r="H126">
-        <f t="shared" si="67"/>
+        <f>H109*G10</f>
         <v>48.766513351694549</v>
       </c>
       <c r="I126">
-        <f t="shared" si="67"/>
+        <f>I109*H10</f>
         <v>48.49801524069445</v>
       </c>
       <c r="J126">
-        <f t="shared" si="67"/>
+        <f>J109*I10</f>
         <v>48.227259135956352</v>
       </c>
       <c r="K126">
-        <f t="shared" si="67"/>
+        <f>K109*J10</f>
         <v>47.954225091993365</v>
       </c>
       <c r="L126">
-        <f t="shared" si="67"/>
+        <f>L109*K10</f>
         <v>47.678892562158303</v>
       </c>
       <c r="M126">
-        <f t="shared" si="67"/>
+        <f>M109*L10</f>
         <v>47.40124037315752</v>
       </c>
       <c r="N126">
-        <f t="shared" si="67"/>
+        <f>N109*M10</f>
         <v>47.42510311242193</v>
       </c>
       <c r="O126">
-        <f t="shared" si="67"/>
+        <f>O109*N10</f>
         <v>47.446349150481382</v>
       </c>
       <c r="P126">
-        <f t="shared" si="67"/>
+        <f>P109*O10</f>
         <v>47.464934844092255</v>
       </c>
       <c r="Q126">
-        <f t="shared" si="67"/>
+        <f>Q109*P10</f>
         <v>47.480815531736489</v>
       </c>
       <c r="R126">
-        <f t="shared" si="67"/>
+        <f>R109*Q10</f>
         <v>47.493945504240862</v>
       </c>
       <c r="S126">
-        <f t="shared" si="67"/>
+        <f>S109*R10</f>
         <v>47.471306752856272</v>
       </c>
       <c r="T126">
-        <f t="shared" si="67"/>
+        <f>T109*S10</f>
         <v>47.448675287057071</v>
       </c>
       <c r="U126">
-        <f t="shared" si="67"/>
+        <f>U109*T10</f>
         <v>47.42605243545448</v>
       </c>
       <c r="V126">
-        <f t="shared" si="67"/>
+        <f>V109*U10</f>
         <v>47.403439492019949</v>
       </c>
       <c r="W126">
-        <f t="shared" si="67"/>
+        <f>W109*V10</f>
         <v>47.38083771693028</v>
       </c>
       <c r="X126">
-        <f t="shared" si="67"/>
+        <f>X109*W10</f>
         <v>47.382830918529777</v>
       </c>
       <c r="Y126">
-        <f t="shared" si="67"/>
+        <f>Y109*X10</f>
         <v>47.384832103424628</v>
       </c>
       <c r="Z126">
-        <f t="shared" si="67"/>
+        <f>Z109*Y10</f>
         <v>47.386823134775902</v>
       </c>
       <c r="AA126">
-        <f t="shared" si="67"/>
+        <f>AA109*Z10</f>
         <v>47.38880395808264</v>
       </c>
       <c r="AB126">
-        <f t="shared" si="67"/>
+        <f>AB109*AA10</f>
         <v>47.390774518029964</v>
       </c>
       <c r="AC126">
-        <f t="shared" si="67"/>
+        <f>AC109*AB10</f>
         <v>47.396065470946724</v>
       </c>
       <c r="AD126">
-        <f t="shared" si="67"/>
+        <f>AD109*AC10</f>
         <v>47.401360125855383</v>
       </c>
       <c r="AE126">
-        <f t="shared" si="67"/>
+        <f>AE109*AD10</f>
         <v>47.40665847757738</v>
       </c>
       <c r="AF126">
-        <f t="shared" si="67"/>
+        <f>AF109*AE10</f>
         <v>47.411960520724897</v>
       </c>
       <c r="AG126">
-        <f t="shared" si="67"/>
+        <f>AG109*AF10</f>
         <v>47.417266249708035</v>
       </c>
     </row>
-    <row r="127" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:33" ht="15.75">
       <c r="A127" s="3" t="s">
         <v>111</v>
       </c>
@@ -56006,134 +55996,134 @@
         <v>Passenger HDV</v>
       </c>
       <c r="C127">
-        <f t="shared" ref="C127:AG127" si="68">C110*B11</f>
+        <f>C110*B11</f>
         <v>315.94377106041452</v>
       </c>
       <c r="D127">
-        <f t="shared" si="68"/>
+        <f>D110*C11</f>
         <v>315.37492009739714</v>
       </c>
       <c r="E127">
-        <f t="shared" si="68"/>
+        <f>E110*D11</f>
         <v>314.77736648371416</v>
       </c>
       <c r="F127">
-        <f t="shared" si="68"/>
+        <f>F110*E11</f>
         <v>314.15083090848896</v>
       </c>
       <c r="G127">
-        <f t="shared" si="68"/>
+        <f>G110*F11</f>
         <v>313.49502547761267</v>
       </c>
       <c r="H127">
-        <f t="shared" si="68"/>
+        <f>H110*G11</f>
         <v>312.80965325138862</v>
       </c>
       <c r="I127">
-        <f t="shared" si="68"/>
+        <f>I110*H11</f>
         <v>311.95557577314037</v>
       </c>
       <c r="J127">
-        <f t="shared" si="68"/>
+        <f>J110*I11</f>
         <v>311.07392228968484</v>
       </c>
       <c r="K127">
-        <f t="shared" si="68"/>
+        <f>K110*J11</f>
         <v>310.16452049616777</v>
       </c>
       <c r="L127">
-        <f t="shared" si="68"/>
+        <f>L110*K11</f>
         <v>309.22719314458249</v>
       </c>
       <c r="M127">
-        <f t="shared" si="68"/>
+        <f>M110*L11</f>
         <v>308.2617578344562</v>
       </c>
       <c r="N127">
-        <f t="shared" si="68"/>
+        <f>N110*M11</f>
         <v>308.72999503672645</v>
       </c>
       <c r="O127">
-        <f t="shared" si="68"/>
+        <f>O110*N11</f>
         <v>309.18077240665434</v>
       </c>
       <c r="P127">
-        <f t="shared" si="68"/>
+        <f>P110*O11</f>
         <v>309.61374360333713</v>
       </c>
       <c r="Q127">
-        <f t="shared" si="68"/>
+        <f>Q110*P11</f>
         <v>310.02855508818931</v>
       </c>
       <c r="R127">
-        <f t="shared" si="68"/>
+        <f>R110*Q11</f>
         <v>310.42484590174865</v>
       </c>
       <c r="S127">
-        <f t="shared" si="68"/>
+        <f>S110*R11</f>
         <v>310.37578447586145</v>
       </c>
       <c r="T127">
-        <f t="shared" si="68"/>
+        <f>T110*S11</f>
         <v>310.32759346967816</v>
       </c>
       <c r="U127">
-        <f t="shared" si="68"/>
+        <f>U110*T11</f>
         <v>310.28025984638532</v>
       </c>
       <c r="V127">
-        <f t="shared" si="68"/>
+        <f>V110*U11</f>
         <v>310.23377077450999</v>
       </c>
       <c r="W127">
-        <f t="shared" si="68"/>
+        <f>W110*V11</f>
         <v>310.18811362446206</v>
       </c>
       <c r="X127">
-        <f t="shared" si="68"/>
+        <f>X110*W11</f>
         <v>310.05474720473188</v>
       </c>
       <c r="Y127">
-        <f t="shared" si="68"/>
+        <f>Y110*X11</f>
         <v>309.92081663414712</v>
       </c>
       <c r="Z127">
-        <f t="shared" si="68"/>
+        <f>Z110*Y11</f>
         <v>309.78644820620997</v>
       </c>
       <c r="AA127">
-        <f t="shared" si="68"/>
+        <f>AA110*Z11</f>
         <v>309.65164030795989</v>
       </c>
       <c r="AB127">
-        <f t="shared" si="68"/>
+        <f>AB110*AA11</f>
         <v>309.51639131556806</v>
       </c>
       <c r="AC127">
-        <f t="shared" si="68"/>
+        <f>AC110*AB11</f>
         <v>309.57124527403232</v>
       </c>
       <c r="AD127">
-        <f t="shared" si="68"/>
+        <f>AD110*AC11</f>
         <v>309.62615861796769</v>
       </c>
       <c r="AE127">
-        <f t="shared" si="68"/>
+        <f>AE110*AD11</f>
         <v>309.68113140048519</v>
       </c>
       <c r="AF127">
-        <f t="shared" si="68"/>
+        <f>AF110*AE11</f>
         <v>309.7361636734779</v>
       </c>
       <c r="AG127">
-        <f t="shared" si="68"/>
+        <f>AG110*AF11</f>
         <v>309.79125548766564</v>
       </c>
     </row>
-    <row r="128" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:33">
       <c r="A128" s="2"/>
     </row>
-    <row r="129" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:33" ht="15.75">
       <c r="A129" s="2" t="s">
         <v>170</v>
       </c>
@@ -56231,394 +56221,394 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="130" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:33">
       <c r="A130" s="3" t="s">
         <v>119</v>
       </c>
       <c r="C130" s="83">
-        <f t="shared" ref="C130:L132" si="69">SUMIFS(C$117:C$127,$B$117:$B$127,$A130)</f>
+        <f>SUMIFS(C$117:C$127,$B$117:$B$127,$A130)</f>
         <v>122.95576366291621</v>
       </c>
       <c r="D130" s="83">
-        <f t="shared" si="69"/>
+        <f>SUMIFS(D$117:D$127,$B$117:$B$127,$A130)</f>
         <v>120.56036236212623</v>
       </c>
       <c r="E130" s="83">
-        <f t="shared" si="69"/>
+        <f>SUMIFS(E$117:E$127,$B$117:$B$127,$A130)</f>
         <v>118.43090034085387</v>
       </c>
       <c r="F130" s="83">
-        <f t="shared" si="69"/>
+        <f>SUMIFS(F$117:F$127,$B$117:$B$127,$A130)</f>
         <v>116.24483968968724</v>
       </c>
       <c r="G130" s="83">
-        <f t="shared" si="69"/>
+        <f>SUMIFS(G$117:G$127,$B$117:$B$127,$A130)</f>
         <v>114.04041740132254</v>
       </c>
       <c r="H130" s="83">
-        <f t="shared" si="69"/>
+        <f>SUMIFS(H$117:H$127,$B$117:$B$127,$A130)</f>
         <v>111.80420549981139</v>
       </c>
       <c r="I130" s="83">
-        <f t="shared" si="69"/>
+        <f>SUMIFS(I$117:I$127,$B$117:$B$127,$A130)</f>
         <v>109.4645641110977</v>
       </c>
       <c r="J130" s="83">
-        <f t="shared" si="69"/>
+        <f>SUMIFS(J$117:J$127,$B$117:$B$127,$A130)</f>
         <v>107.15422667552413</v>
       </c>
       <c r="K130" s="83">
-        <f t="shared" si="69"/>
+        <f>SUMIFS(K$117:K$127,$B$117:$B$127,$A130)</f>
         <v>104.87279732212798</v>
       </c>
       <c r="L130" s="83">
-        <f t="shared" si="69"/>
+        <f>SUMIFS(L$117:L$127,$B$117:$B$127,$A130)</f>
         <v>102.61528922250253</v>
       </c>
       <c r="M130" s="83">
-        <f t="shared" ref="M130:V132" si="70">SUMIFS(M$117:M$127,$B$117:$B$127,$A130)</f>
+        <f>SUMIFS(M$117:M$127,$B$117:$B$127,$A130)</f>
         <v>100.36276426574412</v>
       </c>
       <c r="N130" s="83">
-        <f t="shared" si="70"/>
+        <f>SUMIFS(N$117:N$127,$B$117:$B$127,$A130)</f>
         <v>100.67930358124943</v>
       </c>
       <c r="O130" s="83">
-        <f t="shared" si="70"/>
+        <f>SUMIFS(O$117:O$127,$B$117:$B$127,$A130)</f>
         <v>101.0095981821494</v>
       </c>
       <c r="P130" s="83">
-        <f t="shared" si="70"/>
+        <f>SUMIFS(P$117:P$127,$B$117:$B$127,$A130)</f>
         <v>101.33086148533251</v>
       </c>
       <c r="Q130" s="83">
-        <f t="shared" si="70"/>
+        <f>SUMIFS(Q$117:Q$127,$B$117:$B$127,$A130)</f>
         <v>101.64516875755893</v>
       </c>
       <c r="R130" s="83">
-        <f t="shared" si="70"/>
+        <f>SUMIFS(R$117:R$127,$B$117:$B$127,$A130)</f>
         <v>101.95894492385507</v>
       </c>
       <c r="S130" s="83">
-        <f t="shared" si="70"/>
+        <f>SUMIFS(S$117:S$127,$B$117:$B$127,$A130)</f>
         <v>102.24922758615378</v>
       </c>
       <c r="T130" s="83">
-        <f t="shared" si="70"/>
+        <f>SUMIFS(T$117:T$127,$B$117:$B$127,$A130)</f>
         <v>102.54503053685337</v>
       </c>
       <c r="U130" s="83">
-        <f t="shared" si="70"/>
+        <f>SUMIFS(U$117:U$127,$B$117:$B$127,$A130)</f>
         <v>102.82347909240374</v>
       </c>
       <c r="V130" s="83">
-        <f t="shared" si="70"/>
+        <f>SUMIFS(V$117:V$127,$B$117:$B$127,$A130)</f>
         <v>103.1303149110619</v>
       </c>
       <c r="W130" s="83">
-        <f t="shared" ref="W130:AG132" si="71">SUMIFS(W$117:W$127,$B$117:$B$127,$A130)</f>
+        <f>SUMIFS(W$117:W$127,$B$117:$B$127,$A130)</f>
         <v>103.44241082516075</v>
       </c>
       <c r="X130" s="83">
-        <f t="shared" si="71"/>
+        <f>SUMIFS(X$117:X$127,$B$117:$B$127,$A130)</f>
         <v>103.76748457641942</v>
       </c>
       <c r="Y130" s="83">
-        <f t="shared" si="71"/>
+        <f>SUMIFS(Y$117:Y$127,$B$117:$B$127,$A130)</f>
         <v>104.08910754909668</v>
       </c>
       <c r="Z130" s="83">
-        <f t="shared" si="71"/>
+        <f>SUMIFS(Z$117:Z$127,$B$117:$B$127,$A130)</f>
         <v>104.41481064992269</v>
       </c>
       <c r="AA130" s="83">
-        <f t="shared" si="71"/>
+        <f>SUMIFS(AA$117:AA$127,$B$117:$B$127,$A130)</f>
         <v>104.74106215044711</v>
       </c>
       <c r="AB130" s="83">
-        <f t="shared" si="71"/>
+        <f>SUMIFS(AB$117:AB$127,$B$117:$B$127,$A130)</f>
         <v>105.06195136390443</v>
       </c>
       <c r="AC130" s="83">
-        <f t="shared" si="71"/>
+        <f>SUMIFS(AC$117:AC$127,$B$117:$B$127,$A130)</f>
         <v>105.36473398871115</v>
       </c>
       <c r="AD130" s="83">
-        <f t="shared" si="71"/>
+        <f>SUMIFS(AD$117:AD$127,$B$117:$B$127,$A130)</f>
         <v>105.66793138702464</v>
       </c>
       <c r="AE130" s="83">
-        <f t="shared" si="71"/>
+        <f>SUMIFS(AE$117:AE$127,$B$117:$B$127,$A130)</f>
         <v>105.96879436012651</v>
       </c>
       <c r="AF130" s="83">
-        <f t="shared" si="71"/>
+        <f>SUMIFS(AF$117:AF$127,$B$117:$B$127,$A130)</f>
         <v>106.26627864523388</v>
       </c>
       <c r="AG130" s="83">
-        <f t="shared" si="71"/>
+        <f>SUMIFS(AG$117:AG$127,$B$117:$B$127,$A130)</f>
         <v>106.55599296106729</v>
       </c>
     </row>
-    <row r="131" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:33">
       <c r="A131" s="3" t="s">
         <v>117</v>
       </c>
       <c r="C131" s="83">
-        <f t="shared" si="69"/>
+        <f>SUMIFS(C$117:C$127,$B$117:$B$127,$A131)</f>
         <v>865.92240714375305</v>
       </c>
       <c r="D131" s="83">
-        <f t="shared" si="69"/>
+        <f>SUMIFS(D$117:D$127,$B$117:$B$127,$A131)</f>
         <v>836.8606372886702</v>
       </c>
       <c r="E131" s="83">
-        <f t="shared" si="69"/>
+        <f>SUMIFS(E$117:E$127,$B$117:$B$127,$A131)</f>
         <v>807.57158584177023</v>
       </c>
       <c r="F131" s="83">
-        <f t="shared" si="69"/>
+        <f>SUMIFS(F$117:F$127,$B$117:$B$127,$A131)</f>
         <v>778.39077391707087</v>
       </c>
       <c r="G131" s="83">
-        <f t="shared" si="69"/>
+        <f>SUMIFS(G$117:G$127,$B$117:$B$127,$A131)</f>
         <v>749.29320671395431</v>
       </c>
       <c r="H131" s="83">
-        <f t="shared" si="69"/>
+        <f>SUMIFS(H$117:H$127,$B$117:$B$127,$A131)</f>
         <v>720.30570604635352</v>
       </c>
       <c r="I131" s="83">
-        <f t="shared" si="69"/>
+        <f>SUMIFS(I$117:I$127,$B$117:$B$127,$A131)</f>
         <v>692.098697622955</v>
       </c>
       <c r="J131" s="83">
-        <f t="shared" si="69"/>
+        <f>SUMIFS(J$117:J$127,$B$117:$B$127,$A131)</f>
         <v>663.95003841403718</v>
       </c>
       <c r="K131" s="83">
-        <f t="shared" si="69"/>
+        <f>SUMIFS(K$117:K$127,$B$117:$B$127,$A131)</f>
         <v>635.86500189981871</v>
       </c>
       <c r="L131" s="83">
-        <f t="shared" si="69"/>
+        <f>SUMIFS(L$117:L$127,$B$117:$B$127,$A131)</f>
         <v>607.85334236346625</v>
       </c>
       <c r="M131" s="83">
-        <f t="shared" si="70"/>
+        <f>SUMIFS(M$117:M$127,$B$117:$B$127,$A131)</f>
         <v>579.93863044745774</v>
       </c>
       <c r="N131" s="83">
-        <f t="shared" si="70"/>
+        <f>SUMIFS(N$117:N$127,$B$117:$B$127,$A131)</f>
         <v>578.65418407643324</v>
       </c>
       <c r="O131" s="83">
-        <f t="shared" si="70"/>
+        <f>SUMIFS(O$117:O$127,$B$117:$B$127,$A131)</f>
         <v>577.36801708575786</v>
       </c>
       <c r="P131" s="83">
-        <f t="shared" si="70"/>
+        <f>SUMIFS(P$117:P$127,$B$117:$B$127,$A131)</f>
         <v>576.10293448200434</v>
       </c>
       <c r="Q131" s="83">
-        <f t="shared" si="70"/>
+        <f>SUMIFS(Q$117:Q$127,$B$117:$B$127,$A131)</f>
         <v>574.85687507189675</v>
       </c>
       <c r="R131" s="83">
-        <f t="shared" si="70"/>
+        <f>SUMIFS(R$117:R$127,$B$117:$B$127,$A131)</f>
         <v>573.62342368213444</v>
       </c>
       <c r="S131" s="83">
-        <f t="shared" si="70"/>
+        <f>SUMIFS(S$117:S$127,$B$117:$B$127,$A131)</f>
         <v>572.59510911450673</v>
       </c>
       <c r="T131" s="83">
-        <f t="shared" si="70"/>
+        <f>SUMIFS(T$117:T$127,$B$117:$B$127,$A131)</f>
         <v>571.57437973493927</v>
       </c>
       <c r="U131" s="83">
-        <f t="shared" si="70"/>
+        <f>SUMIFS(U$117:U$127,$B$117:$B$127,$A131)</f>
         <v>570.58386815344591</v>
       </c>
       <c r="V131" s="83">
-        <f t="shared" si="70"/>
+        <f>SUMIFS(V$117:V$127,$B$117:$B$127,$A131)</f>
         <v>569.57759519317869</v>
       </c>
       <c r="W131" s="83">
-        <f t="shared" si="71"/>
+        <f>SUMIFS(W$117:W$127,$B$117:$B$127,$A131)</f>
         <v>568.57845498231973</v>
       </c>
       <c r="X131" s="83">
-        <f t="shared" si="71"/>
+        <f>SUMIFS(X$117:X$127,$B$117:$B$127,$A131)</f>
         <v>567.63957028785148</v>
       </c>
       <c r="Y131" s="83">
-        <f t="shared" si="71"/>
+        <f>SUMIFS(Y$117:Y$127,$B$117:$B$127,$A131)</f>
         <v>566.73200951744025</v>
       </c>
       <c r="Z131" s="83">
-        <f t="shared" si="71"/>
+        <f>SUMIFS(Z$117:Z$127,$B$117:$B$127,$A131)</f>
         <v>565.83210767669846</v>
       </c>
       <c r="AA131" s="83">
-        <f t="shared" si="71"/>
+        <f>SUMIFS(AA$117:AA$127,$B$117:$B$127,$A131)</f>
         <v>564.94312170642695</v>
       </c>
       <c r="AB131" s="83">
-        <f t="shared" si="71"/>
+        <f>SUMIFS(AB$117:AB$127,$B$117:$B$127,$A131)</f>
         <v>564.07069603458376</v>
       </c>
       <c r="AC131" s="83">
-        <f t="shared" si="71"/>
+        <f>SUMIFS(AC$117:AC$127,$B$117:$B$127,$A131)</f>
         <v>563.29956713258571</v>
       </c>
       <c r="AD131" s="83">
-        <f t="shared" si="71"/>
+        <f>SUMIFS(AD$117:AD$127,$B$117:$B$127,$A131)</f>
         <v>562.53796694915548</v>
       </c>
       <c r="AE131" s="83">
-        <f t="shared" si="71"/>
+        <f>SUMIFS(AE$117:AE$127,$B$117:$B$127,$A131)</f>
         <v>561.78838395390119</v>
       </c>
       <c r="AF131" s="83">
-        <f t="shared" si="71"/>
+        <f>SUMIFS(AF$117:AF$127,$B$117:$B$127,$A131)</f>
         <v>561.05161011159805</v>
       </c>
       <c r="AG131" s="83">
-        <f t="shared" si="71"/>
+        <f>SUMIFS(AG$117:AG$127,$B$117:$B$127,$A131)</f>
         <v>560.33179250998364</v>
       </c>
     </row>
-    <row r="132" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:33">
       <c r="A132" s="3" t="s">
         <v>118</v>
       </c>
       <c r="C132" s="83">
-        <f t="shared" si="69"/>
+        <f>SUMIFS(C$117:C$127,$B$117:$B$127,$A132)</f>
         <v>446.76120003515064</v>
       </c>
       <c r="D132" s="83">
-        <f t="shared" si="69"/>
+        <f>SUMIFS(D$117:D$127,$B$117:$B$127,$A132)</f>
         <v>444.77134979664311</v>
       </c>
       <c r="E132" s="83">
-        <f t="shared" si="69"/>
+        <f>SUMIFS(E$117:E$127,$B$117:$B$127,$A132)</f>
         <v>442.77571153955955</v>
       </c>
       <c r="F132" s="83">
-        <f t="shared" si="69"/>
+        <f>SUMIFS(F$117:F$127,$B$117:$B$127,$A132)</f>
         <v>440.77424752437662</v>
       </c>
       <c r="G132" s="83">
-        <f t="shared" si="69"/>
+        <f>SUMIFS(G$117:G$127,$B$117:$B$127,$A132)</f>
         <v>438.76691946139834</v>
       </c>
       <c r="H132" s="83">
-        <f t="shared" si="69"/>
+        <f>SUMIFS(H$117:H$127,$B$117:$B$127,$A132)</f>
         <v>436.75368846681636</v>
       </c>
       <c r="I132" s="83">
-        <f t="shared" si="69"/>
+        <f>SUMIFS(I$117:I$127,$B$117:$B$127,$A132)</f>
         <v>434.66280235104773</v>
       </c>
       <c r="J132" s="83">
-        <f t="shared" si="69"/>
+        <f>SUMIFS(J$117:J$127,$B$117:$B$127,$A132)</f>
         <v>432.56659283227418</v>
       </c>
       <c r="K132" s="83">
-        <f t="shared" si="69"/>
+        <f>SUMIFS(K$117:K$127,$B$117:$B$127,$A132)</f>
         <v>430.46504197578145</v>
       </c>
       <c r="L132" s="83">
-        <f t="shared" si="69"/>
+        <f>SUMIFS(L$117:L$127,$B$117:$B$127,$A132)</f>
         <v>428.35813142570919</v>
       </c>
       <c r="M132" s="83">
-        <f t="shared" si="70"/>
+        <f>SUMIFS(M$117:M$127,$B$117:$B$127,$A132)</f>
         <v>426.2458423872099</v>
       </c>
       <c r="N132" s="83">
-        <f t="shared" si="70"/>
+        <f>SUMIFS(N$117:N$127,$B$117:$B$127,$A132)</f>
         <v>426.40398954161503</v>
       </c>
       <c r="O132" s="83">
-        <f t="shared" si="70"/>
+        <f>SUMIFS(O$117:O$127,$B$117:$B$127,$A132)</f>
         <v>426.56186175007042</v>
       </c>
       <c r="P132" s="83">
-        <f t="shared" si="70"/>
+        <f>SUMIFS(P$117:P$127,$B$117:$B$127,$A132)</f>
         <v>426.7194356493352</v>
       </c>
       <c r="Q132" s="83">
-        <f t="shared" si="70"/>
+        <f>SUMIFS(Q$117:Q$127,$B$117:$B$127,$A132)</f>
         <v>426.87668764203397</v>
       </c>
       <c r="R132" s="83">
-        <f t="shared" si="70"/>
+        <f>SUMIFS(R$117:R$127,$B$117:$B$127,$A132)</f>
         <v>427.0335938843121</v>
       </c>
       <c r="S132" s="83">
-        <f t="shared" si="70"/>
+        <f>SUMIFS(S$117:S$127,$B$117:$B$127,$A132)</f>
         <v>426.96898445891748</v>
       </c>
       <c r="T132" s="83">
-        <f t="shared" si="70"/>
+        <f>SUMIFS(T$117:T$127,$B$117:$B$127,$A132)</f>
         <v>426.90523896892978</v>
       </c>
       <c r="U132" s="83">
-        <f t="shared" si="70"/>
+        <f>SUMIFS(U$117:U$127,$B$117:$B$127,$A132)</f>
         <v>426.84234600356302</v>
       </c>
       <c r="V132" s="83">
-        <f t="shared" si="70"/>
+        <f>SUMIFS(V$117:V$127,$B$117:$B$127,$A132)</f>
         <v>426.78029431360369</v>
       </c>
       <c r="W132" s="83">
-        <f t="shared" si="71"/>
+        <f>SUMIFS(W$117:W$127,$B$117:$B$127,$A132)</f>
         <v>426.71907280905123</v>
       </c>
       <c r="X132" s="83">
-        <f t="shared" si="71"/>
+        <f>SUMIFS(X$117:X$127,$B$117:$B$127,$A132)</f>
         <v>426.58460011554439</v>
       </c>
       <c r="Y132" s="83">
-        <f t="shared" si="71"/>
+        <f>SUMIFS(Y$117:Y$127,$B$117:$B$127,$A132)</f>
         <v>426.44969311755318</v>
       </c>
       <c r="Z132" s="83">
-        <f t="shared" si="71"/>
+        <f>SUMIFS(Z$117:Z$127,$B$117:$B$127,$A132)</f>
         <v>426.31441738493851</v>
       </c>
       <c r="AA132" s="83">
-        <f t="shared" si="71"/>
+        <f>SUMIFS(AA$117:AA$127,$B$117:$B$127,$A132)</f>
         <v>426.17877184469273</v>
       </c>
       <c r="AB132" s="83">
-        <f t="shared" si="71"/>
+        <f>SUMIFS(AB$117:AB$127,$B$117:$B$127,$A132)</f>
         <v>426.04275541777645</v>
       </c>
       <c r="AC132" s="83">
-        <f t="shared" si="71"/>
+        <f>SUMIFS(AC$117:AC$127,$B$117:$B$127,$A132)</f>
         <v>426.07407868986945</v>
       </c>
       <c r="AD132" s="83">
-        <f t="shared" si="71"/>
+        <f>SUMIFS(AD$117:AD$127,$B$117:$B$127,$A132)</f>
         <v>426.10545283924421</v>
       </c>
       <c r="AE132" s="83">
-        <f t="shared" si="71"/>
+        <f>SUMIFS(AE$117:AE$127,$B$117:$B$127,$A132)</f>
         <v>426.13687798285252</v>
       </c>
       <c r="AF132" s="83">
-        <f t="shared" si="71"/>
+        <f>SUMIFS(AF$117:AF$127,$B$117:$B$127,$A132)</f>
         <v>426.16835423750365</v>
       </c>
       <c r="AG132" s="83">
-        <f t="shared" si="71"/>
+        <f>SUMIFS(AG$117:AG$127,$B$117:$B$127,$A132)</f>
         <v>426.19988171988524</v>
       </c>
     </row>
-    <row r="134" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:33" ht="15.75">
       <c r="A134" s="2" t="s">
         <v>171</v>
       </c>
@@ -56716,7 +56706,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="135" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:33">
       <c r="A135" s="3" t="s">
         <v>119</v>
       </c>
@@ -56728,123 +56718,123 @@
         <v>1.9481813860771857E-2</v>
       </c>
       <c r="E135" s="82">
-        <f t="shared" ref="E135:AG137" si="72">1-(E130/D130)</f>
+        <f t="shared" ref="E135:AG137" si="60">1-(E130/D130)</f>
         <v>1.7663036005782007E-2</v>
       </c>
       <c r="F135" s="82">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>1.8458532738288458E-2</v>
       </c>
       <c r="G135" s="82">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>1.89636141634274E-2</v>
       </c>
       <c r="H135" s="82">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>1.9608941745992037E-2</v>
       </c>
       <c r="I135" s="82">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>2.0926237776607071E-2</v>
       </c>
       <c r="J135" s="82">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>2.1105802177486144E-2</v>
       </c>
       <c r="K135" s="82">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>2.1291081315015115E-2</v>
       </c>
       <c r="L135" s="82">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>2.1526155087589371E-2</v>
       </c>
       <c r="M135" s="82">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>2.1951163163163923E-2</v>
       </c>
       <c r="N135" s="82">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>-3.153951745162864E-3</v>
       </c>
       <c r="O135" s="82">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>-3.2806603656472255E-3</v>
       </c>
       <c r="P135" s="82">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>-3.1805225341434706E-3</v>
       </c>
       <c r="Q135" s="82">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>-3.1017921649854063E-3</v>
       </c>
       <c r="R135" s="82">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>-3.0869757031399825E-3</v>
       </c>
       <c r="S135" s="82">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>-2.8470543954284278E-3</v>
       </c>
       <c r="T135" s="82">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>-2.8929602470626481E-3</v>
       </c>
       <c r="U135" s="82">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>-2.7153783473718995E-3</v>
       </c>
       <c r="V135" s="82">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>-2.9841026715544672E-3</v>
       </c>
       <c r="W135" s="82">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>-3.0262286541837824E-3</v>
       </c>
       <c r="X135" s="82">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>-3.1425577639341284E-3</v>
       </c>
       <c r="Y135" s="82">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>-3.0994581201435611E-3</v>
       </c>
       <c r="Z135" s="82">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>-3.1290795789786774E-3</v>
       </c>
       <c r="AA135" s="82">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>-3.1245711072374061E-3</v>
       </c>
       <c r="AB135" s="82">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>-3.063642919683307E-3</v>
       </c>
       <c r="AC135" s="82">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>-2.8819436615827865E-3</v>
       </c>
       <c r="AD135" s="82">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>-2.8775984794491283E-3</v>
       </c>
       <c r="AE135" s="82">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>-2.8472495784923613E-3</v>
       </c>
       <c r="AF135" s="82">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>-2.8072819635598378E-3</v>
       </c>
       <c r="AG135" s="82">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>-2.7263052731958393E-3</v>
       </c>
     </row>
-    <row r="136" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:33">
       <c r="A136" s="3" t="s">
         <v>117</v>
       </c>
@@ -56852,127 +56842,127 @@
         <v>0</v>
       </c>
       <c r="D136" s="82">
-        <f t="shared" ref="D136:S137" si="73">1-(D131/C131)</f>
+        <f t="shared" ref="D136:S137" si="61">1-(D131/C131)</f>
         <v>3.356163279218416E-2</v>
       </c>
       <c r="E136" s="82">
-        <f t="shared" si="73"/>
+        <f t="shared" si="61"/>
         <v>3.4998720386458904E-2</v>
       </c>
       <c r="F136" s="82">
-        <f t="shared" si="73"/>
+        <f t="shared" si="61"/>
         <v>3.6134025065137521E-2</v>
       </c>
       <c r="G136" s="82">
-        <f t="shared" si="73"/>
+        <f t="shared" si="61"/>
         <v>3.738169590151974E-2</v>
       </c>
       <c r="H136" s="82">
-        <f t="shared" si="73"/>
+        <f t="shared" si="61"/>
         <v>3.8686458662459011E-2</v>
       </c>
       <c r="I136" s="82">
-        <f t="shared" si="73"/>
+        <f t="shared" si="61"/>
         <v>3.9159773671962772E-2</v>
       </c>
       <c r="J136" s="82">
-        <f t="shared" si="73"/>
+        <f t="shared" si="61"/>
         <v>4.0671452360184546E-2</v>
       </c>
       <c r="K136" s="82">
-        <f t="shared" si="73"/>
+        <f t="shared" si="61"/>
         <v>4.2299924526406518E-2</v>
       </c>
       <c r="L136" s="82">
-        <f t="shared" si="73"/>
+        <f t="shared" si="61"/>
         <v>4.4052840544235083E-2</v>
       </c>
       <c r="M136" s="82">
-        <f t="shared" si="73"/>
+        <f t="shared" si="61"/>
         <v>4.5923432463939484E-2</v>
       </c>
       <c r="N136" s="82">
-        <f t="shared" si="73"/>
+        <f t="shared" si="61"/>
         <v>2.2147970553944019E-3</v>
       </c>
       <c r="O136" s="82">
-        <f t="shared" si="73"/>
+        <f t="shared" si="61"/>
         <v>2.2226867550058094E-3</v>
       </c>
       <c r="P136" s="82">
-        <f t="shared" si="73"/>
+        <f t="shared" si="61"/>
         <v>2.1911199898791978E-3</v>
       </c>
       <c r="Q136" s="82">
-        <f t="shared" si="73"/>
+        <f t="shared" si="61"/>
         <v>2.162911062461359E-3</v>
       </c>
       <c r="R136" s="82">
-        <f t="shared" si="73"/>
+        <f t="shared" si="61"/>
         <v>2.1456669359796177E-3</v>
       </c>
       <c r="S136" s="82">
-        <f t="shared" si="73"/>
+        <f t="shared" si="61"/>
         <v>1.7926648828718861E-3</v>
       </c>
       <c r="T136" s="82">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>1.7826372655295186E-3</v>
       </c>
       <c r="U136" s="82">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>1.7329530794447656E-3</v>
       </c>
       <c r="V136" s="82">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>1.7635846655177367E-3</v>
       </c>
       <c r="W136" s="82">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>1.754177515567612E-3</v>
       </c>
       <c r="X136" s="82">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>1.6512843324276716E-3</v>
       </c>
       <c r="Y136" s="82">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>1.5988328120800643E-3</v>
       </c>
       <c r="Z136" s="82">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>1.5878789721230913E-3</v>
       </c>
       <c r="AA136" s="82">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>1.5711126290123278E-3</v>
       </c>
       <c r="AB136" s="82">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>1.5442716944813473E-3</v>
       </c>
       <c r="AC136" s="82">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>1.3670784662616065E-3</v>
       </c>
       <c r="AD136" s="82">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>1.3520340292592081E-3</v>
       </c>
       <c r="AE136" s="82">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>1.3325020519406872E-3</v>
       </c>
       <c r="AF136" s="82">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>1.3114793102656508E-3</v>
       </c>
       <c r="AG136" s="82">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>1.2829792993040989E-3</v>
       </c>
     </row>
-    <row r="137" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:33">
       <c r="A137" s="3" t="s">
         <v>118</v>
       </c>
@@ -56980,123 +56970,123 @@
         <v>0</v>
       </c>
       <c r="D137" s="82">
-        <f t="shared" si="73"/>
+        <f t="shared" si="61"/>
         <v>4.4539459522244806E-3</v>
       </c>
       <c r="E137" s="82">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>4.4868858077211637E-3</v>
       </c>
       <c r="F137" s="82">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>4.5202660467162925E-3</v>
       </c>
       <c r="G137" s="82">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>4.5540956039344938E-3</v>
       </c>
       <c r="H137" s="82">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>4.588383730143808E-3</v>
       </c>
       <c r="I137" s="82">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>4.7873347632357843E-3</v>
       </c>
       <c r="J137" s="82">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>4.8226107857294309E-3</v>
       </c>
       <c r="K137" s="82">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>4.8583290788422051E-3</v>
       </c>
       <c r="L137" s="82">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>4.8944986110877053E-3</v>
       </c>
       <c r="M137" s="82">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>4.9311286130344634E-3</v>
       </c>
       <c r="N137" s="82">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>-3.7102333601524151E-4</v>
       </c>
       <c r="O137" s="82">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>-3.7024092721349433E-4</v>
       </c>
       <c r="P137" s="82">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>-3.6940456565504043E-4</v>
       </c>
       <c r="Q137" s="82">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>-3.6851378109714616E-4</v>
       </c>
       <c r="R137" s="82">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>-3.6756807485738285E-4</v>
       </c>
       <c r="S137" s="82">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>1.5129822646253732E-4</v>
       </c>
       <c r="T137" s="82">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>1.4929770617522209E-4</v>
       </c>
       <c r="U137" s="82">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>1.4732301135178538E-4</v>
       </c>
       <c r="V137" s="82">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>1.4537379090973079E-4</v>
       </c>
       <c r="W137" s="82">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>1.4344969851742828E-4</v>
       </c>
       <c r="X137" s="82">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>3.1513166876184773E-4</v>
       </c>
       <c r="Y137" s="82">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>3.1624910499505887E-4</v>
       </c>
       <c r="Z137" s="82">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>3.1721381161220474E-4</v>
       </c>
       <c r="AA137" s="82">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>3.1818192093491238E-4</v>
       </c>
       <c r="AB137" s="82">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>3.1915345367283798E-4</v>
       </c>
       <c r="AC137" s="82">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>-7.3521428764378172E-5</v>
       </c>
       <c r="AD137" s="82">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>-7.3635433235574865E-5</v>
       </c>
       <c r="AE137" s="82">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>-7.3749686606783271E-5</v>
       </c>
       <c r="AF137" s="82">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>-7.3864188427252842E-5</v>
       </c>
       <c r="AG137" s="82">
-        <f t="shared" si="72"/>
+        <f t="shared" si="60"/>
         <v>-7.3978938295304886E-5</v>
       </c>
     </row>
@@ -57111,12 +57101,12 @@
     <tabColor rgb="FF002060"/>
   </sheetPr>
   <dimension ref="A1:AF7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32">
       <c r="A1" t="s">
         <v>178</v>
       </c>
@@ -57214,7 +57204,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:32">
       <c r="A2" t="s">
         <v>172</v>
       </c>
@@ -57343,7 +57333,7 @@
         <v>5.5925664622652749E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:32">
       <c r="A3" t="s">
         <v>173</v>
       </c>
@@ -57472,7 +57462,7 @@
         <v>-7.3978938295304886E-5</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:32">
       <c r="A4" t="s">
         <v>174</v>
       </c>
@@ -57570,7 +57560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:32">
       <c r="A5" t="s">
         <v>175</v>
       </c>
@@ -57668,7 +57658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:32">
       <c r="A6" t="s">
         <v>176</v>
       </c>
@@ -57766,7 +57756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:32">
       <c r="A7" t="s">
         <v>177</v>
       </c>
@@ -57875,9 +57865,9 @@
     <tabColor rgb="FF002060"/>
   </sheetPr>
   <dimension ref="A1:AF7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32">
       <c r="A1" t="s">
         <v>178</v>
       </c>
@@ -57975,7 +57965,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:32">
       <c r="A2" t="s">
         <v>172</v>
       </c>
@@ -58104,7 +58094,7 @@
         <v>5.3868678908547199E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:32">
       <c r="A3" t="s">
         <v>173</v>
       </c>
@@ -58233,7 +58223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:32">
       <c r="A4" t="s">
         <v>174</v>
       </c>
@@ -58331,7 +58321,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:32">
       <c r="A5" t="s">
         <v>175</v>
       </c>
@@ -58429,7 +58419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:32">
       <c r="A6" t="s">
         <v>176</v>
       </c>
@@ -58527,7 +58517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:32">
       <c r="A7" t="s">
         <v>177</v>
       </c>
@@ -58636,9 +58626,9 @@
     <tabColor rgb="FF002060"/>
   </sheetPr>
   <dimension ref="A1:AF7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32">
       <c r="A1" t="s">
         <v>178</v>
       </c>
@@ -58736,7 +58726,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:32">
       <c r="A2" t="s">
         <v>172</v>
       </c>
@@ -58865,7 +58855,7 @@
         <v>-2.7263052731958393E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:32">
       <c r="A3" t="s">
         <v>173</v>
       </c>
@@ -58994,7 +58984,7 @@
         <v>1.2829792993040989E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:32">
       <c r="A4" t="s">
         <v>174</v>
       </c>
@@ -59092,7 +59082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:32">
       <c r="A5" t="s">
         <v>175</v>
       </c>
@@ -59190,7 +59180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:32">
       <c r="A6" t="s">
         <v>176</v>
       </c>
@@ -59288,7 +59278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:32">
       <c r="A7" t="s">
         <v>177</v>
       </c>
@@ -59397,9 +59387,9 @@
     <tabColor rgb="FF002060"/>
   </sheetPr>
   <dimension ref="A1:AF7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32">
       <c r="A1" t="s">
         <v>178</v>
       </c>
@@ -59497,7 +59487,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:32">
       <c r="A2" t="s">
         <v>172</v>
       </c>
@@ -59595,7 +59585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:32">
       <c r="A3" t="s">
         <v>173</v>
       </c>
@@ -59693,7 +59683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:32">
       <c r="A4" t="s">
         <v>174</v>
       </c>
@@ -59791,7 +59781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:32">
       <c r="A5" t="s">
         <v>175</v>
       </c>
@@ -59889,7 +59879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:32">
       <c r="A6" t="s">
         <v>176</v>
       </c>
@@ -59987,7 +59977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:32">
       <c r="A7" t="s">
         <v>177</v>
       </c>
